--- a/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$H$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -490,32 +490,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BY1047</t>
+          <t>GRY2BR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IIT</t>
+          <t>ISLL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2013-03-14</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Byggteknik</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bärkraftigt byggande och boende</t>
+          <t>Ryska V: Samtida rysk litteratur och kultur</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -525,39 +525,39 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GIK289</t>
+          <t>GKI2W3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IIT</t>
+          <t>ISLL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Informatik</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Objektorienterad programmering och problemlösning</t>
+          <t>Kinesiska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -567,19 +567,19 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GRY2BR</t>
+          <t>GKI3C9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -589,17 +589,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ryska V: Samtida rysk litteratur och kultur</t>
+          <t>Kinesiska för affärslivet II</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -609,432 +609,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>GKI2W3</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>KIA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2022-04-28</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Kinesiska</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Kinesiska I med didaktisk inriktning</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>AHI29Q</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>HIA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2023-10-05</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Historia</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Historievetenskaplig litteraturkurs</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>AHI29R</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>HIA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2023-10-05</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Historia</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Historievetenskapens teori och metod</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29R</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>GFI37Z</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>FIA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2023-12-07</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Filosofi</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Gud och bevisen: filosofiska argument för och mot Guds existens</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI37Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>GIH3AQ</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>IDA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>IHV</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2024-02-27</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Styrketräningens teori och praktiska tillämpning</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>GKI3C9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>KIA</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Kinesiska</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Kinesiska för affärslivet II</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>GPG3CN</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Pedagogiskt arbete</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Undervisning och lärande genom rollspel - inriktning pedagogiskt arbete</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>GHI3CP</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>HIA</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Historia</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Undervisning och lärande genom rollspel – inriktning historiedidaktik</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3CP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>GRK3CQ</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>RKA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Religionsvetenskap</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Undervisning och lärande genom rollspel – inriktning religionsdidaktik</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>APG2CC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Pedagogiskt arbete</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Mentorsutbildning för en kvalitativ introduktionsperiod</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H14"/>
+  <autoFilter ref="A1:H4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
@@ -1042,26 +622,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$H$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -490,12 +490,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GRY2BR</t>
+          <t>EN3029</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -505,17 +505,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2008-01-11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ryska V: Samtida rysk litteratur och kultur</t>
+          <t>Engelska: Samtida irländsk skönlitteratur</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -525,19 +525,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>AR1003</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -547,17 +547,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2008-10-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kinesiska I med didaktisk inriktning</t>
+          <t>Den moderna arabiska novellen</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -567,54 +567,6060 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>AR1004</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2008-10-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Arabiska</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Arabiska dialekter med inriktning på den Syriska</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>AR1007</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2009-04-24</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Arabiska</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Arabiska dialekter med inriktning på den syriska II</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>AR1009</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Arabiska</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Arabiska dialekter: Syriska III</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>AR1012</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2010-09-21</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Arabiska</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Arabiska dialekter: Syriska IV</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>KI1030</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kinesiska i tal och skrift IV</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>KI2001</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kinesisk modern litteratur I</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>AR2001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2011-11-29</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Arabiska</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Arabiska VIII</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>KI1031</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2011-11-29</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kinesiska i tal och konversation</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>EN1086</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2012-02-16</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Engelsk språkstruktur</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>AR1018</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2012-04-19</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Arabiska</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Arabiska för nybörjare I</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>EN2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Litteratur och teori</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk III - Andraspråksforskning</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>AR1025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2013-06-14</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Arabiska</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Arabiska VI - muntlig kommunikation</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>JP1045</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2013-10-31</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Att kommunicera på japanskt vis</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>JP1046</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2013-10-31</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Att göra affärer i Japan</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1046</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TY3012</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Tyska</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tyska: Språkvetenskapens historia</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TY3013</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Tyska</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tyska: Modern kvinnolitteratur</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>EN3064</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2013-12-09</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Engelska: Avancerad litteraturteori</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SS3004</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2014-04-11</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk i ett tvärspråkligt perspektiv</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>KI1043</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2014-07-11</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kinesisk textläsning på medelnivå</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>PR2005</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Portugisiska</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Portugisiska: Vetenskaplig metod och akademiskt skrivande</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SS3007</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Flerspråkighet, interaktion och identitetsskapande i klassrum</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>KI2012</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2015-02-05</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kinesiska: Forskningsmetodik</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SS1085</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2015-03-03</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk för lärare åk 7-9, 45 hp (1-45). Ingår i Lärarlyftet II</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>EN3070</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Engelska IV, examensarbete 2 för ämneslärarexamen, åk 7-9</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>EN3071</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Engelska IV, inklusive examensarbete 2 för ämneslärarexamen, gy</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>AR2006</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2015-06-15</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Arabiska</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Arabiska: Avancerad grammatik II</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>AR2007</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2015-06-15</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Arabiska</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Det egna jaget och den andre – gestaltning i arabisk litteratur</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>AR2009</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2015-09-15</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Arabiska</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Modern arabisk litteratur och sökandet efter frihet</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>AR2010</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2015-09-15</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Arabiska</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Arabiska: Avancerad grammatik</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>AR2011</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2015-09-18</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Arabiska</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Den arabiska akademiska kanon</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>EN1129</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2015-10-09</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Engelska: Skriftlig språkfärdighet</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>SS3010</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2015-12-14</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Svensk fonologi i ett andraspråksperspektiv</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>EN2046</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Engelska III, inklusive examensarbete 1 för ämneslärarexamen, gy</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>EN2047</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Engelska III, examensarbete 1 för ämneslärarexamen, åk 7-9</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>JP2013</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2016-04-15</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Japanska: Modern och nutida litteratur</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>SS3014</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2016-11-18</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Flerspråkighet i ett samhällsperspektiv</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>KI1051</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2017-12-01</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Kinesiska: grundläggande språkfärdighet</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>GEN222</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2018-03-22</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Engelska för lärare, 45 hp (1-45 hp), åk 7-9 - ingår i Lärarlyftet II</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>GSS22M</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2018-04-19</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Studiehandledning på modersmål</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>GSS22P</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2018-04-19</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Den globala skolan - förskola och grundskola</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>GTY23C</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2018-06-05</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Tyska</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tyskspråkig barn- och ungdomslitteratur</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>GJP243</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Japanska IV: Språkfärdighet</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>GFR27N</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2019-03-07</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Franska: Skriftlig språkfärdighet II</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>GFR27Q</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2019-03-07</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Franska II: Introduktion till lingvistik och akademiskt skrivande</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>GFR27R</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2019-03-07</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Franskspråkig litteratur II: Fram till 1900</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>GKI27M</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2019-03-08</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Kinesiska V: Fördjupningskurs i modern kinesiska</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>GFR27S</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2019-03-11</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Franska med inriktning arbetsliv</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>GFR283</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2019-03-12</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Litteratur och kultur i Maghrebregionen</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>GSV2BN</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Svenska</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Svenska: Text och tal</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>GSV2BP</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Svenska</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Svenska: Barn- och ungdomslitteratur i samhällsdialog</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>ARY23F</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2019-10-09</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ryska</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ryska VI: Stalintidens ideologi och estetik</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>GRY2BR</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2019-10-09</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Ryska</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Ryska V: Samtida rysk litteratur och kultur</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>AJP23N</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Introduktion till interkulturella litteraturstudier</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>AJP23P</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Interkulturella litteraturstudier: Akademiskt skrivande</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>AJP23Q</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Världslitteraturer: Asien och Europa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>AJP23R</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Världslitteraturer: Nord- och Sydamerika</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>AFR24Z</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2020-03-09</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Franska: Argumentation och retorik</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>GSS2G8</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk för lärare i åk 4-6, 30 hp (1-30 hp). Ingår i Lärarlyftet.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>ARY25M</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2020-04-21</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Ryska</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ryska VI: Det virtuella Ryssland: politik, språk och nya medier</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>GSS2GP</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2020-04-27</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Modersmål: Arabiska III med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>GEN2HB</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Engelska för internationellt företagande: kommunikation och kultur</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>GRY2HL</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Ryska</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Introduktion till rysk opera 1</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>AJP25X</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2020-09-02</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Interkulturella litteraturstudier: Litteratur och genus - teori och kritik</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>GFR2HZ</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2020-09-04</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Franska: Förberedande kurs IV</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>GSS2J5</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Svenska i vardags-, samhälls- och arbetsliv för internationella studenter</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>GSS2JA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>GEN2JG</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Engelska, Språkdidaktik I</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>GSP2JH</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Spanska</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Spanska för lärare åk 7-9, 45 hp (1-45 hp). Ingår i Lärarlyftet.</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>AJP264</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Migrationslitteratur i dåtid och nutid</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>GFR2KQ</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2020-11-11</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Franska III: Språkhistoria</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>GFR2KR</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2020-11-11</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Franska: Examensarbete för kandidatexamen</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>GSP2KS</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2020-11-20</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Spanska</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Spanska III Lingvistisk inriktning: Kandidatexamensarbete</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>GSS2L2</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Modersmål: Arabiska I med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>GSS2MN</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2021-02-25</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk II med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>GKI2MY</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2021-03-02</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Kinesiska II med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N3</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Tyska</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tyska: Språk och nya medier</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N4</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Tyska</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tyskspråkig nutidslitteratur och litteraturkritik</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>GKI2PX</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2021-05-03</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Kinesiska: skriftlig tillämpning</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>GKI2PY</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2021-05-03</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Kinesiska i tal och skrift III</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>GKI2Q2</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2021-05-04</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Kinesisk språkstruktur</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>GSS2QV</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>GFR2R3</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Franska II: Muntlig franska</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>GFR2R4</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Franska II med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>AJP26Z</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>GEN2RZ</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>AJP278</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Interkulturella litteraturstudier: Teori och metod</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>AJP279</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>AJP27A</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>AJP27B</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>GAR2SQ</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Arabiska</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Modern arabisk litteratur</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>GTY2ST</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Tyska</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tyska: Tysk grammatik med textkommentar</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>GTY2SV</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Tyska</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>GIT2T6</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Italienska</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Italienska nobelpristagare i litteratur</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>GIT2TD</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Italienska</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>GIT2TG</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Italienska</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Italienska A: Kultur och samhälle, norra Italien</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>GIT2TH</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Italienska</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>GIT2TJ</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Italienska</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>GIT2TK</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Italienska</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>GIT2TM</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Italienska</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>GIT2TN</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Italienska</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Italienska A: Textanalys, deckargenren</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>GEN2VE</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Engelskspråkig litteratur</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>GKI2VL</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Kinas kultur och samhälle - introduktionskurs</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>GFR2W9</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Franska: Språkdidaktik I</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>GFR2WA</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Franska I med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>GKI2W3</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Kinesiska I med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>AJP287</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Japanska: Interkulturell kommunikation</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>GSS2XE</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>GIT2Y9</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Italienska</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Italienska A: Textanalys, familjeskildringar</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>GIT2YA</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Italienska</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Italienska A: Textanalys, krig och fred</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>GIT2YB</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Italienska</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>GIT2YC</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Italienska</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>GIT2YD</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Italienska</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Italienska A: Textanalys, kvinnoskildringar</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>GRY325</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Ryska</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Introduktion till rysk opera 2</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>GTY32H</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2023-01-27</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Tyska</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Tyska: Språkdidaktik II</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>AKI28Y</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>GFR35F</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>GSS35H</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>AFR29D</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>ATY29E</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Tyska</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>GRY36G</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Ryska</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Introduktion till rysk film</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>GRY36H</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Ryska</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Sovjetisk och postsovjetisk science fiction-film</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>GRY37X</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Ryska</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>AJP2A9</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>GSP39N</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Spanska</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Spanska: Förberedande kurs</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>GSS39R</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>GSS39S</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Den globala skolan - undervisning inom grundskolan</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>GSS39T</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>GSS39U</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>AJP2AH</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Klassisk japanska</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>GEN3BR</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Kulturella texter och kontexter</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
           <t>GKI3C9</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>KIA</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
         <is>
           <t>2024-06-19</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>Kinesiska</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>Kinesiska för affärslivet II</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>GKI3CD</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Kinesiska: Kandidatexamensarbete</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>GKI3CE</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Kinesiska III med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B7</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Tyska</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Tyska: Språk, media och AI</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>GFR3DL</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>GPR3E5</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Portugisiska</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>GSV3FP</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Svenska</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>GFR3HL</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Franska: Språkdidaktik II</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HE</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Sociolingvistiska perspektiv på modersmålsundervisning</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HF</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Flerspråkiga perspektiv på skriftspråksutveckling</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>GSV3JE</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Svenska</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>GSS3K2</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>GEN3K3</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Engelska II</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H4"/>
+  <autoFilter ref="A1:H147"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
@@ -622,6 +6628,292 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId292"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$H$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$H$149</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H147"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6619,8 +6619,92 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CP</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Svenska</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CQ</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Svenska</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H147"/>
+  <autoFilter ref="A1:H149"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
@@ -6914,6 +6998,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId290"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId296"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$H$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$149</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,17 +432,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H149"/>
+  <dimension ref="A1:I149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="58" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,20 +469,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Ämnesnamn</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Kursnamn</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -490,12 +496,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>EN3029</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -505,39 +511,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2008-01-11</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Engelska</t>
-        </is>
-      </c>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Engelska: Samtida irländsk skönlitteratur</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
+          <t>Svenska som andraspråk III - Andraspråksforskning</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AR1003</t>
+          <t>JP1045</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -547,39 +554,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2008-10-23</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Arabiska</t>
-        </is>
-      </c>
+          <t>2013-10-31</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Den moderna arabiska novellen</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
+          <t>Att kommunicera på japanskt vis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AR1004</t>
+          <t>JP1046</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -589,39 +597,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2008-10-23</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Arabiska</t>
-        </is>
-      </c>
+          <t>2013-10-31</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arabiska dialekter med inriktning på den Syriska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
+          <t>Att göra affärer i Japan</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1046</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AR1007</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -631,39 +640,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2009-04-24</t>
+          <t>2011-02-01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>2013-11-04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arabiska dialekter med inriktning på den syriska II</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
+          <t>Kinesiska i tal och skrift IV</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AR1009</t>
+          <t>SS3004</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -673,39 +687,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Arabiska</t>
-        </is>
-      </c>
+          <t>2014-04-11</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arabiska dialekter: Syriska III</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
+          <t>Svenska som andraspråk i ett tvärspråkligt perspektiv</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AR1012</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -715,39 +730,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2010-09-21</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Arabiska</t>
-        </is>
-      </c>
+          <t>2014-07-11</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arabiska dialekter: Syriska IV</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
+          <t>Kinesisk textläsning på medelnivå</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -757,34 +773,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Kinesiska</t>
-        </is>
-      </c>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kinesiska i tal och skrift IV</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>Flerspråkighet, interaktion och identitetsskapande i klassrum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KI2001</t>
+          <t>KI2012</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -799,39 +816,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+          <t>2015-02-05</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Kinesiska</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Kinesisk modern litteratur I</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
+          <t>Kinesiska: Forskningsmetodik</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -841,39 +859,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2011-11-29</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Arabiska</t>
-        </is>
-      </c>
+          <t>2015-03-03</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arabiska VIII</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>Svenska som andraspråk för lärare åk 7-9, 45 hp (1-45). Ingår i Lärarlyftet II</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>KI1031</t>
+          <t>EN3070</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -883,34 +902,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2011-11-29</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Kinesiska</t>
-        </is>
-      </c>
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kinesiska i tal och konversation</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
+          <t>Engelska IV, examensarbete 2 för ämneslärarexamen, åk 7-9</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EN1086</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -925,39 +945,40 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2012-02-16</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Engelska</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Engelsk språkstruktur</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
+          <t>Engelska IV, inklusive examensarbete 2 för ämneslärarexamen, gy</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AR1018</t>
+          <t>EN1129</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -967,34 +988,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2012-04-19</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Arabiska</t>
-        </is>
-      </c>
+          <t>2015-10-09</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arabiska för nybörjare I</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
+          <t>Engelska: Skriftlig språkfärdighet</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>EN2025</t>
+          <t>EN3064</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1009,34 +1031,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
+          <t>2013-12-09</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>2015-11-03</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Engelska</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Litteratur och teori</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
+          <t>Engelska: Avancerad litteraturteori</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS3010</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1051,39 +1078,40 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+          <t>2015-12-14</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Svenska som andraspråk</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Svenska som andraspråk III - Andraspråksforskning</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>Svensk fonologi i ett andraspråksperspektiv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AR1025</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1093,39 +1121,40 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2013-06-14</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Arabiska</t>
-        </is>
-      </c>
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arabiska VI - muntlig kommunikation</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
+          <t>Engelska III, inklusive examensarbete 1 för ämneslärarexamen, gy</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>JP1045</t>
+          <t>EN2047</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1135,39 +1164,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2013-10-31</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Japanska</t>
-        </is>
-      </c>
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Att kommunicera på japanskt vis</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+          <t>Engelska III, examensarbete 1 för ämneslärarexamen, åk 7-9</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>JP1046</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1177,39 +1207,44 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2013-10-31</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>2016-04-14</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Att göra affärer i Japan</t>
+          <t>Portugisiska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1046</t>
+          <t>Portugisiska: Vetenskaplig metod och akademiskt skrivande</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TY3012</t>
+          <t>JP2013</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1219,39 +1254,40 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Tyska</t>
-        </is>
-      </c>
+          <t>2016-04-15</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tyska: Språkvetenskapens historia</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+          <t>Japanska: Modern och nutida litteratur</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TY3013</t>
+          <t>EN2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1261,39 +1297,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>2016-05-26</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tyska: Modern kvinnolitteratur</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+          <t>Litteratur och teori</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>EN3064</t>
+          <t>SS3014</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1303,39 +1344,40 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2013-12-09</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Engelska</t>
-        </is>
-      </c>
+          <t>2016-11-18</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Engelska: Avancerad litteraturteori</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
+          <t>Flerspråkighet i ett samhällsperspektiv</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SS3004</t>
+          <t>AR1025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1345,39 +1387,44 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2014-04-11</t>
+          <t>2013-06-14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk i ett tvärspråkligt perspektiv</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+          <t>Arabiska VI - muntlig kommunikation</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>AR2006</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1387,39 +1434,44 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2014-07-11</t>
+          <t>2015-06-15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kinesisk textläsning på medelnivå</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>Arabiska: Avancerad grammatik II</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2006</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>AR2007</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1429,39 +1481,44 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2015-06-15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Portugisiska</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Portugisiska: Vetenskaplig metod och akademiskt skrivande</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>Det egna jaget och den andre – gestaltning i arabisk litteratur</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2007</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>AR2009</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1471,39 +1528,44 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2015-09-15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Flerspråkighet, interaktion och identitetsskapande i klassrum</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>Modern arabisk litteratur och sökandet efter frihet</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>KI2012</t>
+          <t>AR2010</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1513,39 +1575,44 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2015-02-05</t>
+          <t>2015-09-15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kinesiska: Forskningsmetodik</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
+          <t>Arabiska: Avancerad grammatik</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>AR2011</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1555,39 +1622,44 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare åk 7-9, 45 hp (1-45). Ingår i Lärarlyftet II</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>Den arabiska akademiska kanon</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>EN3070</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1597,34 +1669,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2015-03-12</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Engelska</t>
-        </is>
-      </c>
+          <t>2017-12-01</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Engelska IV, examensarbete 2 för ämneslärarexamen, åk 7-9</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
+          <t>Kinesiska: grundläggande språkfärdighet</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>GEN222</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1639,39 +1712,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2015-03-12</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+          <t>2018-03-22</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Engelska</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Engelska IV, inklusive examensarbete 2 för ämneslärarexamen, gy</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>Engelska för lärare, 45 hp (1-45 hp), åk 7-9 - ingår i Lärarlyftet II</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>AR2006</t>
+          <t>GSS22M</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1681,39 +1755,40 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2015-06-15</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Arabiska</t>
-        </is>
-      </c>
+          <t>2018-04-19</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arabiska: Avancerad grammatik II</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2006</t>
+          <t>Studiehandledning på modersmål</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>AR2007</t>
+          <t>GSS22P</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1723,39 +1798,40 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2015-06-15</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Arabiska</t>
-        </is>
-      </c>
+          <t>2018-04-19</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Det egna jaget och den andre – gestaltning i arabisk litteratur</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2007</t>
+          <t>Den globala skolan - förskola och grundskola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>AR2009</t>
+          <t>GTY23C</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1765,39 +1841,40 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2015-09-15</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Arabiska</t>
-        </is>
-      </c>
+          <t>2018-06-05</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Modern arabisk litteratur och sökandet efter frihet</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+          <t>Tyskspråkig barn- och ungdomslitteratur</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>AR2010</t>
+          <t>GJP243</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1807,39 +1884,40 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2015-09-15</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Arabiska</t>
-        </is>
-      </c>
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arabiska: Avancerad grammatik</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+          <t>Japanska IV: Språkfärdighet</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>AR2011</t>
+          <t>GFR27N</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1849,39 +1927,40 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Arabiska</t>
-        </is>
-      </c>
+          <t>2019-03-07</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Den arabiska akademiska kanon</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
+          <t>Franska: Skriftlig språkfärdighet II</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>EN1129</t>
+          <t>GFR27Q</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1891,39 +1970,40 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2015-10-09</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Engelska</t>
-        </is>
-      </c>
+          <t>2019-03-07</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Engelska: Skriftlig språkfärdighet</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
+          <t>Franska II: Introduktion till lingvistik och akademiskt skrivande</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SS3010</t>
+          <t>GFR27R</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1933,39 +2013,40 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2015-12-14</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Svenska som andraspråk</t>
-        </is>
-      </c>
+          <t>2019-03-07</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svensk fonologi i ett andraspråksperspektiv</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
+          <t>Franskspråkig litteratur II: Fram till 1900</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EN2046</t>
+          <t>GKI27M</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1975,39 +2056,40 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2016-02-05</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Engelska</t>
-        </is>
-      </c>
+          <t>2019-03-08</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Engelska III, inklusive examensarbete 1 för ämneslärarexamen, gy</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+          <t>Kinesiska V: Fördjupningskurs i modern kinesiska</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>EN2047</t>
+          <t>GFR27S</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2017,39 +2099,40 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2016-02-05</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Engelska</t>
-        </is>
-      </c>
+          <t>2019-03-11</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Engelska III, examensarbete 1 för ämneslärarexamen, åk 7-9</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
+          <t>Franska med inriktning arbetsliv</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>JP2013</t>
+          <t>GFR283</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2059,39 +2142,40 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Japanska</t>
-        </is>
-      </c>
+          <t>2019-03-12</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Japanska: Modern och nutida litteratur</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
+          <t>Litteratur och kultur i Maghrebregionen</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>SS3014</t>
+          <t>GSV2BN</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2101,39 +2185,40 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2016-11-18</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Svenska som andraspråk</t>
-        </is>
-      </c>
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Flerspråkighet i ett samhällsperspektiv</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
+          <t>Svenska: Text och tal</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>GSV2BP</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2143,39 +2228,40 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Kinesiska</t>
-        </is>
-      </c>
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kinesiska: grundläggande språkfärdighet</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>Svenska: Barn- och ungdomslitteratur i samhällsdialog</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GEN222</t>
+          <t>ARY23F</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2185,39 +2271,40 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2018-03-22</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Engelska</t>
-        </is>
-      </c>
+          <t>2019-10-09</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Engelska för lärare, 45 hp (1-45 hp), åk 7-9 - ingår i Lärarlyftet II</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
+          <t>Ryska VI: Stalintidens ideologi och estetik</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GSS22M</t>
+          <t>GRY2BR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2227,39 +2314,40 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2018-04-19</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Svenska som andraspråk</t>
-        </is>
-      </c>
+          <t>2019-10-09</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Studiehandledning på modersmål</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
+          <t>Ryska V: Samtida rysk litteratur och kultur</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GSS22P</t>
+          <t>AR1003</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2269,39 +2357,44 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2018-04-19</t>
+          <t>2008-10-23</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>2019-12-20</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Den globala skolan - förskola och grundskola</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
+          <t>Den moderna arabiska novellen</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GTY23C</t>
+          <t>AR1018</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2311,39 +2404,44 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2012-04-19</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>2019-12-20</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tyskspråkig barn- och ungdomslitteratur</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
+          <t>Arabiska för nybörjare I</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GJP243</t>
+          <t>TY3012</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2353,39 +2451,44 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>2019-12-20</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Japanska IV: Språkfärdighet</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
+          <t>Tyska: Språkvetenskapens historia</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GFR27N</t>
+          <t>AJP23N</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2395,39 +2498,40 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Franska</t>
-        </is>
-      </c>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Franska: Skriftlig språkfärdighet II</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
+          <t>Introduktion till interkulturella litteraturstudier</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GFR27Q</t>
+          <t>AJP23P</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2437,39 +2541,40 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Franska</t>
-        </is>
-      </c>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Franska II: Introduktion till lingvistik och akademiskt skrivande</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
+          <t>Interkulturella litteraturstudier: Akademiskt skrivande</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GFR27R</t>
+          <t>AJP23Q</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2479,39 +2584,40 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Franska</t>
-        </is>
-      </c>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Franskspråkig litteratur II: Fram till 1900</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
+          <t>Världslitteraturer: Asien och Europa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GKI27M</t>
+          <t>AJP23R</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2521,34 +2627,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2019-03-08</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Kinesiska</t>
-        </is>
-      </c>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kinesiska V: Fördjupningskurs i modern kinesiska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
+          <t>Världslitteraturer: Nord- och Sydamerika</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GFR27S</t>
+          <t>AFR24Z</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2563,39 +2670,40 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2019-03-11</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
+          <t>2020-03-09</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
         <is>
           <t>Franska</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Franska med inriktning arbetsliv</t>
-        </is>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
+          <t>Franska: Argumentation och retorik</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GFR283</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2605,39 +2713,40 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2019-03-12</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Franska</t>
-        </is>
-      </c>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Litteratur och kultur i Maghrebregionen</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
+          <t>Svenska som andraspråk för lärare i åk 4-6, 30 hp (1-30 hp). Ingår i Lärarlyftet.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GSV2BN</t>
+          <t>ARY25M</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2647,39 +2756,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Svenska</t>
-        </is>
-      </c>
+          <t>2020-04-21</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svenska: Text och tal</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
+          <t>Ryska VI: Det virtuella Ryssland: politik, språk och nya medier</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GSV2BP</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2689,39 +2799,40 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Svenska</t>
-        </is>
-      </c>
+          <t>2020-04-27</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svenska: Barn- och ungdomslitteratur i samhällsdialog</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
+          <t>Modersmål: Arabiska III med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>ARY23F</t>
+          <t>GEN2HB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2731,39 +2842,40 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Ryska</t>
-        </is>
-      </c>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ryska VI: Stalintidens ideologi och estetik</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
+          <t>Engelska för internationellt företagande: kommunikation och kultur</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GRY2BR</t>
+          <t>EN1086</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2773,39 +2885,44 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2012-02-16</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ryska V: Samtida rysk litteratur och kultur</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
+          <t>Engelsk språkstruktur</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>AJP23N</t>
+          <t>EN3029</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2815,39 +2932,44 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
+          <t>2008-01-11</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Introduktion till interkulturella litteraturstudier</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
+          <t>Engelska: Samtida irländsk skönlitteratur</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>AJP23P</t>
+          <t>KI2001</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2857,39 +2979,44 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
+          <t>2011-02-01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademiskt skrivande</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
+          <t>Kinesisk modern litteratur I</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AJP23Q</t>
+          <t>AR1004</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2899,39 +3026,44 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
+          <t>2008-10-23</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Världslitteraturer: Asien och Europa</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
+          <t>Arabiska dialekter med inriktning på den Syriska</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AJP23R</t>
+          <t>AR1007</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2941,39 +3073,44 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
+          <t>2009-04-24</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Världslitteraturer: Nord- och Sydamerika</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
+          <t>Arabiska dialekter med inriktning på den syriska II</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AFR24Z</t>
+          <t>AR1009</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2983,39 +3120,44 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2020-03-09</t>
+          <t>2009-12-01</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Franska: Argumentation och retorik</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
+          <t>Arabiska dialekter: Syriska III</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>AR1012</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3025,39 +3167,44 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2010-09-21</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i åk 4-6, 30 hp (1-30 hp). Ingår i Lärarlyftet.</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>Arabiska dialekter: Syriska IV</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>ARY25M</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3067,39 +3214,44 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2020-04-21</t>
+          <t>2011-11-29</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ryska VI: Det virtuella Ryssland: politik, språk och nya medier</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
+          <t>Arabiska VIII</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>KI1031</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3109,39 +3261,44 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2020-04-27</t>
+          <t>2011-11-29</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska III med didaktisk inriktning</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>Kinesiska i tal och konversation</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GEN2HB</t>
+          <t>GRY2HL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3151,39 +3308,40 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Engelska</t>
-        </is>
-      </c>
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Engelska för internationellt företagande: kommunikation och kultur</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
+          <t>Introduktion till rysk opera 1</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GRY2HL</t>
+          <t>AJP25X</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3193,39 +3351,40 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Ryska</t>
-        </is>
-      </c>
+          <t>2020-09-02</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Introduktion till rysk opera 1</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
+          <t>Interkulturella litteraturstudier: Litteratur och genus - teori och kritik</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>AJP25X</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3235,39 +3394,40 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Japanska</t>
-        </is>
-      </c>
+          <t>2020-09-04</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Litteratur och genus - teori och kritik</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
+          <t>Franska: Förberedande kurs IV</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GFR2HZ</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3277,34 +3437,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Franska</t>
-        </is>
-      </c>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Franska: Förberedande kurs IV</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+          <t>Svenska i vardags-, samhälls- och arbetsliv för internationella studenter</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3319,39 +3480,40 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
         <is>
           <t>Svenska som andraspråk</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Svenska i vardags-, samhälls- och arbetsliv för internationella studenter</t>
-        </is>
-      </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>GEN2JG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3361,39 +3523,40 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Svenska som andraspråk</t>
-        </is>
-      </c>
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>Engelska, Språkdidaktik I</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GEN2JG</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3406,36 +3569,37 @@
           <t>2020-09-21</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Engelska</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Engelska, Språkdidaktik I</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
+          <t>Spanska för lärare åk 7-9, 45 hp (1-45 hp). Ingår i Lärarlyftet.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>AJP264</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3445,39 +3609,40 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Spanska</t>
-        </is>
-      </c>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spanska för lärare åk 7-9, 45 hp (1-45 hp). Ingår i Lärarlyftet.</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>Migrationslitteratur i dåtid och nutid</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>AJP264</t>
+          <t>GFR2KQ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3487,34 +3652,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Japanska</t>
-        </is>
-      </c>
+          <t>2020-11-11</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Migrationslitteratur i dåtid och nutid</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
+          <t>Franska III: Språkhistoria</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GFR2KQ</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3532,36 +3698,37 @@
           <t>2020-11-11</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
         <is>
           <t>Franska</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Franska III: Språkhistoria</t>
-        </is>
-      </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
+          <t>Franska: Examensarbete för kandidatexamen</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GFR2KR</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3571,39 +3738,40 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Franska</t>
-        </is>
-      </c>
+          <t>2020-11-20</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Franska: Examensarbete för kandidatexamen</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+          <t>Spanska III Lingvistisk inriktning: Kandidatexamensarbete</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3613,34 +3781,35 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Spanska</t>
-        </is>
-      </c>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spanska III Lingvistisk inriktning: Kandidatexamensarbete</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>Modersmål: Arabiska I med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3655,39 +3824,40 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
+          <t>2021-02-25</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Svenska som andraspråk</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Modersmål: Arabiska I med didaktisk inriktning</t>
-        </is>
-      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>Svenska som andraspråk II med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3697,39 +3867,40 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Svenska som andraspråk</t>
-        </is>
-      </c>
+          <t>2021-03-02</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk II med didaktisk inriktning</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>Kinesiska II med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3739,34 +3910,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Kinesiska</t>
-        </is>
-      </c>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kinesiska II med didaktisk inriktning</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>Tyska: Språk och nya medier</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>GTY2N4</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3784,36 +3956,37 @@
           <t>2021-03-04</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
         <is>
           <t>Tyska</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Tyska: Språk och nya medier</t>
-        </is>
-      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>Tyskspråkig nutidslitteratur och litteraturkritik</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GTY2N4</t>
+          <t>GKI2PX</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3823,34 +3996,35 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Tyska</t>
-        </is>
-      </c>
+          <t>2021-05-03</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tyskspråkig nutidslitteratur och litteraturkritik</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
+          <t>Kinesiska: skriftlig tillämpning</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GKI2PX</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3868,31 +4042,32 @@
           <t>2021-05-03</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
         <is>
           <t>Kinesiska</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Kinesiska: skriftlig tillämpning</t>
-        </is>
-      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
+          <t>Kinesiska i tal och skrift III</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GKI2Q2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3907,39 +4082,40 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
+          <t>2021-05-04</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
         <is>
           <t>Kinesiska</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Kinesiska i tal och skrift III</t>
-        </is>
-      </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>Kinesisk språkstruktur</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2Q2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GKI2Q2</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3949,39 +4125,40 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2021-05-04</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Kinesiska</t>
-        </is>
-      </c>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kinesisk språkstruktur</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2Q2</t>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>GFR2R3</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3991,34 +4168,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Svenska som andraspråk</t>
-        </is>
-      </c>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>Franska II: Muntlig franska</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GFR2R3</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4036,36 +4214,37 @@
           <t>2021-09-06</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
         <is>
           <t>Franska</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Franska II: Muntlig franska</t>
-        </is>
-      </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
+          <t>Franska II med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4078,36 +4257,37 @@
           <t>2021-09-06</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Franska</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Franska II med didaktisk inriktning</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>GEN2RZ</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4117,39 +4297,40 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Japanska</t>
-        </is>
-      </c>
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GEN2RZ</t>
+          <t>AJP278</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4162,31 +4343,32 @@
           <t>2021-11-09</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Engelska</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
+          <t>Interkulturella litteraturstudier: Teori och metod</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AJP278</t>
+          <t>AJP279</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4204,31 +4386,32 @@
           <t>2021-11-09</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
         <is>
           <t>Japanska</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Interkulturella litteraturstudier: Teori och metod</t>
-        </is>
-      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
+          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>AJP279</t>
+          <t>AJP27A</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4246,31 +4429,32 @@
           <t>2021-11-09</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
         <is>
           <t>Japanska</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
-        </is>
-      </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
+          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>AJP27A</t>
+          <t>AJP27B</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4288,36 +4472,37 @@
           <t>2021-11-09</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
         <is>
           <t>Japanska</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
-        </is>
-      </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>AJP27B</t>
+          <t>GAR2SQ</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4327,39 +4512,40 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Japanska</t>
-        </is>
-      </c>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
+          <t>Modern arabisk litteratur</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GAR2SQ</t>
+          <t>GTY2ST</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4369,34 +4555,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Arabiska</t>
-        </is>
-      </c>
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Modern arabisk litteratur</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
+          <t>Tyska: Tysk grammatik med textkommentar</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GTY2ST</t>
+          <t>GTY2SV</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4414,36 +4601,37 @@
           <t>2021-12-16</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
         <is>
           <t>Tyska</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Tyska: Tysk grammatik med textkommentar</t>
-        </is>
-      </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GTY2SV</t>
+          <t>GEN2VE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4453,39 +4641,40 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Tyska</t>
-        </is>
-      </c>
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
+          <t>Engelskspråkig litteratur</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GIT2T6</t>
+          <t>GKI2VL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4495,39 +4684,40 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Italienska</t>
-        </is>
-      </c>
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Italienska nobelpristagare i litteratur</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
+          <t>Kinas kultur och samhälle - introduktionskurs</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GIT2TD</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4537,39 +4727,40 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Italienska</t>
-        </is>
-      </c>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
+          <t>Franska: Språkdidaktik I</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GIT2TG</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4579,39 +4770,40 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Italienska</t>
-        </is>
-      </c>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, norra Italien</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
+          <t>Franska I med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>GKI2W3</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4621,39 +4813,40 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Italienska</t>
-        </is>
-      </c>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>Kinesiska I med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GIT2TJ</t>
+          <t>AJP287</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4663,39 +4856,40 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Italienska</t>
-        </is>
-      </c>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+          <t>Japanska: Interkulturell kommunikation</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4705,39 +4899,40 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Italienska</t>
-        </is>
-      </c>
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GIT2TM</t>
+          <t>GRY325</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4747,39 +4942,40 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Italienska</t>
-        </is>
-      </c>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
+          <t>Introduktion till rysk opera 2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GIT2TN</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4789,39 +4985,40 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Italienska</t>
-        </is>
-      </c>
+          <t>2023-01-27</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, deckargenren</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
+          <t>Tyska: Språkdidaktik II</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GEN2VE</t>
+          <t>AKI28Y</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4831,39 +5028,40 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Engelska</t>
-        </is>
-      </c>
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Engelskspråkig litteratur</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
+          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GKI2VL</t>
+          <t>GFR35F</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4873,39 +5071,40 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Kinesiska</t>
-        </is>
-      </c>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kinas kultur och samhälle - introduktionskurs</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
+          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4915,39 +5114,40 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Franska</t>
-        </is>
-      </c>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Franska: Språkdidaktik I</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>GRY36G</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4957,39 +5157,40 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Franska</t>
-        </is>
-      </c>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Franska I med didaktisk inriktning</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>Introduktion till rysk film</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>GRY36H</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4999,39 +5200,40 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Kinesiska</t>
-        </is>
-      </c>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kinesiska I med didaktisk inriktning</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>Sovjetisk och postsovjetisk science fiction-film</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>AJP287</t>
+          <t>GRY37X</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5041,39 +5243,40 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Japanska</t>
-        </is>
-      </c>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Japanska: Interkulturell kommunikation</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
+          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>AFR29D</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5083,39 +5286,44 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y9</t>
+          <t>AJP2A9</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5125,39 +5333,40 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Italienska</t>
-        </is>
-      </c>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, familjeskildringar</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GIT2YA</t>
+          <t>ATY29E</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5167,39 +5376,44 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, krig och fred</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GIT2YB</t>
+          <t>TY3013</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5209,34 +5423,39 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
+          <t>Tyska: Modern kvinnolitteratur</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GIT2YC</t>
+          <t>GIT2T6</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5251,34 +5470,39 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t>Italienska</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
-        </is>
-      </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
+          <t>Italienska nobelpristagare i litteratur</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GIT2YD</t>
+          <t>GIT2TD</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5293,39 +5517,44 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
           <t>Italienska</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Italienska A: Textanalys, kvinnoskildringar</t>
-        </is>
-      </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
+          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GRY325</t>
+          <t>GIT2TG</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5335,39 +5564,44 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Introduktion till rysk opera 2</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
+          <t>Italienska A: Kultur och samhälle, norra Italien</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5377,39 +5611,44 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tyska: Språkdidaktik II</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>AKI28Y</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5419,39 +5658,44 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
+          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GFR35F</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -5461,39 +5705,44 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
+          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>GIT2TM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5503,39 +5752,44 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>AFR29D</t>
+          <t>GIT2TN</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5545,39 +5799,44 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
+          <t>Italienska A: Textanalys, deckargenren</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>ATY29E</t>
+          <t>GIT2Y9</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5587,39 +5846,44 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+          <t>Italienska A: Textanalys, familjeskildringar</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GRY36G</t>
+          <t>GIT2YA</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5629,39 +5893,44 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Introduktion till rysk film</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
+          <t>Italienska A: Textanalys, krig och fred</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GRY36H</t>
+          <t>GIT2YB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5671,39 +5940,44 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sovjetisk och postsovjetisk science fiction-film</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
+          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GRY37X</t>
+          <t>GIT2YC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5713,39 +5987,44 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
+          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>AJP2A9</t>
+          <t>GIT2YD</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5755,27 +6034,32 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
+          <t>Italienska A: Textanalys, kvinnoskildringar</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
         </is>
       </c>
     </row>
@@ -5800,22 +6084,23 @@
           <t>2023-12-19</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
         <is>
           <t>Spanska</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>Spanska: Förberedande kurs</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
         </is>
@@ -5842,22 +6127,23 @@
           <t>2023-12-19</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
         <is>
           <t>Svenska som andraspråk</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
@@ -5884,22 +6170,23 @@
           <t>2023-12-19</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
         <is>
           <t>Svenska som andraspråk</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>Den globala skolan - undervisning inom grundskolan</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
@@ -5926,22 +6213,23 @@
           <t>2023-12-19</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
         <is>
           <t>Svenska som andraspråk</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>Den globala skolan - undervisning inom gymnasieskolan</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
@@ -5968,22 +6256,23 @@
           <t>2023-12-19</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
         <is>
           <t>Svenska som andraspråk</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
@@ -6010,22 +6299,23 @@
           <t>2024-04-26</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
         <is>
           <t>Japanska</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>Klassisk japanska</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
         </is>
@@ -6052,22 +6342,23 @@
           <t>2024-05-24</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
         <is>
           <t>Engelska</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>Kulturella texter och kontexter</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
         </is>
@@ -6094,22 +6385,23 @@
           <t>2024-06-19</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
         <is>
           <t>Kinesiska</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>Kinesiska för affärslivet II</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
         </is>
@@ -6136,22 +6428,23 @@
           <t>2024-06-19</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
         <is>
           <t>Kinesiska</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t>Kinesiska: Kandidatexamensarbete</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
         </is>
@@ -6178,22 +6471,23 @@
           <t>2024-06-19</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
         <is>
           <t>Kinesiska</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>Kinesiska III med didaktisk inriktning</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
@@ -6220,22 +6514,23 @@
           <t>2024-11-13</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
         <is>
           <t>Tyska</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t>Tyska: Språk, media och AI</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
@@ -6262,22 +6557,23 @@
           <t>2025-01-13</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
         <is>
           <t>Franska</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
@@ -6304,22 +6600,23 @@
           <t>2025-02-03</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
         <is>
           <t>Portugisiska</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
         </is>
@@ -6346,22 +6643,23 @@
           <t>2025-05-14</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
         <is>
           <t>Svenska</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
@@ -6388,22 +6686,23 @@
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
         <is>
           <t>Franska</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t>Franska: Språkdidaktik II</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
         </is>
@@ -6430,22 +6729,23 @@
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
         <is>
           <t>Svenska som andraspråk</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>Sociolingvistiska perspektiv på modersmålsundervisning</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
         </is>
@@ -6472,22 +6772,23 @@
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
         <is>
           <t>Svenska som andraspråk</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>Flerspråkiga perspektiv på skriftspråksutveckling</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
         </is>
@@ -6514,22 +6815,23 @@
           <t>2026-01-27</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
         <is>
           <t>Svenska</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
+      <c r="G145" t="inlineStr">
         <is>
           <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
@@ -6556,22 +6858,23 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
         <is>
           <t>Svenska som andraspråk</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
         </is>
@@ -6598,22 +6901,23 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
         <is>
           <t>Engelska</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>Engelska II</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
@@ -6640,22 +6944,23 @@
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
         <is>
           <t>Svenska</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
@@ -6682,326 +6987,327 @@
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
         <is>
           <t>Svenska</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H149"/>
+  <autoFilter ref="A1:I149"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId220"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId232"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId234"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId236"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId244"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId246"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId248"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId252"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId256"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId258"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId260"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId262"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId264"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId266"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId268"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId270"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId272"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId274"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId276"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId278"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId280"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId282"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId284"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId286"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId288"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId290"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId294"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId296"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$150</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I149"/>
+  <dimension ref="A1:I150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -801,12 +801,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KI2012</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -816,18 +816,18 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2015-02-05</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kinesiska: Forskningsmetodik</t>
+          <t>Litteracitet och flerspråkighet</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -837,19 +837,19 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>KI2012</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -859,18 +859,18 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2015-02-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare åk 7-9, 45 hp (1-45). Ingår i Lärarlyftet II</t>
+          <t>Kinesiska: Forskningsmetodik</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -880,19 +880,19 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>EN3070</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -902,18 +902,18 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2015-03-12</t>
+          <t>2015-03-03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Engelska IV, examensarbete 2 för ämneslärarexamen, åk 7-9</t>
+          <t>Svenska som andraspråk för lärare åk 7-9, 45 hp (1-45). Ingår i Lärarlyftet II</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>EN3070</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Engelska IV, inklusive examensarbete 2 för ämneslärarexamen, gy</t>
+          <t>Engelska IV, examensarbete 2 för ämneslärarexamen, åk 7-9</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -966,14 +966,14 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>EN1129</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2015-10-09</t>
+          <t>2015-03-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -999,7 +999,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Engelska: Skriftlig språkfärdighet</t>
+          <t>Engelska IV, inklusive examensarbete 2 för ämneslärarexamen, gy</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1009,14 +1009,14 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>EN3064</t>
+          <t>EN1129</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1031,14 +1031,10 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2013-12-09</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2015-11-03</t>
-        </is>
-      </c>
+          <t>2015-10-09</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>Engelska</t>
@@ -1046,7 +1042,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Engelska: Avancerad litteraturteori</t>
+          <t>Engelska: Skriftlig språkfärdighet</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1056,19 +1052,19 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>SS3010</t>
+          <t>EN3064</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1078,18 +1074,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2015-12-14</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>2013-12-09</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2015-11-03</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Svensk fonologi i ett andraspråksperspektiv</t>
+          <t>Engelska: Avancerad litteraturteori</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1099,19 +1099,19 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>EN2046</t>
+          <t>SS3010</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1121,18 +1121,18 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2016-02-05</t>
+          <t>2015-12-14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Engelska III, inklusive examensarbete 1 för ämneslärarexamen, gy</t>
+          <t>Svensk fonologi i ett andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>EN2047</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Engelska III, examensarbete 1 för ämneslärarexamen, åk 7-9</t>
+          <t>Engelska III, inklusive examensarbete 1 för ämneslärarexamen, gy</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1185,19 +1185,19 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>EN2047</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1207,22 +1207,18 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2016-04-14</t>
-        </is>
-      </c>
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Portugisiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Portugisiska: Vetenskaplig metod och akademiskt skrivande</t>
+          <t>Engelska III, examensarbete 1 för ämneslärarexamen, åk 7-9</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1232,19 +1228,19 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>JP2013</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1254,18 +1250,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Portugisiska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Japanska: Modern och nutida litteratur</t>
+          <t>Portugisiska: Vetenskaplig metod och akademiskt skrivande</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1275,19 +1275,19 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>EN2025</t>
+          <t>JP2013</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1297,22 +1297,18 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2016-05-26</t>
-        </is>
-      </c>
+          <t>2016-04-15</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Litteratur och teori</t>
+          <t>Japanska: Modern och nutida litteratur</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1322,19 +1318,19 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>SS3014</t>
+          <t>EN2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1344,18 +1340,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2016-11-18</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2016-05-26</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Flerspråkighet i ett samhällsperspektiv</t>
+          <t>Litteratur och teori</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1365,19 +1365,19 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>AR1025</t>
+          <t>SS3014</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1387,22 +1387,18 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2013-06-14</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2017-10-03</t>
-        </is>
-      </c>
+          <t>2016-11-18</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Arabiska VI - muntlig kommunikation</t>
+          <t>Flerspråkighet i ett samhällsperspektiv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1412,14 +1408,14 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>AR2006</t>
+          <t>AR1025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1434,7 +1430,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2015-06-15</t>
+          <t>2013-06-14</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1449,7 +1445,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arabiska: Avancerad grammatik II</t>
+          <t>Arabiska VI - muntlig kommunikation</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1459,14 +1455,14 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AR2007</t>
+          <t>AR2006</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1496,7 +1492,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Det egna jaget och den andre – gestaltning i arabisk litteratur</t>
+          <t>Arabiska: Avancerad grammatik II</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1506,14 +1502,14 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2006</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AR2009</t>
+          <t>AR2007</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1528,7 +1524,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2015-09-15</t>
+          <t>2015-06-15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1543,7 +1539,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Modern arabisk litteratur och sökandet efter frihet</t>
+          <t>Det egna jaget och den andre – gestaltning i arabisk litteratur</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1553,14 +1549,14 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2007</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AR2010</t>
+          <t>AR2009</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1590,7 +1586,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Arabiska: Avancerad grammatik</t>
+          <t>Modern arabisk litteratur och sökandet efter frihet</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1600,14 +1596,14 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AR2011</t>
+          <t>AR2010</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1622,7 +1618,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2015-09-15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1637,7 +1633,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Den arabiska akademiska kanon</t>
+          <t>Arabiska: Avancerad grammatik</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1647,19 +1643,19 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>AR2011</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1669,18 +1665,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>2015-09-18</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Kinesiska: grundläggande språkfärdighet</t>
+          <t>Den arabiska akademiska kanon</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1690,19 +1690,19 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GEN222</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1712,18 +1712,18 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2018-03-22</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Engelska för lärare, 45 hp (1-45 hp), åk 7-9 - ingår i Lärarlyftet II</t>
+          <t>Kinesiska: grundläggande språkfärdighet</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1733,19 +1733,19 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GSS22M</t>
+          <t>GEN222</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1755,18 +1755,18 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2018-04-19</t>
+          <t>2018-03-22</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Studiehandledning på modersmål</t>
+          <t>Engelska för lärare, 45 hp (1-45 hp), åk 7-9 - ingår i Lärarlyftet II</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1776,14 +1776,14 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GSS22P</t>
+          <t>GSS22M</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Den globala skolan - förskola och grundskola</t>
+          <t>Studiehandledning på modersmål</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1819,19 +1819,19 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GTY23C</t>
+          <t>GSS22P</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1841,18 +1841,18 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2018-04-19</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tyskspråkig barn- och ungdomslitteratur</t>
+          <t>Den globala skolan - förskola och grundskola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1862,19 +1862,19 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GJP243</t>
+          <t>GTY23C</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1884,18 +1884,18 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2018-06-05</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Japanska IV: Språkfärdighet</t>
+          <t>Tyskspråkig barn- och ungdomslitteratur</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1905,19 +1905,19 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GFR27N</t>
+          <t>GJP243</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1927,18 +1927,18 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Franska: Skriftlig språkfärdighet II</t>
+          <t>Japanska IV: Språkfärdighet</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1948,14 +1948,14 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GFR27Q</t>
+          <t>GFR27N</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Franska II: Introduktion till lingvistik och akademiskt skrivande</t>
+          <t>Franska: Skriftlig språkfärdighet II</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1991,14 +1991,14 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GFR27R</t>
+          <t>GFR27Q</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Franskspråkig litteratur II: Fram till 1900</t>
+          <t>Franska II: Introduktion till lingvistik och akademiskt skrivande</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2034,19 +2034,19 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GKI27M</t>
+          <t>GFR27R</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2056,18 +2056,18 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2019-03-08</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Kinesiska V: Fördjupningskurs i modern kinesiska</t>
+          <t>Franskspråkig litteratur II: Fram till 1900</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2077,19 +2077,19 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GFR27S</t>
+          <t>GKI27M</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2099,18 +2099,18 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2019-03-11</t>
+          <t>2019-03-08</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Franska med inriktning arbetsliv</t>
+          <t>Kinesiska V: Fördjupningskurs i modern kinesiska</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2120,14 +2120,14 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GFR283</t>
+          <t>GFR27S</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2019-03-12</t>
+          <t>2019-03-11</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Litteratur och kultur i Maghrebregionen</t>
+          <t>Franska med inriktning arbetsliv</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2163,19 +2163,19 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GSV2BN</t>
+          <t>GFR283</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2185,18 +2185,18 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
+          <t>2019-03-12</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Svenska: Text och tal</t>
+          <t>Litteratur och kultur i Maghrebregionen</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2206,14 +2206,14 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GSV2BP</t>
+          <t>GSV2BN</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Svenska: Barn- och ungdomslitteratur i samhällsdialog</t>
+          <t>Svenska: Text och tal</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2249,19 +2249,19 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ARY23F</t>
+          <t>GSV2BP</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2271,18 +2271,18 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ryska VI: Stalintidens ideologi och estetik</t>
+          <t>Svenska: Barn- och ungdomslitteratur i samhällsdialog</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2292,14 +2292,14 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GRY2BR</t>
+          <t>ARY23F</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ryska V: Samtida rysk litteratur och kultur</t>
+          <t>Ryska VI: Stalintidens ideologi och estetik</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2335,19 +2335,19 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>AR1003</t>
+          <t>GRY2BR</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2357,22 +2357,18 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2008-10-23</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2019-10-09</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Den moderna arabiska novellen</t>
+          <t>Ryska V: Samtida rysk litteratur och kultur</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2382,14 +2378,14 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>AR1018</t>
+          <t>AR1003</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2404,7 +2400,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2012-04-19</t>
+          <t>2008-10-23</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2419,7 +2415,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Arabiska för nybörjare I</t>
+          <t>Den moderna arabiska novellen</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2429,19 +2425,19 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>TY3012</t>
+          <t>AR1018</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2451,7 +2447,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2012-04-19</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2461,12 +2457,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tyska: Språkvetenskapens historia</t>
+          <t>Arabiska för nybörjare I</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2476,19 +2472,19 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>AJP23N</t>
+          <t>TY3012</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2498,18 +2494,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Introduktion till interkulturella litteraturstudier</t>
+          <t>Tyska: Språkvetenskapens historia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2519,14 +2519,14 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>AJP23P</t>
+          <t>AJP23N</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademiskt skrivande</t>
+          <t>Introduktion till interkulturella litteraturstudier</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2562,14 +2562,14 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AJP23Q</t>
+          <t>AJP23P</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Världslitteraturer: Asien och Europa</t>
+          <t>Interkulturella litteraturstudier: Akademiskt skrivande</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2605,14 +2605,14 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AJP23R</t>
+          <t>AJP23Q</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Världslitteraturer: Nord- och Sydamerika</t>
+          <t>Världslitteraturer: Asien och Europa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2648,19 +2648,19 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AFR24Z</t>
+          <t>AJP23R</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2670,18 +2670,18 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2020-03-09</t>
+          <t>2020-01-29</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Franska: Argumentation och retorik</t>
+          <t>Världslitteraturer: Nord- och Sydamerika</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2691,19 +2691,19 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>AFR24Z</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2713,18 +2713,18 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-03-09</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i åk 4-6, 30 hp (1-30 hp). Ingår i Lärarlyftet.</t>
+          <t>Franska: Argumentation och retorik</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2734,19 +2734,19 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>ARY25M</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2756,18 +2756,18 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2020-04-21</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ryska VI: Det virtuella Ryssland: politik, språk och nya medier</t>
+          <t>Svenska som andraspråk för lärare i åk 4-6, 30 hp (1-30 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2777,19 +2777,19 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>ARY25M</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2799,18 +2799,18 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2020-04-27</t>
+          <t>2020-04-21</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska III med didaktisk inriktning</t>
+          <t>Ryska VI: Det virtuella Ryssland: politik, språk och nya medier</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2820,19 +2820,19 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GEN2HB</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2842,18 +2842,18 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-04-27</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Engelska för internationellt företagande: kommunikation och kultur</t>
+          <t>Modersmål: Arabiska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2863,14 +2863,14 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>EN1086</t>
+          <t>GEN2HB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2885,14 +2885,10 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2012-02-16</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>Engelska</t>
@@ -2900,7 +2896,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Engelsk språkstruktur</t>
+          <t>Engelska för internationellt företagande: kommunikation och kultur</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2910,14 +2906,14 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>EN3029</t>
+          <t>EN1086</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2932,7 +2928,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2008-01-11</t>
+          <t>2012-02-16</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2947,7 +2943,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Engelska: Samtida irländsk skönlitteratur</t>
+          <t>Engelsk språkstruktur</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2957,19 +2953,19 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>KI2001</t>
+          <t>EN3029</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2979,7 +2975,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
+          <t>2008-01-11</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2989,12 +2985,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Kinesisk modern litteratur I</t>
+          <t>Engelska: Samtida irländsk skönlitteratur</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3004,19 +3000,19 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AR1004</t>
+          <t>KI2001</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3026,22 +3022,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2008-10-23</t>
+          <t>2011-02-01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2020-07-03</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Arabiska dialekter med inriktning på den Syriska</t>
+          <t>Kinesisk modern litteratur I</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3051,14 +3047,14 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AR1007</t>
+          <t>AR1004</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3073,7 +3069,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2009-04-24</t>
+          <t>2008-10-23</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3088,7 +3084,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Arabiska dialekter med inriktning på den syriska II</t>
+          <t>Arabiska dialekter med inriktning på den Syriska</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3098,14 +3094,14 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AR1009</t>
+          <t>AR1007</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3120,7 +3116,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-04-24</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3135,7 +3131,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Arabiska dialekter: Syriska III</t>
+          <t>Arabiska dialekter med inriktning på den syriska II</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3145,14 +3141,14 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AR1012</t>
+          <t>AR1009</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3167,7 +3163,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2010-09-21</t>
+          <t>2009-12-01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3182,7 +3178,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Arabiska dialekter: Syriska IV</t>
+          <t>Arabiska dialekter: Syriska III</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3192,14 +3188,14 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AR1012</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3214,7 +3210,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2011-11-29</t>
+          <t>2010-09-21</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3229,7 +3225,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Arabiska VIII</t>
+          <t>Arabiska dialekter: Syriska IV</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3239,19 +3235,19 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>KI1031</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3271,12 +3267,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Kinesiska i tal och konversation</t>
+          <t>Arabiska VIII</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3286,19 +3282,19 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GRY2HL</t>
+          <t>KI1031</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3308,18 +3304,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
+          <t>2011-11-29</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Introduktion till rysk opera 1</t>
+          <t>Kinesiska i tal och konversation</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3329,19 +3329,19 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AJP25X</t>
+          <t>GRY2HL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3351,18 +3351,18 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Litteratur och genus - teori och kritik</t>
+          <t>Introduktion till rysk opera 1</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3372,19 +3372,19 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GFR2HZ</t>
+          <t>AJP25X</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3394,18 +3394,18 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Franska: Förberedande kurs IV</t>
+          <t>Interkulturella litteraturstudier: Litteratur och genus - teori och kritik</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3415,19 +3415,19 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3437,18 +3437,18 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-09-04</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Svenska i vardags-, samhälls- och arbetsliv för internationella studenter</t>
+          <t>Franska: Förberedande kurs IV</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3458,14 +3458,14 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+          <t>Svenska i vardags-, samhälls- och arbetsliv för internationella studenter</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3501,19 +3501,19 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GEN2JG</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3523,18 +3523,18 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Engelska, Språkdidaktik I</t>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3544,19 +3544,19 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>GEN2JG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3572,12 +3572,12 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Spanska för lärare åk 7-9, 45 hp (1-45 hp). Ingår i Lärarlyftet.</t>
+          <t>Engelska, Språkdidaktik I</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3587,19 +3587,19 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>AJP264</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3609,18 +3609,18 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Migrationslitteratur i dåtid och nutid</t>
+          <t>Spanska för lärare åk 7-9, 45 hp (1-45 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3630,19 +3630,19 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GFR2KQ</t>
+          <t>AJP264</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3652,18 +3652,18 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Franska III: Språkhistoria</t>
+          <t>Migrationslitteratur i dåtid och nutid</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3673,14 +3673,14 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GFR2KR</t>
+          <t>GFR2KQ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Franska: Examensarbete för kandidatexamen</t>
+          <t>Franska III: Språkhistoria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3716,19 +3716,19 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3738,18 +3738,18 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Spanska III Lingvistisk inriktning: Kandidatexamensarbete</t>
+          <t>Franska: Examensarbete för kandidatexamen</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3759,19 +3759,19 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3781,18 +3781,18 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska I med didaktisk inriktning</t>
+          <t>Spanska III Lingvistisk inriktning: Kandidatexamensarbete</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3802,14 +3802,14 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk II med didaktisk inriktning</t>
+          <t>Modersmål: Arabiska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3845,19 +3845,19 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3867,18 +3867,18 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Kinesiska II med didaktisk inriktning</t>
+          <t>Svenska som andraspråk II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3888,19 +3888,19 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3910,18 +3910,18 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tyska: Språk och nya medier</t>
+          <t>Kinesiska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3931,14 +3931,14 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GTY2N4</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tyskspråkig nutidslitteratur och litteraturkritik</t>
+          <t>Tyska: Språk och nya medier</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3974,19 +3974,19 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GKI2PX</t>
+          <t>GTY2N4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3996,18 +3996,18 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Kinesiska: skriftlig tillämpning</t>
+          <t>Tyskspråkig nutidslitteratur och litteraturkritik</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4017,14 +4017,14 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GKI2PX</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Kinesiska i tal och skrift III</t>
+          <t>Kinesiska: skriftlig tillämpning</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4060,14 +4060,14 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GKI2Q2</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2021-05-04</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Kinesisk språkstruktur</t>
+          <t>Kinesiska i tal och skrift III</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4103,19 +4103,19 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2Q2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>GKI2Q2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4125,18 +4125,18 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-05-04</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Kinesisk språkstruktur</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4146,19 +4146,19 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2Q2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GFR2R3</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4168,18 +4168,18 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Franska II: Muntlig franska</t>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4189,14 +4189,14 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>GFR2R3</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Franska II med didaktisk inriktning</t>
+          <t>Franska II: Muntlig franska</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4232,19 +4232,19 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4260,12 +4260,12 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
+          <t>Franska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4275,19 +4275,19 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GEN2RZ</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4297,18 +4297,18 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
+          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4318,19 +4318,19 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>AJP278</t>
+          <t>GEN2RZ</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4346,12 +4346,12 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Teori och metod</t>
+          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4361,14 +4361,14 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AJP279</t>
+          <t>AJP278</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
+          <t>Interkulturella litteraturstudier: Teori och metod</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4404,14 +4404,14 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>AJP27A</t>
+          <t>AJP279</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
+          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>AJP27B</t>
+          <t>AJP27A</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4490,19 +4490,19 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GAR2SQ</t>
+          <t>AJP27B</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4512,18 +4512,18 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Modern arabisk litteratur</t>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4533,19 +4533,19 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GTY2ST</t>
+          <t>GAR2SQ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4555,18 +4555,18 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tyska: Tysk grammatik med textkommentar</t>
+          <t>Modern arabisk litteratur</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4576,14 +4576,14 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GTY2SV</t>
+          <t>GTY2ST</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
+          <t>Tyska: Tysk grammatik med textkommentar</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4619,19 +4619,19 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GEN2VE</t>
+          <t>GTY2SV</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4641,18 +4641,18 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Engelskspråkig litteratur</t>
+          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4662,19 +4662,19 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GKI2VL</t>
+          <t>GEN2VE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4690,12 +4690,12 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Kinas kultur och samhälle - introduktionskurs</t>
+          <t>Engelskspråkig litteratur</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4705,19 +4705,19 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GKI2VL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4727,18 +4727,18 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Franska: Språkdidaktik I</t>
+          <t>Kinas kultur och samhälle - introduktionskurs</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4748,14 +4748,14 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Franska I med didaktisk inriktning</t>
+          <t>Franska: Språkdidaktik I</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4791,19 +4791,19 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4819,12 +4819,12 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Kinesiska I med didaktisk inriktning</t>
+          <t>Franska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4834,19 +4834,19 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>AJP287</t>
+          <t>GKI2W3</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4856,18 +4856,18 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Japanska: Interkulturell kommunikation</t>
+          <t>Kinesiska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4877,19 +4877,19 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>AJP287</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4899,18 +4899,18 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+          <t>Japanska: Interkulturell kommunikation</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4920,19 +4920,19 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GRY325</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4942,18 +4942,18 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Introduktion till rysk opera 2</t>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4963,19 +4963,19 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GRY325</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4985,18 +4985,18 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tyska: Språkdidaktik II</t>
+          <t>Introduktion till rysk opera 2</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5006,19 +5006,19 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>AKI28Y</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5028,18 +5028,18 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
+          <t>Tyska: Språkdidaktik II</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5049,19 +5049,19 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GFR35F</t>
+          <t>AKI28Y</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5071,18 +5071,18 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
+          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5092,19 +5092,19 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>GFR35F</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5120,12 +5120,12 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
+          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5135,19 +5135,19 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GRY36G</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5157,18 +5157,18 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Introduktion till rysk film</t>
+          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5178,14 +5178,14 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GRY36H</t>
+          <t>GRY36G</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sovjetisk och postsovjetisk science fiction-film</t>
+          <t>Introduktion till rysk film</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5221,14 +5221,14 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GRY37X</t>
+          <t>GRY36H</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
+          <t>Sovjetisk och postsovjetisk science fiction-film</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5264,19 +5264,19 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>AFR29D</t>
+          <t>GRY37X</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5286,22 +5286,18 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
+          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5311,19 +5307,19 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>AJP2A9</t>
+          <t>AFR29D</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5333,18 +5329,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
           <t>2023-12-08</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5354,19 +5354,19 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>ATY29E</t>
+          <t>AJP2A9</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5376,22 +5376,18 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
           <t>2023-12-08</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5401,14 +5397,14 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>TY3013</t>
+          <t>ATY29E</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5423,7 +5419,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5438,7 +5434,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tyska: Modern kvinnolitteratur</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5448,19 +5444,19 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GIT2T6</t>
+          <t>TY3013</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5470,22 +5466,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Italienska nobelpristagare i litteratur</t>
+          <t>Tyska: Modern kvinnolitteratur</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5495,14 +5491,14 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GIT2TD</t>
+          <t>GIT2T6</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5532,7 +5528,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
+          <t>Italienska nobelpristagare i litteratur</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5542,14 +5538,14 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GIT2TG</t>
+          <t>GIT2TD</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5579,7 +5575,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, norra Italien</t>
+          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5589,14 +5585,14 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>GIT2TG</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5626,7 +5622,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
+          <t>Italienska A: Kultur och samhälle, norra Italien</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5636,14 +5632,14 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GIT2TJ</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5673,7 +5669,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
+          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5683,14 +5679,14 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5720,7 +5716,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
+          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5730,14 +5726,14 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GIT2TM</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5767,7 +5763,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
+          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5777,14 +5773,14 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GIT2TN</t>
+          <t>GIT2TM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5814,7 +5810,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, deckargenren</t>
+          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5824,14 +5820,14 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y9</t>
+          <t>GIT2TN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5846,7 +5842,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5861,7 +5857,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, familjeskildringar</t>
+          <t>Italienska A: Textanalys, deckargenren</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5871,14 +5867,14 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GIT2YA</t>
+          <t>GIT2Y9</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5908,7 +5904,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, krig och fred</t>
+          <t>Italienska A: Textanalys, familjeskildringar</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5918,14 +5914,14 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GIT2YB</t>
+          <t>GIT2YA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5955,7 +5951,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
+          <t>Italienska A: Textanalys, krig och fred</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5965,14 +5961,14 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GIT2YC</t>
+          <t>GIT2YB</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -6002,7 +5998,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
+          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6012,14 +6008,14 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GIT2YD</t>
+          <t>GIT2YC</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6049,7 +6045,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, kvinnoskildringar</t>
+          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6059,19 +6055,19 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GSP39N</t>
+          <t>GIT2YD</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6081,18 +6077,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Spanska: Förberedande kurs</t>
+          <t>Italienska A: Textanalys, kvinnoskildringar</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6102,19 +6102,19 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>GSP39N</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -6130,12 +6130,12 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Spanska: Förberedande kurs</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6145,14 +6145,14 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GSS39S</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom grundskolan</t>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6188,14 +6188,14 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GSS39T</t>
+          <t>GSS39S</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
+          <t>Den globala skolan - undervisning inom grundskolan</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6231,14 +6231,14 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GSS39T</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
+          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6274,19 +6274,19 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>AJP2AH</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6296,18 +6296,18 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Klassisk japanska</t>
+          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6317,19 +6317,19 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GEN3BR</t>
+          <t>AJP2AH</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6339,18 +6339,18 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Kulturella texter och kontexter</t>
+          <t>Klassisk japanska</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6360,19 +6360,19 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GKI3C9</t>
+          <t>GEN3BR</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -6382,18 +6382,18 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Kinesiska för affärslivet II</t>
+          <t>Kulturella texter och kontexter</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6403,14 +6403,14 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GKI3CD</t>
+          <t>GKI3C9</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Kinesiska: Kandidatexamensarbete</t>
+          <t>Kinesiska för affärslivet II</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6446,14 +6446,14 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>GKI3CD</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Kinesiska III med didaktisk inriktning</t>
+          <t>Kinesiska: Kandidatexamensarbete</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6489,19 +6489,19 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -6511,18 +6511,18 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tyska: Språk, media och AI</t>
+          <t>Kinesiska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6532,19 +6532,19 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6554,18 +6554,18 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
+          <t>Tyska: Språk, media och AI</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6575,19 +6575,19 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GPR3E5</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6597,18 +6597,18 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Portugisiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
+          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6618,19 +6618,19 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GPR3E5</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6640,18 +6640,18 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Portugisiska</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6661,19 +6661,19 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GFR3HL</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6683,18 +6683,18 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Franska: Språkdidaktik II</t>
+          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6704,19 +6704,19 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GSS3HE</t>
+          <t>GFR3HL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6732,12 +6732,12 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Sociolingvistiska perspektiv på modersmålsundervisning</t>
+          <t>Franska: Språkdidaktik II</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6747,14 +6747,14 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GSS3HF</t>
+          <t>GSS3HE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Flerspråkiga perspektiv på skriftspråksutveckling</t>
+          <t>Sociolingvistiska perspektiv på modersmålsundervisning</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6790,19 +6790,19 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSS3HF</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6812,18 +6812,18 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
+          <t>Flerspråkiga perspektiv på skriftspråksutveckling</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6833,19 +6833,19 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GSS3K2</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6855,18 +6855,18 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
+          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6876,19 +6876,19 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>GSS3K2</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6898,18 +6898,18 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Engelska II</t>
+          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6919,19 +6919,19 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6941,18 +6941,18 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+          <t>Engelska II</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6962,14 +6962,14 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6995,22 +6995,65 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CQ</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Svenska</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
           <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr">
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I149"/>
+  <autoFilter ref="A1:I150"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -7308,6 +7351,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId294"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId298"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$153</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I150"/>
+  <dimension ref="A1:I153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -758,12 +758,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>EN2037</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -773,18 +773,18 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Flerspråkighet, interaktion och identitetsskapande i klassrum</t>
+          <t>Social variation, språkkontakt och språklig makt i engelskan</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -794,14 +794,14 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2037</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Litteracitet och flerspråkighet</t>
+          <t>Flerspråkighet, interaktion och identitetsskapande i klassrum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -837,19 +837,19 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>KI2012</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -859,18 +859,18 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2015-02-05</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kinesiska: Forskningsmetodik</t>
+          <t>Litteracitet och flerspråkighet</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -880,19 +880,19 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>KI2012</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -902,18 +902,18 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2015-02-05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare åk 7-9, 45 hp (1-45). Ingår i Lärarlyftet II</t>
+          <t>Kinesiska: Forskningsmetodik</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -923,19 +923,19 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EN3070</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -945,18 +945,18 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2015-03-12</t>
+          <t>2015-03-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Engelska IV, examensarbete 2 för ämneslärarexamen, åk 7-9</t>
+          <t>Svenska som andraspråk för lärare åk 7-9, 45 hp (1-45). Ingår i Lärarlyftet II</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -966,14 +966,14 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>EN3070</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Engelska IV, inklusive examensarbete 2 för ämneslärarexamen, gy</t>
+          <t>Engelska IV, examensarbete 2 för ämneslärarexamen, åk 7-9</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1009,14 +1009,14 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>EN1129</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2015-10-09</t>
+          <t>2015-03-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Engelska: Skriftlig språkfärdighet</t>
+          <t>Engelska IV, inklusive examensarbete 2 för ämneslärarexamen, gy</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1052,14 +1052,14 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>EN3064</t>
+          <t>EN1129</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1074,14 +1074,10 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2013-12-09</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2015-11-03</t>
-        </is>
-      </c>
+          <t>2015-10-09</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>Engelska</t>
@@ -1089,7 +1085,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Engelska: Avancerad litteraturteori</t>
+          <t>Engelska: Skriftlig språkfärdighet</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1099,19 +1095,19 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>SS3010</t>
+          <t>EN3064</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1121,18 +1117,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2015-12-14</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>2013-12-09</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2015-11-03</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Svensk fonologi i ett andraspråksperspektiv</t>
+          <t>Engelska: Avancerad litteraturteori</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1142,19 +1142,19 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>EN2046</t>
+          <t>SS3010</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1164,18 +1164,18 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2016-02-05</t>
+          <t>2015-12-14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Engelska III, inklusive examensarbete 1 för ämneslärarexamen, gy</t>
+          <t>Svensk fonologi i ett andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1185,14 +1185,14 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>EN2047</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Engelska III, examensarbete 1 för ämneslärarexamen, åk 7-9</t>
+          <t>Engelska III, inklusive examensarbete 1 för ämneslärarexamen, gy</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1228,19 +1228,19 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>EN2047</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1250,22 +1250,18 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2016-04-14</t>
-        </is>
-      </c>
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Portugisiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Portugisiska: Vetenskaplig metod och akademiskt skrivande</t>
+          <t>Engelska III, examensarbete 1 för ämneslärarexamen, åk 7-9</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1275,19 +1271,19 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>JP2013</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1297,18 +1293,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Portugisiska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Japanska: Modern och nutida litteratur</t>
+          <t>Portugisiska: Vetenskaplig metod och akademiskt skrivande</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1318,19 +1318,19 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>EN2025</t>
+          <t>JP2013</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1340,22 +1340,18 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2016-05-26</t>
-        </is>
-      </c>
+          <t>2016-04-15</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Litteratur och teori</t>
+          <t>Japanska: Modern och nutida litteratur</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1365,19 +1361,19 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SS3014</t>
+          <t>EN2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1387,18 +1383,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2016-11-18</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2016-05-26</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Flerspråkighet i ett samhällsperspektiv</t>
+          <t>Litteratur och teori</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1408,19 +1408,19 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>AR1025</t>
+          <t>SS3014</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1430,22 +1430,18 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2013-06-14</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2017-10-03</t>
-        </is>
-      </c>
+          <t>2016-11-18</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arabiska VI - muntlig kommunikation</t>
+          <t>Flerspråkighet i ett samhällsperspektiv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1455,14 +1451,14 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AR2006</t>
+          <t>AR1025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1477,7 +1473,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2015-06-15</t>
+          <t>2013-06-14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1492,7 +1488,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Arabiska: Avancerad grammatik II</t>
+          <t>Arabiska VI - muntlig kommunikation</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1502,14 +1498,14 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AR2007</t>
+          <t>AR2006</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1539,7 +1535,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Det egna jaget och den andre – gestaltning i arabisk litteratur</t>
+          <t>Arabiska: Avancerad grammatik II</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1549,14 +1545,14 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2006</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AR2009</t>
+          <t>AR2007</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1571,7 +1567,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2015-09-15</t>
+          <t>2015-06-15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1586,7 +1582,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Modern arabisk litteratur och sökandet efter frihet</t>
+          <t>Det egna jaget och den andre – gestaltning i arabisk litteratur</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1596,14 +1592,14 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2007</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AR2010</t>
+          <t>AR2009</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1633,7 +1629,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Arabiska: Avancerad grammatik</t>
+          <t>Modern arabisk litteratur och sökandet efter frihet</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1643,14 +1639,14 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AR2011</t>
+          <t>AR2010</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1665,7 +1661,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2015-09-15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1680,7 +1676,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Den arabiska akademiska kanon</t>
+          <t>Arabiska: Avancerad grammatik</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1690,19 +1686,19 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>AR2011</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1712,18 +1708,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>2015-09-18</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Kinesiska: grundläggande språkfärdighet</t>
+          <t>Den arabiska akademiska kanon</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1733,19 +1733,19 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GEN222</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1755,18 +1755,18 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2018-03-22</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Engelska för lärare, 45 hp (1-45 hp), åk 7-9 - ingår i Lärarlyftet II</t>
+          <t>Kinesiska: grundläggande språkfärdighet</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1776,19 +1776,19 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GSS22M</t>
+          <t>GEN222</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1798,18 +1798,18 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2018-04-19</t>
+          <t>2018-03-22</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Studiehandledning på modersmål</t>
+          <t>Engelska för lärare, 45 hp (1-45 hp), åk 7-9 - ingår i Lärarlyftet II</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1819,14 +1819,14 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GSS22P</t>
+          <t>GSS22M</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Den globala skolan - förskola och grundskola</t>
+          <t>Studiehandledning på modersmål</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1862,19 +1862,19 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GTY23C</t>
+          <t>GSS22P</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1884,18 +1884,18 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2018-04-19</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tyskspråkig barn- och ungdomslitteratur</t>
+          <t>Den globala skolan - förskola och grundskola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1905,19 +1905,19 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GJP243</t>
+          <t>GTY23C</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1927,18 +1927,18 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2018-06-05</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Japanska IV: Språkfärdighet</t>
+          <t>Tyskspråkig barn- och ungdomslitteratur</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1948,19 +1948,19 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GFR27N</t>
+          <t>GJP243</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1970,18 +1970,18 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Franska: Skriftlig språkfärdighet II</t>
+          <t>Japanska IV: Språkfärdighet</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1991,14 +1991,14 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GFR27Q</t>
+          <t>GFR27N</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Franska II: Introduktion till lingvistik och akademiskt skrivande</t>
+          <t>Franska: Skriftlig språkfärdighet II</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2034,14 +2034,14 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GFR27R</t>
+          <t>GFR27Q</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Franskspråkig litteratur II: Fram till 1900</t>
+          <t>Franska II: Introduktion till lingvistik och akademiskt skrivande</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2077,19 +2077,19 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GKI27M</t>
+          <t>GFR27R</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2099,18 +2099,18 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2019-03-08</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Kinesiska V: Fördjupningskurs i modern kinesiska</t>
+          <t>Franskspråkig litteratur II: Fram till 1900</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2120,19 +2120,19 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GFR27S</t>
+          <t>GKI27M</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2142,18 +2142,18 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2019-03-11</t>
+          <t>2019-03-08</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Franska med inriktning arbetsliv</t>
+          <t>Kinesiska V: Fördjupningskurs i modern kinesiska</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2163,14 +2163,14 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GFR283</t>
+          <t>GFR27S</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2019-03-12</t>
+          <t>2019-03-11</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Litteratur och kultur i Maghrebregionen</t>
+          <t>Franska med inriktning arbetsliv</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2206,19 +2206,19 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GSV2BN</t>
+          <t>GFR283</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2228,18 +2228,18 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
+          <t>2019-03-12</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Svenska: Text och tal</t>
+          <t>Litteratur och kultur i Maghrebregionen</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2249,14 +2249,14 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GSV2BP</t>
+          <t>GSV2BN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Svenska: Barn- och ungdomslitteratur i samhällsdialog</t>
+          <t>Svenska: Text och tal</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2292,19 +2292,19 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ARY23F</t>
+          <t>GSV2BP</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2314,18 +2314,18 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ryska VI: Stalintidens ideologi och estetik</t>
+          <t>Svenska: Barn- och ungdomslitteratur i samhällsdialog</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2335,14 +2335,14 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GRY2BR</t>
+          <t>ARY23F</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ryska V: Samtida rysk litteratur och kultur</t>
+          <t>Ryska VI: Stalintidens ideologi och estetik</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2378,19 +2378,19 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>AR1003</t>
+          <t>GRY2BR</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2400,22 +2400,18 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2008-10-23</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2019-10-09</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Den moderna arabiska novellen</t>
+          <t>Ryska V: Samtida rysk litteratur och kultur</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2425,14 +2421,14 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>AR1018</t>
+          <t>AR1003</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2447,7 +2443,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2012-04-19</t>
+          <t>2008-10-23</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2462,7 +2458,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Arabiska för nybörjare I</t>
+          <t>Den moderna arabiska novellen</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2472,19 +2468,19 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TY3012</t>
+          <t>AR1018</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2494,7 +2490,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2012-04-19</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2504,12 +2500,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tyska: Språkvetenskapens historia</t>
+          <t>Arabiska för nybörjare I</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2519,19 +2515,19 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>AJP23N</t>
+          <t>TY3012</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2541,18 +2537,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Introduktion till interkulturella litteraturstudier</t>
+          <t>Tyska: Språkvetenskapens historia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2562,14 +2562,14 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AJP23P</t>
+          <t>AJP23N</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademiskt skrivande</t>
+          <t>Introduktion till interkulturella litteraturstudier</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2605,14 +2605,14 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AJP23Q</t>
+          <t>AJP23P</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Världslitteraturer: Asien och Europa</t>
+          <t>Interkulturella litteraturstudier: Akademiskt skrivande</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2648,14 +2648,14 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AJP23R</t>
+          <t>AJP23Q</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Världslitteraturer: Nord- och Sydamerika</t>
+          <t>Världslitteraturer: Asien och Europa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2691,19 +2691,19 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AFR24Z</t>
+          <t>AJP23R</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2713,18 +2713,18 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2020-03-09</t>
+          <t>2020-01-29</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Franska: Argumentation och retorik</t>
+          <t>Världslitteraturer: Nord- och Sydamerika</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2734,19 +2734,19 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>AFR24Z</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2756,18 +2756,18 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-03-09</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i åk 4-6, 30 hp (1-30 hp). Ingår i Lärarlyftet.</t>
+          <t>Franska: Argumentation och retorik</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2777,19 +2777,19 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ARY25M</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2799,18 +2799,18 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2020-04-21</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ryska VI: Det virtuella Ryssland: politik, språk och nya medier</t>
+          <t>Svenska som andraspråk för lärare i åk 4-6, 30 hp (1-30 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2820,19 +2820,19 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>ARY25M</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2842,18 +2842,18 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2020-04-27</t>
+          <t>2020-04-21</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska III med didaktisk inriktning</t>
+          <t>Ryska VI: Det virtuella Ryssland: politik, språk och nya medier</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2863,19 +2863,19 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GEN2HB</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2885,18 +2885,18 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-04-27</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Engelska för internationellt företagande: kommunikation och kultur</t>
+          <t>Modersmål: Arabiska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2906,14 +2906,14 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>EN1086</t>
+          <t>GEN2HB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2928,14 +2928,10 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2012-02-16</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>Engelska</t>
@@ -2943,7 +2939,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Engelsk språkstruktur</t>
+          <t>Engelska för internationellt företagande: kommunikation och kultur</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2953,14 +2949,14 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>EN3029</t>
+          <t>EN1086</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2975,7 +2971,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2008-01-11</t>
+          <t>2012-02-16</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2990,7 +2986,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Engelska: Samtida irländsk skönlitteratur</t>
+          <t>Engelsk språkstruktur</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3000,19 +2996,19 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>KI2001</t>
+          <t>EN3029</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3022,7 +3018,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
+          <t>2008-01-11</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3032,12 +3028,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Kinesisk modern litteratur I</t>
+          <t>Engelska: Samtida irländsk skönlitteratur</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3047,19 +3043,19 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AR1004</t>
+          <t>KI2001</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3069,22 +3065,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2008-10-23</t>
+          <t>2011-02-01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2020-07-03</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Arabiska dialekter med inriktning på den Syriska</t>
+          <t>Kinesisk modern litteratur I</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3094,14 +3090,14 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AR1007</t>
+          <t>AR1004</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3116,7 +3112,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2009-04-24</t>
+          <t>2008-10-23</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3131,7 +3127,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Arabiska dialekter med inriktning på den syriska II</t>
+          <t>Arabiska dialekter med inriktning på den Syriska</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3141,14 +3137,14 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AR1009</t>
+          <t>AR1007</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3163,7 +3159,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-04-24</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3178,7 +3174,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Arabiska dialekter: Syriska III</t>
+          <t>Arabiska dialekter med inriktning på den syriska II</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3188,14 +3184,14 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AR1012</t>
+          <t>AR1009</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3210,7 +3206,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2010-09-21</t>
+          <t>2009-12-01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3225,7 +3221,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Arabiska dialekter: Syriska IV</t>
+          <t>Arabiska dialekter: Syriska III</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3235,14 +3231,14 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AR1012</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3257,7 +3253,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2011-11-29</t>
+          <t>2010-09-21</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3272,7 +3268,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Arabiska VIII</t>
+          <t>Arabiska dialekter: Syriska IV</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3282,19 +3278,19 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>KI1031</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3314,12 +3310,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Kinesiska i tal och konversation</t>
+          <t>Arabiska VIII</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3329,19 +3325,19 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GRY2HL</t>
+          <t>KI1031</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3351,18 +3347,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
+          <t>2011-11-29</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Introduktion till rysk opera 1</t>
+          <t>Kinesiska i tal och konversation</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3372,19 +3372,19 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>AJP25X</t>
+          <t>GRY2HL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3394,18 +3394,18 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Litteratur och genus - teori och kritik</t>
+          <t>Introduktion till rysk opera 1</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3415,19 +3415,19 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GFR2HZ</t>
+          <t>AJP25X</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3437,18 +3437,18 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Franska: Förberedande kurs IV</t>
+          <t>Interkulturella litteraturstudier: Litteratur och genus - teori och kritik</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3458,19 +3458,19 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3480,18 +3480,18 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-09-04</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Svenska i vardags-, samhälls- och arbetsliv för internationella studenter</t>
+          <t>Franska: Förberedande kurs IV</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3501,14 +3501,14 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+          <t>Svenska i vardags-, samhälls- och arbetsliv för internationella studenter</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3544,19 +3544,19 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GEN2JG</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3566,18 +3566,18 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Engelska, Språkdidaktik I</t>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3587,19 +3587,19 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>GEN2JG</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3615,12 +3615,12 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Spanska för lärare åk 7-9, 45 hp (1-45 hp). Ingår i Lärarlyftet.</t>
+          <t>Engelska, Språkdidaktik I</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3630,19 +3630,19 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>AJP264</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3652,18 +3652,18 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Migrationslitteratur i dåtid och nutid</t>
+          <t>Spanska för lärare åk 7-9, 45 hp (1-45 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3673,19 +3673,19 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GFR2KQ</t>
+          <t>AJP264</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3695,18 +3695,18 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Franska III: Språkhistoria</t>
+          <t>Migrationslitteratur i dåtid och nutid</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GFR2KR</t>
+          <t>GFR2KQ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Franska: Examensarbete för kandidatexamen</t>
+          <t>Franska III: Språkhistoria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3759,19 +3759,19 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3781,18 +3781,18 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Spanska III Lingvistisk inriktning: Kandidatexamensarbete</t>
+          <t>Franska: Examensarbete för kandidatexamen</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3802,19 +3802,19 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3824,18 +3824,18 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska I med didaktisk inriktning</t>
+          <t>Spanska III Lingvistisk inriktning: Kandidatexamensarbete</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3845,14 +3845,14 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk II med didaktisk inriktning</t>
+          <t>Modersmål: Arabiska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3888,19 +3888,19 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3910,18 +3910,18 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Kinesiska II med didaktisk inriktning</t>
+          <t>Svenska som andraspråk II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3931,19 +3931,19 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3953,18 +3953,18 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tyska: Språk och nya medier</t>
+          <t>Kinesiska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3974,14 +3974,14 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GTY2N4</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tyskspråkig nutidslitteratur och litteraturkritik</t>
+          <t>Tyska: Språk och nya medier</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4017,19 +4017,19 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GKI2PX</t>
+          <t>GTY2N4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4039,18 +4039,18 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Kinesiska: skriftlig tillämpning</t>
+          <t>Tyskspråkig nutidslitteratur och litteraturkritik</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4060,14 +4060,14 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GKI2PX</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Kinesiska i tal och skrift III</t>
+          <t>Kinesiska: skriftlig tillämpning</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4103,14 +4103,14 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GKI2Q2</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2021-05-04</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Kinesisk språkstruktur</t>
+          <t>Kinesiska i tal och skrift III</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4146,19 +4146,19 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2Q2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>GKI2Q2</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4168,18 +4168,18 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-05-04</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Kinesisk språkstruktur</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4189,19 +4189,19 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2Q2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GFR2R3</t>
+          <t>GEN2QW</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4211,18 +4211,18 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Franska II: Muntlig franska</t>
+          <t>Engelska, Språkdidaktik l</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4232,19 +4232,19 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4254,18 +4254,18 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Franska II med didaktisk inriktning</t>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4275,19 +4275,19 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>GFR2R3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4303,12 +4303,12 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
+          <t>Franska II: Muntlig franska</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4318,19 +4318,19 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GEN2RZ</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4340,18 +4340,18 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
+          <t>Franska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4361,14 +4361,14 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AJP278</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Teori och metod</t>
+          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4404,19 +4404,19 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>AJP279</t>
+          <t>GEN2RZ</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4432,12 +4432,12 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
+          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>AJP27A</t>
+          <t>AJP278</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
+          <t>Interkulturella litteraturstudier: Teori och metod</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4490,14 +4490,14 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>AJP27B</t>
+          <t>AJP279</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4533,19 +4533,19 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GAR2SQ</t>
+          <t>AJP27A</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4555,18 +4555,18 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Modern arabisk litteratur</t>
+          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4576,19 +4576,19 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GTY2ST</t>
+          <t>AJP27B</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4598,18 +4598,18 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tyska: Tysk grammatik med textkommentar</t>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4619,19 +4619,19 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GTY2SV</t>
+          <t>GAR2SQ</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4641,18 +4641,18 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
+          <t>Modern arabisk litteratur</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4662,19 +4662,19 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GEN2VE</t>
+          <t>GTY2ST</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4684,18 +4684,18 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Engelskspråkig litteratur</t>
+          <t>Tyska: Tysk grammatik med textkommentar</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4705,19 +4705,19 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GKI2VL</t>
+          <t>GTY2SV</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4727,18 +4727,18 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Kinas kultur och samhälle - introduktionskurs</t>
+          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4748,19 +4748,19 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GEN2VE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4770,18 +4770,18 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Franska: Språkdidaktik I</t>
+          <t>Engelskspråkig litteratur</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4791,19 +4791,19 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>GKI2VL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4813,18 +4813,18 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Franska I med didaktisk inriktning</t>
+          <t>Kinas kultur och samhälle - introduktionskurs</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4834,19 +4834,19 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4862,12 +4862,12 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Kinesiska I med didaktisk inriktning</t>
+          <t>Franska: Språkdidaktik I</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4877,19 +4877,19 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>AJP287</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4899,18 +4899,18 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Japanska: Interkulturell kommunikation</t>
+          <t>Franska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4920,19 +4920,19 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>GKI2W3</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4942,18 +4942,18 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+          <t>Kinesiska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4963,19 +4963,19 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GRY325</t>
+          <t>AJP287</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4985,18 +4985,18 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Introduktion till rysk opera 2</t>
+          <t>Japanska: Interkulturell kommunikation</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5006,19 +5006,19 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5028,18 +5028,18 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tyska: Språkdidaktik II</t>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5049,19 +5049,19 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>AKI28Y</t>
+          <t>GRY325</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5071,18 +5071,18 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
+          <t>Introduktion till rysk opera 2</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5092,19 +5092,19 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GFR35F</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5114,18 +5114,18 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
+          <t>Tyska: Språkdidaktik II</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5135,19 +5135,19 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>AKI28Y</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5157,18 +5157,18 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
+          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5178,19 +5178,19 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GRY36G</t>
+          <t>GFR35F</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5200,18 +5200,18 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Introduktion till rysk film</t>
+          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5221,19 +5221,19 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GRY36H</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5243,18 +5243,18 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sovjetisk och postsovjetisk science fiction-film</t>
+          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5264,14 +5264,14 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GRY37X</t>
+          <t>GRY36G</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
+          <t>Introduktion till rysk film</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5307,19 +5307,19 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>AFR29D</t>
+          <t>GRY36H</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5329,22 +5329,18 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
+          <t>Sovjetisk och postsovjetisk science fiction-film</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5354,19 +5350,19 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>AJP2A9</t>
+          <t>GRY37X</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5376,18 +5372,18 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
+          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5397,19 +5393,19 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>ATY29E</t>
+          <t>AFR29D</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5429,12 +5425,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5444,19 +5440,19 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>TY3013</t>
+          <t>AJP2A9</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5466,22 +5462,18 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
           <t>2023-12-08</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tyska: Modern kvinnolitteratur</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5491,19 +5483,19 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GIT2T6</t>
+          <t>ATY29E</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -5513,22 +5505,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Italienska nobelpristagare i litteratur</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5538,19 +5530,19 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GIT2TD</t>
+          <t>TY3013</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5560,22 +5552,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
+          <t>Tyska: Modern kvinnolitteratur</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5585,14 +5577,14 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GIT2TG</t>
+          <t>GIT2T6</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5622,7 +5614,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, norra Italien</t>
+          <t>Italienska nobelpristagare i litteratur</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5632,14 +5624,14 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>GIT2TD</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5669,7 +5661,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
+          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5679,14 +5671,14 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GIT2TJ</t>
+          <t>GIT2TG</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5716,7 +5708,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
+          <t>Italienska A: Kultur och samhälle, norra Italien</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5726,14 +5718,14 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5763,7 +5755,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
+          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5773,14 +5765,14 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GIT2TM</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5810,7 +5802,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
+          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5820,14 +5812,14 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GIT2TN</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5857,7 +5849,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, deckargenren</t>
+          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5867,14 +5859,14 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y9</t>
+          <t>GIT2TM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5889,7 +5881,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5904,7 +5896,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, familjeskildringar</t>
+          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5914,14 +5906,14 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GIT2YA</t>
+          <t>GIT2TN</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5936,7 +5928,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5951,7 +5943,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, krig och fred</t>
+          <t>Italienska A: Textanalys, deckargenren</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5961,14 +5953,14 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GIT2YB</t>
+          <t>GIT2Y9</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5998,7 +5990,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
+          <t>Italienska A: Textanalys, familjeskildringar</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6008,14 +6000,14 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GIT2YC</t>
+          <t>GIT2YA</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6045,7 +6037,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
+          <t>Italienska A: Textanalys, krig och fred</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6055,14 +6047,14 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GIT2YD</t>
+          <t>GIT2YB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6092,7 +6084,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, kvinnoskildringar</t>
+          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6102,19 +6094,19 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GSP39N</t>
+          <t>GIT2YC</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -6124,18 +6116,22 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Spanska: Förberedande kurs</t>
+          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6145,19 +6141,19 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>GIT2YD</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6167,18 +6163,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Italienska A: Textanalys, kvinnoskildringar</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6188,19 +6188,19 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GSS39S</t>
+          <t>GSP39N</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6216,12 +6216,12 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom grundskolan</t>
+          <t>Spanska: Förberedande kurs</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6231,14 +6231,14 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GSS39T</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6274,14 +6274,14 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GSS39S</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
+          <t>Den globala skolan - undervisning inom grundskolan</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6317,19 +6317,19 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>AJP2AH</t>
+          <t>GSS39T</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6339,18 +6339,18 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Klassisk japanska</t>
+          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6360,19 +6360,19 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GEN3BR</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -6382,18 +6382,18 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Kulturella texter och kontexter</t>
+          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6403,19 +6403,19 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GKI3C9</t>
+          <t>AJP2AH</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -6425,18 +6425,18 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Kinesiska för affärslivet II</t>
+          <t>Klassisk japanska</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6446,19 +6446,19 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GKI3CD</t>
+          <t>GEN3BR</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -6468,18 +6468,18 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Kinesiska: Kandidatexamensarbete</t>
+          <t>Kulturella texter och kontexter</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6489,14 +6489,14 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>GKI3C9</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Kinesiska III med didaktisk inriktning</t>
+          <t>Kinesiska för affärslivet II</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6532,19 +6532,19 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GKI3CD</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6554,18 +6554,18 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tyska: Språk, media och AI</t>
+          <t>Kinesiska: Kandidatexamensarbete</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6575,19 +6575,19 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6597,18 +6597,18 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
+          <t>Kinesiska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6618,19 +6618,19 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GPR3E5</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6640,18 +6640,18 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Portugisiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
+          <t>Tyska: Språk, media och AI</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6661,19 +6661,19 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6683,18 +6683,18 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6704,19 +6704,19 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GFR3HL</t>
+          <t>GPR3E5</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6726,18 +6726,18 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Portugisiska</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Franska: Språkdidaktik II</t>
+          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6747,19 +6747,19 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GSS3HE</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6769,18 +6769,18 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Sociolingvistiska perspektiv på modersmålsundervisning</t>
+          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6790,19 +6790,19 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GSS3HF</t>
+          <t>AEN2BR</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6812,18 +6812,18 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Flerspråkiga perspektiv på skriftspråksutveckling</t>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6833,19 +6833,19 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GFR3HL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6855,18 +6855,18 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
+          <t>Franska: Språkdidaktik II</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6876,14 +6876,14 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GSS3K2</t>
+          <t>GSS3HE</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
+          <t>Sociolingvistiska perspektiv på modersmålsundervisning</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6919,19 +6919,19 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>GSS3HF</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6941,18 +6941,18 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Engelska II</t>
+          <t>Flerspråkiga perspektiv på skriftspråksutveckling</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6962,14 +6962,14 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7005,19 +7005,19 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>GSS3K2</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7027,33 +7027,162 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>GEN3K3</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Engelska II</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CP</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
           <t>Svenska</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CQ</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Svenska</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
         <is>
           <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr">
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I150"/>
+  <autoFilter ref="A1:I153"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -7353,6 +7482,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId296"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId304"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I153"/>
+  <dimension ref="A1:I152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6840,12 +6840,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GFR3HL</t>
+          <t>GSS3HE</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6861,12 +6861,12 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Franska: Språkdidaktik II</t>
+          <t>Sociolingvistiska perspektiv på modersmålsundervisning</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6876,14 +6876,14 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GSS3HE</t>
+          <t>GSS3HF</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Sociolingvistiska perspektiv på modersmålsundervisning</t>
+          <t>Flerspråkiga perspektiv på skriftspråksutveckling</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6919,19 +6919,19 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GSS3HF</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6941,18 +6941,18 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Flerspråkiga perspektiv på skriftspråksutveckling</t>
+          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6962,19 +6962,19 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSS3K2</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -6984,18 +6984,18 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
+          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7005,19 +7005,19 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GSS3K2</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7027,18 +7027,18 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
+          <t>Engelska II</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7048,19 +7048,19 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7070,18 +7070,18 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Engelska II</t>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7091,14 +7091,14 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7134,55 +7134,12 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>ASV2CQ</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Svenska</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I153"/>
+  <autoFilter ref="A1:I152"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -7486,8 +7443,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId300"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId304"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$155</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I152"/>
+  <dimension ref="A1:I155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4196,12 +4196,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GEN2QW</t>
+          <t>GKI2Q9</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4211,18 +4211,18 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Engelska, Språkdidaktik l</t>
+          <t>Kinesiska: Det kinesiska samhället</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4232,19 +4232,19 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2Q9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>GEN2QW</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4260,12 +4260,12 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Engelska, Språkdidaktik l</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4275,19 +4275,19 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GFR2R3</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4297,18 +4297,18 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Franska II: Muntlig franska</t>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4318,14 +4318,14 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>GFR2R3</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Franska II med didaktisk inriktning</t>
+          <t>Franska II: Muntlig franska</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4361,19 +4361,19 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4389,12 +4389,12 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
+          <t>Franska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4404,19 +4404,19 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GEN2RZ</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4426,18 +4426,18 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
+          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4447,19 +4447,19 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>AJP278</t>
+          <t>GEN2RZ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4475,12 +4475,12 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Teori och metod</t>
+          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4490,14 +4490,14 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>AJP279</t>
+          <t>AJP278</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
+          <t>Interkulturella litteraturstudier: Teori och metod</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4533,14 +4533,14 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>AJP27A</t>
+          <t>AJP279</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
+          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4576,14 +4576,14 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>AJP27B</t>
+          <t>AJP27A</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4619,19 +4619,19 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GAR2SQ</t>
+          <t>AJP27B</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4641,18 +4641,18 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Modern arabisk litteratur</t>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4662,19 +4662,19 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GTY2ST</t>
+          <t>GAR2SQ</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4684,18 +4684,18 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tyska: Tysk grammatik med textkommentar</t>
+          <t>Modern arabisk litteratur</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4705,14 +4705,14 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GTY2SV</t>
+          <t>GTY2ST</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
+          <t>Tyska: Tysk grammatik med textkommentar</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4748,19 +4748,19 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GEN2VE</t>
+          <t>GTY2SV</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4770,18 +4770,18 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Engelskspråkig litteratur</t>
+          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4791,19 +4791,19 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GKI2VL</t>
+          <t>GEN2VE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4819,12 +4819,12 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Kinas kultur och samhälle - introduktionskurs</t>
+          <t>Engelskspråkig litteratur</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4834,19 +4834,19 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GKI2VL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4856,18 +4856,18 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Franska: Språkdidaktik I</t>
+          <t>Kinas kultur och samhälle - introduktionskurs</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4877,14 +4877,14 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Franska I med didaktisk inriktning</t>
+          <t>Franska: Språkdidaktik I</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4920,19 +4920,19 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4948,12 +4948,12 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Kinesiska I med didaktisk inriktning</t>
+          <t>Franska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4963,19 +4963,19 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>AJP287</t>
+          <t>GKI2W3</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4985,18 +4985,18 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Japanska: Interkulturell kommunikation</t>
+          <t>Kinesiska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5006,19 +5006,19 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>AJP287</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5028,18 +5028,18 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+          <t>Japanska: Interkulturell kommunikation</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5049,19 +5049,19 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GRY325</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5071,18 +5071,18 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Introduktion till rysk opera 2</t>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5092,19 +5092,19 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GRY325</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5114,18 +5114,18 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tyska: Språkdidaktik II</t>
+          <t>Introduktion till rysk opera 2</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5135,19 +5135,19 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>AKI28Y</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5157,18 +5157,18 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
+          <t>Tyska: Språkdidaktik II</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5178,19 +5178,19 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GFR35F</t>
+          <t>AKI28Y</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5200,18 +5200,18 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
+          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5221,19 +5221,19 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>GFR35F</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5249,12 +5249,12 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
+          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5264,19 +5264,19 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GRY36G</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5286,18 +5286,18 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Introduktion till rysk film</t>
+          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5307,14 +5307,14 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GRY36H</t>
+          <t>GRY36G</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sovjetisk och postsovjetisk science fiction-film</t>
+          <t>Introduktion till rysk film</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5350,14 +5350,14 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GRY37X</t>
+          <t>GRY36H</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
+          <t>Sovjetisk och postsovjetisk science fiction-film</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5393,19 +5393,19 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>AFR29D</t>
+          <t>GRY37X</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5415,22 +5415,18 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
+          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5440,19 +5436,19 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>AJP2A9</t>
+          <t>AFR29D</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5462,18 +5458,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>2023-12-08</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5483,19 +5483,19 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>ATY29E</t>
+          <t>AJP2A9</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -5505,22 +5505,18 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
           <t>2023-12-08</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5530,14 +5526,14 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>TY3013</t>
+          <t>ATY29E</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5552,7 +5548,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5567,7 +5563,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tyska: Modern kvinnolitteratur</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5577,19 +5573,19 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GIT2T6</t>
+          <t>TY3013</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5599,22 +5595,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Italienska nobelpristagare i litteratur</t>
+          <t>Tyska: Modern kvinnolitteratur</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5624,14 +5620,14 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GIT2TD</t>
+          <t>GIT2T6</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5661,7 +5657,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
+          <t>Italienska nobelpristagare i litteratur</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5671,14 +5667,14 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GIT2TG</t>
+          <t>GIT2TD</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5708,7 +5704,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, norra Italien</t>
+          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5718,14 +5714,14 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>GIT2TG</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5755,7 +5751,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
+          <t>Italienska A: Kultur och samhälle, norra Italien</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5765,14 +5761,14 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GIT2TJ</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5802,7 +5798,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
+          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5812,14 +5808,14 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5849,7 +5845,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
+          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5859,14 +5855,14 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GIT2TM</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5896,7 +5892,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
+          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5906,14 +5902,14 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GIT2TN</t>
+          <t>GIT2TM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5943,7 +5939,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, deckargenren</t>
+          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5953,14 +5949,14 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y9</t>
+          <t>GIT2TN</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5975,7 +5971,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5990,7 +5986,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, familjeskildringar</t>
+          <t>Italienska A: Textanalys, deckargenren</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6000,14 +5996,14 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GIT2YA</t>
+          <t>GIT2Y9</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6037,7 +6033,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, krig och fred</t>
+          <t>Italienska A: Textanalys, familjeskildringar</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6047,14 +6043,14 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GIT2YB</t>
+          <t>GIT2YA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6084,7 +6080,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
+          <t>Italienska A: Textanalys, krig och fred</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6094,14 +6090,14 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GIT2YC</t>
+          <t>GIT2YB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6131,7 +6127,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
+          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6141,14 +6137,14 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GIT2YD</t>
+          <t>GIT2YC</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6178,7 +6174,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, kvinnoskildringar</t>
+          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6188,19 +6184,19 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GSP39N</t>
+          <t>GIT2YD</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6210,18 +6206,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Spanska: Förberedande kurs</t>
+          <t>Italienska A: Textanalys, kvinnoskildringar</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6231,19 +6231,19 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>GSP39N</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -6259,12 +6259,12 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Spanska: Förberedande kurs</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6274,14 +6274,14 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GSS39S</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom grundskolan</t>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6317,14 +6317,14 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GSS39T</t>
+          <t>GSS39S</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
+          <t>Den globala skolan - undervisning inom grundskolan</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6360,14 +6360,14 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GSS39T</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
+          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6403,19 +6403,19 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>AJP2AH</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -6425,18 +6425,18 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Klassisk japanska</t>
+          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6446,19 +6446,19 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GEN3BR</t>
+          <t>AJP2AH</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -6468,18 +6468,18 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Kulturella texter och kontexter</t>
+          <t>Klassisk japanska</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6489,19 +6489,19 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GKI3C9</t>
+          <t>GEN3BR</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -6511,18 +6511,18 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Kinesiska för affärslivet II</t>
+          <t>Kulturella texter och kontexter</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6532,14 +6532,14 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GKI3CD</t>
+          <t>GKI3C9</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Kinesiska: Kandidatexamensarbete</t>
+          <t>Kinesiska för affärslivet II</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6575,14 +6575,14 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>GKI3CD</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Kinesiska III med didaktisk inriktning</t>
+          <t>Kinesiska: Kandidatexamensarbete</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6618,19 +6618,19 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6640,18 +6640,18 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tyska: Språk, media och AI</t>
+          <t>Kinesiska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6661,19 +6661,19 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GSS3C6</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6683,18 +6683,18 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
+          <t>Lärande genom fiktionstext i gymnasieskolan</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6704,19 +6704,19 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GPR3E5</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6726,18 +6726,18 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Portugisiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
+          <t>Tyska: Språk, media och AI</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6747,19 +6747,19 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6769,18 +6769,18 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6790,19 +6790,19 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>AEN2BR</t>
+          <t>GPR3E5</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6812,18 +6812,18 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Portugisiska</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6833,19 +6833,19 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GSS3HE</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6855,18 +6855,18 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sociolingvistiska perspektiv på modersmålsundervisning</t>
+          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6876,19 +6876,19 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GSS3HF</t>
+          <t>AEN2BR</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6898,18 +6898,18 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Flerspråkiga perspektiv på skriftspråksutveckling</t>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6919,19 +6919,19 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSS3HC</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6941,18 +6941,18 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
+          <t>Introduktion till modersmålsundervisning och studiehandledning på modersmålet</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6962,14 +6962,14 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HC</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GSS3K2</t>
+          <t>GSS3HE</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
+          <t>Sociolingvistiska perspektiv på modersmålsundervisning</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7005,19 +7005,19 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>GSS3HF</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7027,18 +7027,18 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Engelska II</t>
+          <t>Flerspråkiga perspektiv på skriftspråksutveckling</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7048,14 +7048,14 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7091,19 +7091,19 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>GSS3K2</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7113,33 +7113,162 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>GEN3K3</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Engelska II</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CP</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
           <t>Svenska</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CQ</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Svenska</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
         <is>
           <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr">
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I152"/>
+  <autoFilter ref="A1:I155"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -7443,6 +7572,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId300"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId308"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$148</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I155"/>
+  <dimension ref="A1:I148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3938,12 +3938,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3953,18 +3953,18 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Kinesiska II med didaktisk inriktning</t>
+          <t>Tyska: Språk och nya medier</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3974,14 +3974,14 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>GTY2N4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tyska: Språk och nya medier</t>
+          <t>Tyskspråkig nutidslitteratur och litteraturkritik</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4017,19 +4017,19 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GTY2N4</t>
+          <t>GKI2PX</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4039,18 +4039,18 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tyskspråkig nutidslitteratur och litteraturkritik</t>
+          <t>Kinesiska: skriftlig tillämpning</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4060,14 +4060,14 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GKI2PX</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Kinesiska: skriftlig tillämpning</t>
+          <t>Kinesiska i tal och skrift III</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4103,19 +4103,19 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GEN2QW</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4125,18 +4125,18 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Kinesiska i tal och skrift III</t>
+          <t>Engelska, Språkdidaktik l</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4146,19 +4146,19 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GKI2Q2</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4168,18 +4168,18 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2021-05-04</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Kinesisk språkstruktur</t>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4189,19 +4189,19 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2Q2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GKI2Q9</t>
+          <t>GFR2R3</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4211,18 +4211,18 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Kinesiska: Det kinesiska samhället</t>
+          <t>Franska II: Muntlig franska</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4232,19 +4232,19 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2Q9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GEN2QW</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4254,18 +4254,18 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Engelska, Språkdidaktik l</t>
+          <t>Franska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4275,19 +4275,19 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4297,18 +4297,18 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4318,19 +4318,19 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GFR2R3</t>
+          <t>GEN2RZ</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4340,18 +4340,18 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Franska II: Muntlig franska</t>
+          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4361,19 +4361,19 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>AJP278</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4383,18 +4383,18 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Franska II med didaktisk inriktning</t>
+          <t>Interkulturella litteraturstudier: Teori och metod</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4404,14 +4404,14 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>AJP279</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
+          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4447,19 +4447,19 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GEN2RZ</t>
+          <t>AJP27A</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4475,12 +4475,12 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
+          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4490,14 +4490,14 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>AJP278</t>
+          <t>AJP27B</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Teori och metod</t>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4533,19 +4533,19 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>AJP279</t>
+          <t>GAR2SQ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4555,18 +4555,18 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
+          <t>Modern arabisk litteratur</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4576,19 +4576,19 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>AJP27A</t>
+          <t>GTY2ST</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4598,18 +4598,18 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
+          <t>Tyska: Tysk grammatik med textkommentar</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4619,19 +4619,19 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>AJP27B</t>
+          <t>GTY2SV</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4641,18 +4641,18 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4662,19 +4662,19 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GAR2SQ</t>
+          <t>GEN2VE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4684,18 +4684,18 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Modern arabisk litteratur</t>
+          <t>Engelskspråkig litteratur</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4705,19 +4705,19 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GTY2ST</t>
+          <t>GKI2VL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4727,18 +4727,18 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tyska: Tysk grammatik med textkommentar</t>
+          <t>Kinas kultur och samhälle - introduktionskurs</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4748,19 +4748,19 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GTY2SV</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4770,18 +4770,18 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
+          <t>Franska: Språkdidaktik I</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4791,19 +4791,19 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GEN2VE</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4813,18 +4813,18 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Engelskspråkig litteratur</t>
+          <t>Franska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4834,19 +4834,19 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GKI2VL</t>
+          <t>AJP287</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4856,18 +4856,18 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Kinas kultur och samhälle - introduktionskurs</t>
+          <t>Japanska: Interkulturell kommunikation</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4877,19 +4877,19 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4899,18 +4899,18 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Franska: Språkdidaktik I</t>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4920,19 +4920,19 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>GRY325</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4942,18 +4942,18 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Franska I med didaktisk inriktning</t>
+          <t>Introduktion till rysk opera 2</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4963,19 +4963,19 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4985,18 +4985,18 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Kinesiska I med didaktisk inriktning</t>
+          <t>Tyska: Språkdidaktik II</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5006,19 +5006,19 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>AJP287</t>
+          <t>AKI28Y</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5028,18 +5028,18 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Japanska: Interkulturell kommunikation</t>
+          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5049,19 +5049,19 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>GFR35F</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5071,18 +5071,18 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5092,19 +5092,19 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GRY325</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5114,18 +5114,18 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Introduktion till rysk opera 2</t>
+          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5135,19 +5135,19 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GRY36G</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5157,18 +5157,18 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tyska: Språkdidaktik II</t>
+          <t>Introduktion till rysk film</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5178,19 +5178,19 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>AKI28Y</t>
+          <t>GRY36H</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5200,18 +5200,18 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
+          <t>Sovjetisk och postsovjetisk science fiction-film</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5221,19 +5221,19 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GFR35F</t>
+          <t>GRY37X</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5243,18 +5243,18 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
+          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5264,19 +5264,19 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>AFR29D</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5286,18 +5286,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5307,19 +5311,19 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GRY36G</t>
+          <t>AJP2A9</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5329,18 +5333,18 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Introduktion till rysk film</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5350,19 +5354,19 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GRY36H</t>
+          <t>ATY29E</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5372,18 +5376,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sovjetisk och postsovjetisk science fiction-film</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5393,19 +5401,19 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GRY37X</t>
+          <t>TY3013</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5415,18 +5423,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
+          <t>Tyska: Modern kvinnolitteratur</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5436,19 +5448,19 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>AFR29D</t>
+          <t>GIT2T6</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5458,22 +5470,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
+          <t>Italienska nobelpristagare i litteratur</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5483,19 +5495,19 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>AJP2A9</t>
+          <t>GIT2TD</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -5505,18 +5517,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
+          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5526,19 +5542,19 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>ATY29E</t>
+          <t>GIT2TG</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5548,22 +5564,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
+          <t>Italienska A: Kultur och samhälle, norra Italien</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5573,19 +5589,19 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>TY3013</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5595,22 +5611,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tyska: Modern kvinnolitteratur</t>
+          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5620,14 +5636,14 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GIT2T6</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5657,7 +5673,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Italienska nobelpristagare i litteratur</t>
+          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5667,14 +5683,14 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GIT2TD</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5704,7 +5720,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
+          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5714,14 +5730,14 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GIT2TG</t>
+          <t>GIT2TM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5751,7 +5767,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, norra Italien</t>
+          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5761,14 +5777,14 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>GIT2TN</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5798,7 +5814,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
+          <t>Italienska A: Textanalys, deckargenren</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5808,14 +5824,14 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GIT2TJ</t>
+          <t>GIT2Y9</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5830,7 +5846,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5845,7 +5861,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
+          <t>Italienska A: Textanalys, familjeskildringar</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5855,14 +5871,14 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GIT2YA</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5877,7 +5893,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5892,7 +5908,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
+          <t>Italienska A: Textanalys, krig och fred</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5902,14 +5918,14 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GIT2TM</t>
+          <t>GIT2YB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5924,7 +5940,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5939,7 +5955,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
+          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5949,14 +5965,14 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GIT2TN</t>
+          <t>GIT2YC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5971,7 +5987,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5986,7 +6002,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, deckargenren</t>
+          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5996,14 +6012,14 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y9</t>
+          <t>GIT2YD</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6033,7 +6049,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, familjeskildringar</t>
+          <t>Italienska A: Textanalys, kvinnoskildringar</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6043,19 +6059,19 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GIT2YA</t>
+          <t>GSP39N</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6065,22 +6081,18 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, krig och fred</t>
+          <t>Spanska: Förberedande kurs</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6090,19 +6102,19 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GIT2YB</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -6112,22 +6124,18 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6137,19 +6145,19 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GIT2YC</t>
+          <t>GSS39S</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6159,22 +6167,18 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
+          <t>Den globala skolan - undervisning inom grundskolan</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6184,19 +6188,19 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GIT2YD</t>
+          <t>GSS39T</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6206,22 +6210,18 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, kvinnoskildringar</t>
+          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6231,19 +6231,19 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GSP39N</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -6259,12 +6259,12 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Spanska: Förberedande kurs</t>
+          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6274,19 +6274,19 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>AJP2AH</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6296,18 +6296,18 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Klassisk japanska</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6317,19 +6317,19 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GSS39S</t>
+          <t>GEN3BR</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6339,18 +6339,18 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom grundskolan</t>
+          <t>Kulturella texter och kontexter</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6360,19 +6360,19 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GSS39T</t>
+          <t>GKI3C9</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -6382,18 +6382,18 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
+          <t>Kinesiska för affärslivet II</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6403,19 +6403,19 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -6425,18 +6425,18 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
+          <t>Kinesiska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6446,19 +6446,19 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>AJP2AH</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -6468,18 +6468,18 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Klassisk japanska</t>
+          <t>Tyska: Språk, media och AI</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6489,19 +6489,19 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GEN3BR</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -6511,18 +6511,18 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Kulturella texter och kontexter</t>
+          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6532,19 +6532,19 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GKI3C9</t>
+          <t>GPR3E5</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6554,18 +6554,18 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Portugisiska</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Kinesiska för affärslivet II</t>
+          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6575,19 +6575,19 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GKI3CD</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6597,18 +6597,18 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Kinesiska: Kandidatexamensarbete</t>
+          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6618,19 +6618,19 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>AEN2BR</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6640,18 +6640,18 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Kinesiska III med didaktisk inriktning</t>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6661,14 +6661,14 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GSS3C6</t>
+          <t>GSS3HE</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lärande genom fiktionstext i gymnasieskolan</t>
+          <t>Sociolingvistiska perspektiv på modersmålsundervisning</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6704,19 +6704,19 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GSS3HF</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6726,18 +6726,18 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tyska: Språk, media och AI</t>
+          <t>Flerspråkiga perspektiv på skriftspråksutveckling</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6747,19 +6747,19 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6769,18 +6769,18 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
+          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6790,19 +6790,19 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GPR3E5</t>
+          <t>GSS3K2</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6812,18 +6812,18 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Portugisiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
+          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6833,19 +6833,19 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6855,18 +6855,18 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+          <t>Engelska II</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6876,19 +6876,19 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>AEN2BR</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6898,18 +6898,18 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6919,19 +6919,19 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GSS3HC</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6941,18 +6941,18 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Introduktion till modersmålsundervisning och studiehandledning på modersmålet</t>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6962,313 +6962,12 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HC</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>GSS3HE</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Svenska som andraspråk</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Sociolingvistiska perspektiv på modersmålsundervisning</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>GSS3HF</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Svenska som andraspråk</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Flerspråkiga perspektiv på skriftspråksutveckling</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>GSV3JE</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Svenska</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I151" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>GSS3K2</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Svenska som andraspråk</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>GEN3K3</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>ENA</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Engelska</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Engelska II</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>ASV2CP</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Svenska</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>ASV2CQ</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Svenska</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I155"/>
+  <autoFilter ref="A1:I148"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -7564,20 +7263,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId308"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I148"/>
+  <dimension ref="A1:I170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -539,12 +539,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>JP1045</t>
+          <t>TY1049</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -554,18 +554,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2013-10-31</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Att kommunicera på japanskt vis</t>
+          <t>Tyskspråkig litteratur och litteraturhistoria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -575,14 +579,14 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>JP1046</t>
+          <t>JP1045</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -608,7 +612,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Att göra affärer i Japan</t>
+          <t>Att kommunicera på japanskt vis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -618,19 +622,19 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>JP1046</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -640,22 +644,18 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
+          <t>2013-10-31</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kinesiska i tal och skrift IV</t>
+          <t>Att göra affärer i Japan</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -665,19 +665,19 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1046</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SS3004</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -687,18 +687,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2014-04-11</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2013-11-04</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk i ett tvärspråkligt perspektiv</t>
+          <t>Kinesiska i tal och skrift IV</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -708,19 +712,19 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>SS3003</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -730,18 +734,18 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2014-07-11</t>
+          <t>2014-03-20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kinesisk textläsning på medelnivå</t>
+          <t>Svenska som andraspråk i ett utvecklingsperspektiv - förklaringsmodeller och metodologiska perspektiv</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -751,19 +755,19 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>EN2037</t>
+          <t>SS3004</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -773,18 +777,18 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2014-04-11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Social variation, språkkontakt och språklig makt i engelskan</t>
+          <t>Svenska som andraspråk i ett tvärspråkligt perspektiv</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -794,19 +798,19 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -816,18 +820,18 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Flerspråkighet, interaktion och identitetsskapande i klassrum</t>
+          <t>Kinesisk textläsning på medelnivå</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -837,19 +841,19 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>EN2037</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -859,18 +863,18 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Litteracitet och flerspråkighet</t>
+          <t>Social variation, språkkontakt och språklig makt i engelskan</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -880,19 +884,19 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2037</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>KI2012</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -902,18 +906,18 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2015-02-05</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kinesiska: Forskningsmetodik</t>
+          <t>Flerspråkighet, interaktion och identitetsskapande i klassrum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -923,14 +927,14 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -945,7 +949,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -956,7 +960,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare åk 7-9, 45 hp (1-45). Ingår i Lärarlyftet II</t>
+          <t>Litteracitet och flerspråkighet</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -966,19 +970,19 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>EN3070</t>
+          <t>KI2012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -988,18 +992,18 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2015-03-12</t>
+          <t>2015-02-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Engelska IV, examensarbete 2 för ämneslärarexamen, åk 7-9</t>
+          <t>Kinesiska: Forskningsmetodik</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1009,19 +1013,19 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1031,18 +1035,18 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2015-03-12</t>
+          <t>2015-03-03</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Engelska IV, inklusive examensarbete 2 för ämneslärarexamen, gy</t>
+          <t>Svenska som andraspråk för lärare åk 7-9, 45 hp (1-45). Ingår i Lärarlyftet II</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1052,14 +1056,14 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>EN1129</t>
+          <t>EN3070</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1074,7 +1078,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2015-10-09</t>
+          <t>2015-03-12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -1085,7 +1089,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Engelska: Skriftlig språkfärdighet</t>
+          <t>Engelska IV, examensarbete 2 för ämneslärarexamen, åk 7-9</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1095,14 +1099,14 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>EN3064</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1117,14 +1121,10 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2013-12-09</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2015-11-03</t>
-        </is>
-      </c>
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>Engelska</t>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Engelska: Avancerad litteraturteori</t>
+          <t>Engelska IV, inklusive examensarbete 2 för ämneslärarexamen, gy</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1142,19 +1142,19 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SS3010</t>
+          <t>EN1129</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1164,18 +1164,18 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2015-12-14</t>
+          <t>2015-10-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Svensk fonologi i ett andraspråksperspektiv</t>
+          <t>Engelska: Skriftlig språkfärdighet</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1185,14 +1185,14 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>EN2046</t>
+          <t>EN3064</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1207,10 +1207,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2016-02-05</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>2013-12-09</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2015-11-03</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>Engelska</t>
@@ -1218,7 +1222,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Engelska III, inklusive examensarbete 1 för ämneslärarexamen, gy</t>
+          <t>Engelska: Avancerad litteraturteori</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1228,19 +1232,19 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>EN2047</t>
+          <t>SS3010</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1250,18 +1254,18 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2016-02-05</t>
+          <t>2015-12-14</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Engelska III, examensarbete 1 för ämneslärarexamen, åk 7-9</t>
+          <t>Svensk fonologi i ett andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1271,19 +1275,19 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1293,22 +1297,18 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2016-04-14</t>
-        </is>
-      </c>
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Portugisiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Portugisiska: Vetenskaplig metod och akademiskt skrivande</t>
+          <t>Engelska III, inklusive examensarbete 1 för ämneslärarexamen, gy</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1318,19 +1318,19 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>JP2013</t>
+          <t>EN2047</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1340,18 +1340,18 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
+          <t>2016-02-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Japanska: Modern och nutida litteratur</t>
+          <t>Engelska III, examensarbete 1 för ämneslärarexamen, åk 7-9</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1361,19 +1361,19 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>EN2025</t>
+          <t>TY1069</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1383,22 +1383,18 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2016-05-26</t>
-        </is>
-      </c>
+          <t>2016-02-11</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Litteratur och teori</t>
+          <t>Tyska: Språk- och kulturhistoria med akademiskt skrivande</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1408,19 +1404,19 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>SS3014</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1430,18 +1426,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2016-11-18</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Portugisiska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Flerspråkighet i ett samhällsperspektiv</t>
+          <t>Portugisiska: Vetenskaplig metod och akademiskt skrivande</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1451,19 +1451,19 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AR1025</t>
+          <t>JP2013</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1473,22 +1473,18 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2013-06-14</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2017-10-03</t>
-        </is>
-      </c>
+          <t>2016-04-15</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Arabiska VI - muntlig kommunikation</t>
+          <t>Japanska: Modern och nutida litteratur</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1498,19 +1494,19 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AR2006</t>
+          <t>EN2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1520,22 +1516,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2015-06-15</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2017-10-03</t>
+          <t>2016-05-26</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Arabiska: Avancerad grammatik II</t>
+          <t>Litteratur och teori</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1545,19 +1541,19 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AR2007</t>
+          <t>TY1071</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1567,22 +1563,18 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2015-06-15</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2017-10-03</t>
-        </is>
-      </c>
+          <t>2016-11-01</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Det egna jaget och den andre – gestaltning i arabisk litteratur</t>
+          <t>Tyska grundläggande kurs IV</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1592,19 +1584,19 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AR2009</t>
+          <t>SS3014</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1614,22 +1606,18 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2015-09-15</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2017-10-03</t>
-        </is>
-      </c>
+          <t>2016-11-18</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Modern arabisk litteratur och sökandet efter frihet</t>
+          <t>Flerspråkighet i ett samhällsperspektiv</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1639,19 +1627,19 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AR2010</t>
+          <t>TY1073</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1661,22 +1649,18 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2015-09-15</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2017-10-03</t>
-        </is>
-      </c>
+          <t>2017-02-13</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Arabiska: Avancerad grammatik</t>
+          <t>Tyska: Muntlig språkfärdighet och kulturkunskap II</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1686,14 +1670,14 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>AR2011</t>
+          <t>AR1025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1708,7 +1692,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2013-06-14</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1723,7 +1707,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Den arabiska akademiska kanon</t>
+          <t>Arabiska VI - muntlig kommunikation</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1733,19 +1717,19 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>AR2006</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1755,18 +1739,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>2015-06-15</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Kinesiska: grundläggande språkfärdighet</t>
+          <t>Arabiska: Avancerad grammatik II</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1776,19 +1764,19 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2006</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GEN222</t>
+          <t>AR2007</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1798,18 +1786,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2018-03-22</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>2015-06-15</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Engelska för lärare, 45 hp (1-45 hp), åk 7-9 - ingår i Lärarlyftet II</t>
+          <t>Det egna jaget och den andre – gestaltning i arabisk litteratur</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1819,19 +1811,19 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2007</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GSS22M</t>
+          <t>AR2009</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1841,18 +1833,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2018-04-19</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>2015-09-15</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Studiehandledning på modersmål</t>
+          <t>Modern arabisk litteratur och sökandet efter frihet</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1862,19 +1858,19 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GSS22P</t>
+          <t>AR2010</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1884,18 +1880,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2018-04-19</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>2015-09-15</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Den globala skolan - förskola och grundskola</t>
+          <t>Arabiska: Avancerad grammatik</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1905,19 +1905,19 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GTY23C</t>
+          <t>AR2011</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1927,18 +1927,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>2015-09-18</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tyskspråkig barn- och ungdomslitteratur</t>
+          <t>Den arabiska akademiska kanon</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1948,19 +1952,19 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GJP243</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1970,18 +1974,18 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Japanska IV: Språkfärdighet</t>
+          <t>Kinesiska: grundläggande språkfärdighet</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1991,19 +1995,19 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GFR27N</t>
+          <t>GEN222</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2013,18 +2017,18 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
+          <t>2018-03-22</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Franska: Skriftlig språkfärdighet II</t>
+          <t>Engelska för lärare, 45 hp (1-45 hp), åk 7-9 - ingår i Lärarlyftet II</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2034,19 +2038,19 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GFR27Q</t>
+          <t>GSS22M</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2056,18 +2060,18 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
+          <t>2018-04-19</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Franska II: Introduktion till lingvistik och akademiskt skrivande</t>
+          <t>Studiehandledning på modersmål</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2077,19 +2081,19 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GFR27R</t>
+          <t>GSS22P</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2099,18 +2103,18 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
+          <t>2018-04-19</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Franskspråkig litteratur II: Fram till 1900</t>
+          <t>Den globala skolan - förskola och grundskola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2120,19 +2124,19 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GKI27M</t>
+          <t>GTY23C</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2142,18 +2146,18 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2019-03-08</t>
+          <t>2018-06-05</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Kinesiska V: Fördjupningskurs i modern kinesiska</t>
+          <t>Tyskspråkig barn- och ungdomslitteratur</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2163,19 +2167,19 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GFR27S</t>
+          <t>GJP243</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2185,18 +2189,18 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2019-03-11</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Franska med inriktning arbetsliv</t>
+          <t>Japanska IV: Språkfärdighet</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2206,14 +2210,14 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GFR283</t>
+          <t>GFR27N</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2228,7 +2232,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2019-03-12</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2239,7 +2243,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Litteratur och kultur i Maghrebregionen</t>
+          <t>Franska: Skriftlig språkfärdighet II</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2249,19 +2253,19 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GSV2BN</t>
+          <t>GFR27Q</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2271,18 +2275,18 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Svenska: Text och tal</t>
+          <t>Franska II: Introduktion till lingvistik och akademiskt skrivande</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2292,19 +2296,19 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GSV2BP</t>
+          <t>GFR27R</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2314,18 +2318,18 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Svenska: Barn- och ungdomslitteratur i samhällsdialog</t>
+          <t>Franskspråkig litteratur II: Fram till 1900</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2335,19 +2339,19 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ARY23F</t>
+          <t>GKI27M</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2357,18 +2361,18 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2019-03-08</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ryska VI: Stalintidens ideologi och estetik</t>
+          <t>Kinesiska V: Fördjupningskurs i modern kinesiska</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2378,19 +2382,19 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GRY2BR</t>
+          <t>GFR27S</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2400,18 +2404,18 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2019-03-11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ryska V: Samtida rysk litteratur och kultur</t>
+          <t>Franska med inriktning arbetsliv</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2421,19 +2425,19 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>AR1003</t>
+          <t>GFR283</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2443,22 +2447,18 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2008-10-23</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2019-03-12</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Den moderna arabiska novellen</t>
+          <t>Litteratur och kultur i Maghrebregionen</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2468,19 +2468,19 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>AR1018</t>
+          <t>GSV2BN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2490,22 +2490,18 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2012-04-19</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Arabiska för nybörjare I</t>
+          <t>Svenska: Text och tal</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2515,19 +2511,19 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>TY3012</t>
+          <t>GSV2BP</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2537,22 +2533,18 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tyska: Språkvetenskapens historia</t>
+          <t>Svenska: Barn- och ungdomslitteratur i samhällsdialog</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2562,19 +2554,19 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AJP23N</t>
+          <t>ARY23F</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2584,18 +2576,18 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Introduktion till interkulturella litteraturstudier</t>
+          <t>Ryska VI: Stalintidens ideologi och estetik</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2605,19 +2597,19 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AJP23P</t>
+          <t>GRY2BR</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2627,18 +2619,18 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademiskt skrivande</t>
+          <t>Ryska V: Samtida rysk litteratur och kultur</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2648,19 +2640,19 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AJP23Q</t>
+          <t>AR1003</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2670,18 +2662,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>2008-10-23</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Världslitteraturer: Asien och Europa</t>
+          <t>Den moderna arabiska novellen</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2691,19 +2687,19 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AJP23R</t>
+          <t>AR1018</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2713,18 +2709,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>2012-04-19</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Världslitteraturer: Nord- och Sydamerika</t>
+          <t>Arabiska för nybörjare I</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2734,19 +2734,19 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AFR24Z</t>
+          <t>TY1050</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2756,18 +2756,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2020-03-09</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Franska: Argumentation och retorik</t>
+          <t>Tyska: Skriftlig språkfärdighet II</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2777,19 +2781,19 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2799,18 +2803,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>2013-11-04</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i åk 4-6, 30 hp (1-30 hp). Ingår i Lärarlyftet.</t>
+          <t>Tyska, Språkdidaktik II</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2820,19 +2828,19 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>ARY25M</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2842,18 +2850,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2020-04-21</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ryska VI: Det virtuella Ryssland: politik, språk och nya medier</t>
+          <t>Tyska: Den moderna tyskspråkiga lingvistikens utveckling</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2863,19 +2875,19 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>TY3012</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2885,18 +2897,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2020-04-27</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska III med didaktisk inriktning</t>
+          <t>Tyska: Språkvetenskapens historia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2906,19 +2922,19 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GEN2HB</t>
+          <t>AJP23N</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2928,18 +2944,18 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-01-29</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Engelska för internationellt företagande: kommunikation och kultur</t>
+          <t>Introduktion till interkulturella litteraturstudier</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2949,19 +2965,19 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>EN1086</t>
+          <t>AJP23P</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2971,22 +2987,18 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2012-02-16</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Engelsk språkstruktur</t>
+          <t>Interkulturella litteraturstudier: Akademiskt skrivande</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2996,19 +3008,19 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>EN3029</t>
+          <t>AJP23Q</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3018,22 +3030,18 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2008-01-11</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Engelska: Samtida irländsk skönlitteratur</t>
+          <t>Världslitteraturer: Asien och Europa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3043,19 +3051,19 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>KI2001</t>
+          <t>AJP23R</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3065,22 +3073,18 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Kinesisk modern litteratur I</t>
+          <t>Världslitteraturer: Nord- och Sydamerika</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3090,19 +3094,19 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AR1004</t>
+          <t>AFR24Z</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3112,22 +3116,18 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2008-10-23</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2020-07-03</t>
-        </is>
-      </c>
+          <t>2020-03-09</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Arabiska dialekter med inriktning på den Syriska</t>
+          <t>Franska: Argumentation och retorik</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3137,19 +3137,19 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AR1007</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3159,22 +3159,18 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2009-04-24</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2020-07-03</t>
-        </is>
-      </c>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Arabiska dialekter med inriktning på den syriska II</t>
+          <t>Svenska som andraspråk för lärare i åk 4-6, 30 hp (1-30 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3184,19 +3180,19 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AR1009</t>
+          <t>ARY25M</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3206,22 +3202,18 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2020-07-03</t>
-        </is>
-      </c>
+          <t>2020-04-21</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Arabiska dialekter: Syriska III</t>
+          <t>Ryska VI: Det virtuella Ryssland: politik, språk och nya medier</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3231,19 +3223,19 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>AR1012</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3253,22 +3245,18 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2010-09-21</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2020-07-03</t>
-        </is>
-      </c>
+          <t>2020-04-27</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Arabiska dialekter: Syriska IV</t>
+          <t>Modersmål: Arabiska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3278,19 +3266,19 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>GEN2HB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3300,22 +3288,18 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2011-11-29</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2020-07-03</t>
-        </is>
-      </c>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Arabiska VIII</t>
+          <t>Engelska för internationellt företagande: kommunikation och kultur</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3325,19 +3309,19 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>KI1031</t>
+          <t>EN1086</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3347,22 +3331,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2011-11-29</t>
+          <t>2012-02-16</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2020-07-03</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Kinesiska i tal och konversation</t>
+          <t>Engelsk språkstruktur</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3372,19 +3356,19 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GRY2HL</t>
+          <t>EN3029</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3394,18 +3378,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
+          <t>2008-01-11</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Introduktion till rysk opera 1</t>
+          <t>Engelska: Samtida irländsk skönlitteratur</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3415,19 +3403,19 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>AJP25X</t>
+          <t>KI2001</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3437,18 +3425,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Litteratur och genus - teori och kritik</t>
+          <t>Kinesisk modern litteratur I</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3458,19 +3450,19 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GFR2HZ</t>
+          <t>AR1004</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3480,18 +3472,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
+          <t>2008-10-23</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Franska: Förberedande kurs IV</t>
+          <t>Arabiska dialekter med inriktning på den Syriska</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3501,19 +3497,19 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>AR1007</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3523,18 +3519,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
+          <t>2009-04-24</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Svenska i vardags-, samhälls- och arbetsliv för internationella studenter</t>
+          <t>Arabiska dialekter med inriktning på den syriska II</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3544,19 +3544,19 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>AR1009</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3566,18 +3566,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+          <t>Arabiska dialekter: Syriska III</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3587,19 +3591,19 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GEN2JG</t>
+          <t>AR1012</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3609,18 +3613,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
+          <t>2010-09-21</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Engelska, Språkdidaktik I</t>
+          <t>Arabiska dialekter: Syriska IV</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3630,19 +3638,19 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3652,18 +3660,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
+          <t>2011-11-29</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Spanska för lärare åk 7-9, 45 hp (1-45 hp). Ingår i Lärarlyftet.</t>
+          <t>Arabiska VIII</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3673,19 +3685,19 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AJP264</t>
+          <t>KI1031</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3695,18 +3707,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>2011-11-29</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Migrationslitteratur i dåtid och nutid</t>
+          <t>Kinesiska i tal och konversation</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3716,19 +3732,19 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GFR2KQ</t>
+          <t>GRY2HL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3738,18 +3754,18 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Franska III: Språkhistoria</t>
+          <t>Introduktion till rysk opera 1</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3759,19 +3775,19 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GFR2KR</t>
+          <t>AJP25X</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3781,18 +3797,18 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Franska: Examensarbete för kandidatexamen</t>
+          <t>Interkulturella litteraturstudier: Litteratur och genus - teori och kritik</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3802,19 +3818,19 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3824,18 +3840,18 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2020-09-04</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Spanska III Lingvistisk inriktning: Kandidatexamensarbete</t>
+          <t>Franska: Förberedande kurs IV</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3845,14 +3861,14 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3867,7 +3883,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3878,7 +3894,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska I med didaktisk inriktning</t>
+          <t>Svenska i vardags-, samhälls- och arbetsliv för internationella studenter</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3888,14 +3904,14 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3910,7 +3926,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3921,7 +3937,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk II med didaktisk inriktning</t>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3931,19 +3947,19 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>GEN2JG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3953,18 +3969,18 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tyska: Språk och nya medier</t>
+          <t>Engelska, Språkdidaktik I</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3974,19 +3990,19 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GTY2N4</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3996,18 +4012,18 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tyskspråkig nutidslitteratur och litteraturkritik</t>
+          <t>Spanska för lärare åk 7-9, 45 hp (1-45 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4017,19 +4033,19 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GKI2PX</t>
+          <t>AJP264</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4039,18 +4055,18 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Kinesiska: skriftlig tillämpning</t>
+          <t>Migrationslitteratur i dåtid och nutid</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4060,19 +4076,19 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>ASS26C</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4082,18 +4098,18 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2020-11-06</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Kinesiska i tal och skrift III</t>
+          <t>Sveriges nationella minoriteter – språk, kultur och identitet</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4103,19 +4119,19 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GEN2QW</t>
+          <t>GFR2KQ</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4125,18 +4141,18 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Engelska, Språkdidaktik l</t>
+          <t>Franska III: Språkhistoria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4146,19 +4162,19 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4168,18 +4184,18 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Franska: Examensarbete för kandidatexamen</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4189,19 +4205,19 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GFR2R3</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4211,18 +4227,18 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Franska II: Muntlig franska</t>
+          <t>Spanska III Lingvistisk inriktning: Kandidatexamensarbete</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4232,19 +4248,19 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4254,18 +4270,18 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Franska II med didaktisk inriktning</t>
+          <t>Modersmål: Arabiska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4275,19 +4291,19 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4297,18 +4313,18 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
+          <t>Svenska som andraspråk II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4318,19 +4334,19 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GEN2RZ</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4340,18 +4356,18 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
+          <t>Tyska: Språk och nya medier</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4361,19 +4377,19 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AJP278</t>
+          <t>GTY2N4</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4383,18 +4399,18 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Teori och metod</t>
+          <t>Tyskspråkig nutidslitteratur och litteraturkritik</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4404,19 +4420,19 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>AJP279</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4426,18 +4442,18 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
+          <t>Tyska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4447,19 +4463,19 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>AJP27A</t>
+          <t>GKI2PX</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4469,18 +4485,18 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
+          <t>Kinesiska: skriftlig tillämpning</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4490,19 +4506,19 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>AJP27B</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4512,18 +4528,18 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+          <t>Kinesiska i tal och skrift III</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4533,19 +4549,19 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GAR2SQ</t>
+          <t>GKI2QA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4555,18 +4571,18 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Modern arabisk litteratur</t>
+          <t>Kinesiska: Kandidatexamensarbete</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4576,19 +4592,19 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GTY2ST</t>
+          <t>GEN2QW</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4598,18 +4614,18 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tyska: Tysk grammatik med textkommentar</t>
+          <t>Engelska, Språkdidaktik l</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4619,19 +4635,19 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GTY2SV</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4641,18 +4657,18 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4662,19 +4678,19 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GEN2VE</t>
+          <t>GFR2R3</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4684,18 +4700,18 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Engelskspråkig litteratur</t>
+          <t>Franska II: Muntlig franska</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4705,19 +4721,19 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GKI2VL</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4727,18 +4743,18 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Kinas kultur och samhälle - introduktionskurs</t>
+          <t>Franska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4748,19 +4764,19 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4770,18 +4786,18 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Franska: Språkdidaktik I</t>
+          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4791,19 +4807,19 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>GEN2RZ</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4813,18 +4829,18 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Franska I med didaktisk inriktning</t>
+          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4834,14 +4850,14 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>AJP287</t>
+          <t>AJP278</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4856,7 +4872,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -4867,7 +4883,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Japanska: Interkulturell kommunikation</t>
+          <t>Interkulturella litteraturstudier: Teori och metod</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4877,19 +4893,19 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>AJP279</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4899,18 +4915,18 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4920,19 +4936,19 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GRY325</t>
+          <t>AJP27A</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4942,18 +4958,18 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Introduktion till rysk opera 2</t>
+          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4963,19 +4979,19 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>AJP27B</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4985,18 +5001,18 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tyska: Språkdidaktik II</t>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5006,19 +5022,19 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>AKI28Y</t>
+          <t>GAR2SQ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5028,18 +5044,18 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
+          <t>Modern arabisk litteratur</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5049,19 +5065,19 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GFR35F</t>
+          <t>GTY2ST</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5071,18 +5087,18 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
+          <t>Tyska: Tysk grammatik med textkommentar</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5092,19 +5108,19 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>GTY2SV</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5114,18 +5130,18 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
+          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5135,19 +5151,19 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GRY36G</t>
+          <t>GEN2VE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5157,18 +5173,18 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Introduktion till rysk film</t>
+          <t>Engelskspråkig litteratur</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5178,19 +5194,19 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GRY36H</t>
+          <t>GKI2VL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5200,18 +5216,18 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sovjetisk och postsovjetisk science fiction-film</t>
+          <t>Kinas kultur och samhälle - introduktionskurs</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5221,19 +5237,19 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GRY37X</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5243,18 +5259,18 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
+          <t>Franska: Språkdidaktik I</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5264,14 +5280,14 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>AFR29D</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5286,14 +5302,10 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>Franska</t>
@@ -5301,7 +5313,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
+          <t>Franska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5311,14 +5323,14 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>AJP2A9</t>
+          <t>AJP287</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5333,7 +5345,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -5344,7 +5356,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
+          <t>Japanska: Interkulturell kommunikation</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5354,19 +5366,19 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>ATY29E</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5376,22 +5388,18 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5401,19 +5409,19 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>TY3013</t>
+          <t>GFR2YU</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5423,22 +5431,18 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2022-11-29</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tyska: Modern kvinnolitteratur</t>
+          <t>Franska: Språkdidaktik II</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5448,19 +5452,19 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GIT2T6</t>
+          <t>GRY325</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5470,22 +5474,18 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Italienska nobelpristagare i litteratur</t>
+          <t>Introduktion till rysk opera 2</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5495,19 +5495,19 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GIT2TD</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -5517,22 +5517,18 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-01-27</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
+          <t>Tyska: Språkdidaktik II</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5542,19 +5538,19 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GIT2TG</t>
+          <t>AKI28Y</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5564,22 +5560,18 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, norra Italien</t>
+          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5589,19 +5581,19 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>GFR35F</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5611,22 +5603,18 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
+          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5636,19 +5624,19 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GIT2TJ</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5658,22 +5646,18 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
+          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5683,19 +5667,19 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GRY36G</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -5705,22 +5689,18 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
+          <t>Introduktion till rysk film</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5730,19 +5710,19 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GIT2TM</t>
+          <t>GRY36H</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5752,22 +5732,18 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
+          <t>Sovjetisk och postsovjetisk science fiction-film</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5777,19 +5753,19 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GIT2TN</t>
+          <t>GRY37X</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5799,22 +5775,18 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, deckargenren</t>
+          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5824,19 +5796,19 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y9</t>
+          <t>AFR29D</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5846,22 +5818,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, familjeskildringar</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5871,19 +5843,19 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GIT2YA</t>
+          <t>AJP2A9</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5893,22 +5865,18 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, krig och fred</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5918,19 +5886,19 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GIT2YB</t>
+          <t>ATY29E</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5940,22 +5908,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5965,19 +5933,19 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GIT2YC</t>
+          <t>TY3013</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5987,22 +5955,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
+          <t>Tyska: Modern kvinnolitteratur</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6012,19 +5980,19 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GIT2YD</t>
+          <t>TY3016</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6034,22 +6002,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2014-01-27</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, kvinnoskildringar</t>
+          <t>Tyska: Former och villkor för dramer och prosatexter</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6059,19 +6027,19 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GSP39N</t>
+          <t>GIT2T6</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6081,18 +6049,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Spanska: Förberedande kurs</t>
+          <t>Italienska nobelpristagare i litteratur</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6102,19 +6074,19 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>GIT2TD</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -6124,18 +6096,22 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6145,19 +6121,19 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GSS39S</t>
+          <t>GIT2TG</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6167,18 +6143,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom grundskolan</t>
+          <t>Italienska A: Kultur och samhälle, norra Italien</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6188,19 +6168,19 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GSS39T</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6210,18 +6190,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
+          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6231,19 +6215,19 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -6253,18 +6237,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
+          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6274,19 +6262,19 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>AJP2AH</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6296,18 +6284,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Klassisk japanska</t>
+          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6317,19 +6309,19 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GEN3BR</t>
+          <t>GIT2TM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6339,18 +6331,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Kulturella texter och kontexter</t>
+          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6360,19 +6356,19 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GKI3C9</t>
+          <t>GIT2TN</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -6382,18 +6378,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Kinesiska för affärslivet II</t>
+          <t>Italienska A: Textanalys, deckargenren</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6403,19 +6403,19 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>GIT2TP</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -6425,18 +6425,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Kinesiska III med didaktisk inriktning</t>
+          <t>Italienska A: Kultur och samhälle, mellersta Italien</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6446,19 +6450,19 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GIT2TQ</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -6468,18 +6472,22 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tyska: Språk, media och AI</t>
+          <t>Italienska A: Textanalys, en litterär resa i mellersta Italien</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6489,19 +6497,19 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TQ</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GIT2Y9</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -6511,18 +6519,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
+          <t>Italienska A: Textanalys, familjeskildringar</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6532,19 +6544,19 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GPR3E5</t>
+          <t>GIT2YA</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6554,18 +6566,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Portugisiska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
+          <t>Italienska A: Textanalys, krig och fred</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6575,19 +6591,19 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GIT2YB</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6597,18 +6613,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6618,19 +6638,19 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>AEN2BR</t>
+          <t>GIT2YC</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6640,18 +6660,22 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6661,19 +6685,19 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GSS3HE</t>
+          <t>GIT2YD</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6683,18 +6707,22 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Sociolingvistiska perspektiv på modersmålsundervisning</t>
+          <t>Italienska A: Textanalys, kvinnoskildringar</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6704,19 +6732,19 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GSS3HF</t>
+          <t>GSP39N</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6726,18 +6754,18 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Flerspråkiga perspektiv på skriftspråksutveckling</t>
+          <t>Spanska: Förberedande kurs</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6747,19 +6775,19 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6769,18 +6797,18 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6790,14 +6818,14 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GSS3K2</t>
+          <t>GSS39S</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6812,7 +6840,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -6823,7 +6851,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
+          <t>Den globala skolan - undervisning inom grundskolan</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6833,19 +6861,19 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>GSS39T</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6855,18 +6883,18 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Engelska II</t>
+          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6876,19 +6904,19 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6898,18 +6926,18 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6919,19 +6947,19 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>AJP2AH</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6941,33 +6969,979 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
+          <t>Japanska</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Klassisk japanska</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>GEN3BQ</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Teman inom populärlitteraturen</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>GEN3BR</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Kulturella texter och kontexter</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BN</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk II med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>GKI3C9</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Kinesiska för affärslivet II</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>GKI3CE</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Kinesiska</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Kinesiska III med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>GSS3C6</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Lärande genom fiktionstext i gymnasieskolan</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>GSS3C7</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>GFR3D2</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Franska I med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>GFR3D3</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Franska II med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B7</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Tyska</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Tyska: Språk, media och AI</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CU</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Tyska</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Tyska II med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>GFR3DL</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Franska</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>GPR3E5</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Portugisiska</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>GSV3FP</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
           <t>Svenska</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>AEN2BR</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HE</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Sociolingvistiska perspektiv på modersmålsundervisning</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HF</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Flerspråkiga perspektiv på skriftspråksutveckling</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>GSV3JE</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Svenska</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>GSS3K2</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>GEN3K3</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Engelska</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Engelska II</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CP</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Svenska</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CQ</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Svenska</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
         <is>
           <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr">
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I148"/>
+  <autoFilter ref="A1:I170"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -7263,6 +8237,50 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId338"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$162</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I170"/>
+  <dimension ref="A1:I162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SS3003</t>
+          <t>SS3004</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2014-03-20</t>
+          <t>2014-04-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk i ett utvecklingsperspektiv - förklaringsmodeller och metodologiska perspektiv</t>
+          <t>Svenska som andraspråk i ett tvärspråkligt perspektiv</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -755,19 +755,19 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SS3004</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -777,18 +777,18 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2014-04-11</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk i ett tvärspråkligt perspektiv</t>
+          <t>Kinesisk textläsning på medelnivå</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -798,19 +798,19 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>EN2037</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -820,18 +820,18 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2014-07-11</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kinesisk textläsning på medelnivå</t>
+          <t>Social variation, språkkontakt och språklig makt i engelskan</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -841,19 +841,19 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2037</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>EN2037</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -863,18 +863,18 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Social variation, språkkontakt och språklig makt i engelskan</t>
+          <t>Flerspråkighet, interaktion och identitetsskapande i klassrum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -884,14 +884,14 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Flerspråkighet, interaktion och identitetsskapande i klassrum</t>
+          <t>Litteracitet och flerspråkighet</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -927,19 +927,19 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>KI2012</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -949,18 +949,18 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2015-02-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Litteracitet och flerspråkighet</t>
+          <t>Kinesiska: Forskningsmetodik</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -970,19 +970,19 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>KI2012</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -992,18 +992,18 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2015-02-05</t>
+          <t>2015-03-03</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kinesiska: Forskningsmetodik</t>
+          <t>Svenska som andraspråk för lärare åk 7-9, 45 hp (1-45). Ingår i Lärarlyftet II</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1013,19 +1013,19 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>EN3070</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1035,18 +1035,18 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2015-03-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare åk 7-9, 45 hp (1-45). Ingår i Lärarlyftet II</t>
+          <t>Engelska IV, examensarbete 2 för ämneslärarexamen, åk 7-9</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>EN3070</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Engelska IV, examensarbete 2 för ämneslärarexamen, åk 7-9</t>
+          <t>Engelska IV, inklusive examensarbete 2 för ämneslärarexamen, gy</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1099,14 +1099,14 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>EN1129</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2015-03-12</t>
+          <t>2015-10-09</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Engelska IV, inklusive examensarbete 2 för ämneslärarexamen, gy</t>
+          <t>Engelska: Skriftlig språkfärdighet</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>EN1129</t>
+          <t>EN3064</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1164,10 +1164,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2015-10-09</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>2013-12-09</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2015-11-03</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>Engelska</t>
@@ -1175,7 +1179,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Engelska: Skriftlig språkfärdighet</t>
+          <t>Engelska: Avancerad litteraturteori</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1185,19 +1189,19 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>EN3064</t>
+          <t>SS3010</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1207,22 +1211,18 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2013-12-09</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2015-11-03</t>
-        </is>
-      </c>
+          <t>2015-12-14</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Engelska: Avancerad litteraturteori</t>
+          <t>Svensk fonologi i ett andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1232,19 +1232,19 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>SS3010</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1254,18 +1254,18 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2015-12-14</t>
+          <t>2016-02-05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Svensk fonologi i ett andraspråksperspektiv</t>
+          <t>Engelska III, inklusive examensarbete 1 för ämneslärarexamen, gy</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1275,14 +1275,14 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>EN2046</t>
+          <t>EN2047</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Engelska III, inklusive examensarbete 1 för ämneslärarexamen, gy</t>
+          <t>Engelska III, examensarbete 1 för ämneslärarexamen, åk 7-9</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1318,19 +1318,19 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>EN2047</t>
+          <t>TY1069</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1340,18 +1340,18 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2016-02-05</t>
+          <t>2016-02-11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Engelska III, examensarbete 1 för ämneslärarexamen, åk 7-9</t>
+          <t>Tyska: Språk- och kulturhistoria med akademiskt skrivande</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1361,19 +1361,19 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TY1069</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1383,18 +1383,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2016-02-11</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Portugisiska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tyska: Språk- och kulturhistoria med akademiskt skrivande</t>
+          <t>Portugisiska: Vetenskaplig metod och akademiskt skrivande</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1404,19 +1408,19 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>JP2013</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1426,22 +1430,18 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2016-04-14</t>
-        </is>
-      </c>
+          <t>2016-04-15</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Portugisiska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Portugisiska: Vetenskaplig metod och akademiskt skrivande</t>
+          <t>Japanska: Modern och nutida litteratur</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1451,19 +1451,19 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>JP2013</t>
+          <t>EN2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1473,18 +1473,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2016-05-26</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Japanska: Modern och nutida litteratur</t>
+          <t>Litteratur och teori</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1494,19 +1498,19 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>EN2025</t>
+          <t>SS3014</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1516,22 +1520,18 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2016-05-26</t>
-        </is>
-      </c>
+          <t>2016-11-18</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Litteratur och teori</t>
+          <t>Flerspråkighet i ett samhällsperspektiv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1541,14 +1541,14 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TY1071</t>
+          <t>TY1073</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2016-11-01</t>
+          <t>2017-02-13</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tyska grundläggande kurs IV</t>
+          <t>Tyska: Muntlig språkfärdighet och kulturkunskap II</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SS3014</t>
+          <t>AR1025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1606,18 +1606,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2016-11-18</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>2013-06-14</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Flerspråkighet i ett samhällsperspektiv</t>
+          <t>Arabiska VI - muntlig kommunikation</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1627,19 +1631,19 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TY1073</t>
+          <t>AR2006</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1649,18 +1653,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2017-02-13</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>2015-06-15</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tyska: Muntlig språkfärdighet och kulturkunskap II</t>
+          <t>Arabiska: Avancerad grammatik II</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1670,14 +1678,14 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2006</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>AR1025</t>
+          <t>AR2007</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1692,7 +1700,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2013-06-14</t>
+          <t>2015-06-15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1707,7 +1715,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Arabiska VI - muntlig kommunikation</t>
+          <t>Det egna jaget och den andre – gestaltning i arabisk litteratur</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1717,14 +1725,14 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2007</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>AR2006</t>
+          <t>AR2009</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1739,7 +1747,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2015-06-15</t>
+          <t>2015-09-15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1754,7 +1762,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Arabiska: Avancerad grammatik II</t>
+          <t>Modern arabisk litteratur och sökandet efter frihet</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1764,14 +1772,14 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>AR2007</t>
+          <t>AR2010</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1786,7 +1794,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2015-06-15</t>
+          <t>2015-09-15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1801,7 +1809,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Det egna jaget och den andre – gestaltning i arabisk litteratur</t>
+          <t>Arabiska: Avancerad grammatik</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1811,14 +1819,14 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>AR2009</t>
+          <t>AR2011</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1833,7 +1841,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2015-09-15</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1848,7 +1856,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Modern arabisk litteratur och sökandet efter frihet</t>
+          <t>Den arabiska akademiska kanon</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1858,19 +1866,19 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>AR2010</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1880,22 +1888,18 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2015-09-15</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2017-10-03</t>
-        </is>
-      </c>
+          <t>2017-12-01</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Arabiska: Avancerad grammatik</t>
+          <t>Kinesiska: grundläggande språkfärdighet</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1905,19 +1909,19 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>AR2011</t>
+          <t>GEN222</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1927,22 +1931,18 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2017-10-03</t>
-        </is>
-      </c>
+          <t>2018-03-22</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Den arabiska akademiska kanon</t>
+          <t>Engelska för lärare, 45 hp (1-45 hp), åk 7-9 - ingår i Lärarlyftet II</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1952,19 +1952,19 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>GSS22M</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1974,18 +1974,18 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2018-04-19</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Kinesiska: grundläggande språkfärdighet</t>
+          <t>Studiehandledning på modersmål</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1995,19 +1995,19 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GEN222</t>
+          <t>GSS22P</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2017,18 +2017,18 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2018-03-22</t>
+          <t>2018-04-19</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Engelska för lärare, 45 hp (1-45 hp), åk 7-9 - ingår i Lärarlyftet II</t>
+          <t>Den globala skolan - förskola och grundskola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2038,19 +2038,19 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GSS22M</t>
+          <t>GTY23C</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2060,18 +2060,18 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2018-04-19</t>
+          <t>2018-06-05</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Studiehandledning på modersmål</t>
+          <t>Tyskspråkig barn- och ungdomslitteratur</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2081,19 +2081,19 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GSS22P</t>
+          <t>GJP243</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2103,18 +2103,18 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2018-04-19</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Den globala skolan - förskola och grundskola</t>
+          <t>Japanska IV: Språkfärdighet</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2124,19 +2124,19 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GTY23C</t>
+          <t>GFR27N</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2146,18 +2146,18 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tyskspråkig barn- och ungdomslitteratur</t>
+          <t>Franska: Skriftlig språkfärdighet II</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2167,19 +2167,19 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GJP243</t>
+          <t>GFR27Q</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2189,18 +2189,18 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Japanska IV: Språkfärdighet</t>
+          <t>Franska II: Introduktion till lingvistik och akademiskt skrivande</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2210,14 +2210,14 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GFR27N</t>
+          <t>GFR27R</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Franska: Skriftlig språkfärdighet II</t>
+          <t>Franskspråkig litteratur II: Fram till 1900</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2253,19 +2253,19 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GFR27Q</t>
+          <t>GKI27M</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2275,18 +2275,18 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
+          <t>2019-03-08</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Franska II: Introduktion till lingvistik och akademiskt skrivande</t>
+          <t>Kinesiska V: Fördjupningskurs i modern kinesiska</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2296,14 +2296,14 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GFR27R</t>
+          <t>GFR27S</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
+          <t>2019-03-11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Franskspråkig litteratur II: Fram till 1900</t>
+          <t>Franska med inriktning arbetsliv</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2339,19 +2339,19 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GKI27M</t>
+          <t>GFR283</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2361,18 +2361,18 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2019-03-08</t>
+          <t>2019-03-12</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Kinesiska V: Fördjupningskurs i modern kinesiska</t>
+          <t>Litteratur och kultur i Maghrebregionen</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2382,19 +2382,19 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GFR27S</t>
+          <t>GSV2BN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2404,18 +2404,18 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2019-03-11</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Franska med inriktning arbetsliv</t>
+          <t>Svenska: Text och tal</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2425,19 +2425,19 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GFR283</t>
+          <t>GSV2BP</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2447,18 +2447,18 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2019-03-12</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Litteratur och kultur i Maghrebregionen</t>
+          <t>Svenska: Barn- och ungdomslitteratur i samhällsdialog</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2468,19 +2468,19 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GSV2BN</t>
+          <t>ARY23F</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2490,18 +2490,18 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Svenska: Text och tal</t>
+          <t>Ryska VI: Stalintidens ideologi och estetik</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2511,19 +2511,19 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GSV2BP</t>
+          <t>GRY2BR</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2533,18 +2533,18 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Svenska: Barn- och ungdomslitteratur i samhällsdialog</t>
+          <t>Ryska V: Samtida rysk litteratur och kultur</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2554,19 +2554,19 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>ARY23F</t>
+          <t>AR1003</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2576,18 +2576,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>2008-10-23</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ryska VI: Stalintidens ideologi och estetik</t>
+          <t>Den moderna arabiska novellen</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2597,19 +2601,19 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GRY2BR</t>
+          <t>AR1018</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2619,18 +2623,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>2012-04-19</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ryska V: Samtida rysk litteratur och kultur</t>
+          <t>Arabiska för nybörjare I</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2640,19 +2648,19 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AR1003</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2662,7 +2670,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2008-10-23</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2672,12 +2680,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Den moderna arabiska novellen</t>
+          <t>Tyska: Den moderna tyskspråkiga lingvistikens utveckling</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2687,19 +2695,19 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AR1018</t>
+          <t>TY3012</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2709,7 +2717,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2012-04-19</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2719,12 +2727,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Arabiska för nybörjare I</t>
+          <t>Tyska: Språkvetenskapens historia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2734,19 +2742,19 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>TY1050</t>
+          <t>AJP23N</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2756,22 +2764,18 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tyska: Skriftlig språkfärdighet II</t>
+          <t>Introduktion till interkulturella litteraturstudier</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2781,19 +2785,19 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>AJP23P</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2803,22 +2807,18 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tyska, Språkdidaktik II</t>
+          <t>Interkulturella litteraturstudier: Akademiskt skrivande</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2828,19 +2828,19 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>AJP23Q</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2850,22 +2850,18 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tyska: Den moderna tyskspråkiga lingvistikens utveckling</t>
+          <t>Världslitteraturer: Asien och Europa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2875,19 +2871,19 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>TY3012</t>
+          <t>AJP23R</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2897,22 +2893,18 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tyska: Språkvetenskapens historia</t>
+          <t>Världslitteraturer: Nord- och Sydamerika</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2922,19 +2914,19 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>AJP23N</t>
+          <t>AFR24Z</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2944,18 +2936,18 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
+          <t>2020-03-09</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Introduktion till interkulturella litteraturstudier</t>
+          <t>Franska: Argumentation och retorik</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2965,19 +2957,19 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>AJP23P</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2987,18 +2979,18 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademiskt skrivande</t>
+          <t>Svenska som andraspråk för lärare i åk 4-6, 30 hp (1-30 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3008,19 +3000,19 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AJP23Q</t>
+          <t>ARY25M</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3030,18 +3022,18 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
+          <t>2020-04-21</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Världslitteraturer: Asien och Europa</t>
+          <t>Ryska VI: Det virtuella Ryssland: politik, språk och nya medier</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3051,19 +3043,19 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AJP23R</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3073,18 +3065,18 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
+          <t>2020-04-27</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Världslitteraturer: Nord- och Sydamerika</t>
+          <t>Modersmål: Arabiska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3094,19 +3086,19 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AFR24Z</t>
+          <t>GEN2HB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3116,18 +3108,18 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2020-03-09</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Franska: Argumentation och retorik</t>
+          <t>Engelska för internationellt företagande: kommunikation och kultur</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3137,19 +3129,19 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>EN1086</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3159,18 +3151,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+          <t>2012-02-16</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i åk 4-6, 30 hp (1-30 hp). Ingår i Lärarlyftet.</t>
+          <t>Engelsk språkstruktur</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3180,19 +3176,19 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>ARY25M</t>
+          <t>EN3029</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3202,18 +3198,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2020-04-21</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>2008-01-11</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ryska VI: Det virtuella Ryssland: politik, språk och nya medier</t>
+          <t>Engelska: Samtida irländsk skönlitteratur</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3223,19 +3223,19 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>KI2001</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3245,18 +3245,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2020-04-27</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska III med didaktisk inriktning</t>
+          <t>Kinesisk modern litteratur I</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3266,19 +3270,19 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GEN2HB</t>
+          <t>AR1004</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3288,18 +3292,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
+          <t>2008-10-23</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Engelska för internationellt företagande: kommunikation och kultur</t>
+          <t>Arabiska dialekter med inriktning på den Syriska</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3309,19 +3317,19 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>EN1086</t>
+          <t>AR1007</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3331,22 +3339,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2012-02-16</t>
+          <t>2009-04-24</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Engelsk språkstruktur</t>
+          <t>Arabiska dialekter med inriktning på den syriska II</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3356,19 +3364,19 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>EN3029</t>
+          <t>AR1009</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3378,22 +3386,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2008-01-11</t>
+          <t>2009-12-01</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Engelska: Samtida irländsk skönlitteratur</t>
+          <t>Arabiska dialekter: Syriska III</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3403,19 +3411,19 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>KI2001</t>
+          <t>AR1012</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3425,22 +3433,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
+          <t>2010-09-21</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Kinesisk modern litteratur I</t>
+          <t>Arabiska dialekter: Syriska IV</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3450,14 +3458,14 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>AR1004</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3472,7 +3480,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2008-10-23</t>
+          <t>2011-11-29</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3487,7 +3495,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Arabiska dialekter med inriktning på den Syriska</t>
+          <t>Arabiska VIII</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3497,19 +3505,19 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>AR1007</t>
+          <t>KI1031</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3519,7 +3527,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2009-04-24</t>
+          <t>2011-11-29</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3529,12 +3537,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Arabiska dialekter med inriktning på den syriska II</t>
+          <t>Kinesiska i tal och konversation</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3544,19 +3552,19 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>AR1009</t>
+          <t>GRY2HL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3566,22 +3574,18 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>2020-07-03</t>
-        </is>
-      </c>
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Arabiska dialekter: Syriska III</t>
+          <t>Introduktion till rysk opera 1</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3591,19 +3595,19 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>AR1012</t>
+          <t>AJP25X</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3613,22 +3617,18 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2010-09-21</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>2020-07-03</t>
-        </is>
-      </c>
+          <t>2020-09-02</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Arabiska dialekter: Syriska IV</t>
+          <t>Interkulturella litteraturstudier: Litteratur och genus - teori och kritik</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3638,19 +3638,19 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3660,22 +3660,18 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2011-11-29</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>2020-07-03</t>
-        </is>
-      </c>
+          <t>2020-09-04</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Arabiska VIII</t>
+          <t>Franska: Förberedande kurs IV</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3685,19 +3681,19 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>KI1031</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3707,22 +3703,18 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2011-11-29</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>2020-07-03</t>
-        </is>
-      </c>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Kinesiska i tal och konversation</t>
+          <t>Svenska i vardags-, samhälls- och arbetsliv för internationella studenter</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3732,19 +3724,19 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GRY2HL</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3754,18 +3746,18 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Introduktion till rysk opera 1</t>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3775,19 +3767,19 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>AJP25X</t>
+          <t>GEN2JG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3797,18 +3789,18 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Litteratur och genus - teori och kritik</t>
+          <t>Engelska, Språkdidaktik I</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3818,19 +3810,19 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GFR2HZ</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3840,18 +3832,18 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Franska: Förberedande kurs IV</t>
+          <t>Spanska för lärare åk 7-9, 45 hp (1-45 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3861,19 +3853,19 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>AJP264</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3883,18 +3875,18 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Svenska i vardags-, samhälls- och arbetsliv för internationella studenter</t>
+          <t>Migrationslitteratur i dåtid och nutid</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3904,19 +3896,19 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>GFR2KQ</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3926,18 +3918,18 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+          <t>Franska III: Språkhistoria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3947,19 +3939,19 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GEN2JG</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3969,18 +3961,18 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Engelska, Språkdidaktik I</t>
+          <t>Franska: Examensarbete för kandidatexamen</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3990,14 +3982,14 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4012,7 +4004,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -4023,7 +4015,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Spanska för lärare åk 7-9, 45 hp (1-45 hp). Ingår i Lärarlyftet.</t>
+          <t>Spanska III Lingvistisk inriktning: Kandidatexamensarbete</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4033,19 +4025,19 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>AJP264</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4055,18 +4047,18 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Migrationslitteratur i dåtid och nutid</t>
+          <t>Modersmål: Arabiska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4076,14 +4068,14 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>ASS26C</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4098,7 +4090,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2020-11-06</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4109,7 +4101,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sveriges nationella minoriteter – språk, kultur och identitet</t>
+          <t>Svenska som andraspråk II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4119,19 +4111,19 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GFR2KQ</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4141,18 +4133,18 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Franska III: Språkhistoria</t>
+          <t>Tyska: Språk och nya medier</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4162,19 +4154,19 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GFR2KR</t>
+          <t>GTY2N4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4184,18 +4176,18 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Franska: Examensarbete för kandidatexamen</t>
+          <t>Tyskspråkig nutidslitteratur och litteraturkritik</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4205,19 +4197,19 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4227,18 +4219,18 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Spanska III Lingvistisk inriktning: Kandidatexamensarbete</t>
+          <t>Tyska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4248,19 +4240,19 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GKI2PX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4270,18 +4262,18 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska I med didaktisk inriktning</t>
+          <t>Kinesiska: skriftlig tillämpning</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4291,19 +4283,19 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4313,18 +4305,18 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk II med didaktisk inriktning</t>
+          <t>Kinesiska i tal och skrift III</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4334,19 +4326,19 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>GKI2QA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4356,18 +4348,18 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tyska: Språk och nya medier</t>
+          <t>Kinesiska: Kandidatexamensarbete</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4377,19 +4369,19 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GTY2N4</t>
+          <t>GEN2QW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4399,18 +4391,18 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tyskspråkig nutidslitteratur och litteraturkritik</t>
+          <t>Engelska, Språkdidaktik l</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4420,19 +4412,19 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4442,18 +4434,18 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tyska III med didaktisk inriktning</t>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4463,19 +4455,19 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GKI2PX</t>
+          <t>GFR2R3</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4485,18 +4477,18 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Kinesiska: skriftlig tillämpning</t>
+          <t>Franska II: Muntlig franska</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4506,19 +4498,19 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4528,18 +4520,18 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Kinesiska i tal och skrift III</t>
+          <t>Franska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4549,19 +4541,19 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GKI2QA</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4571,18 +4563,18 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Kinesiska: Kandidatexamensarbete</t>
+          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4592,14 +4584,14 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GEN2QW</t>
+          <t>GEN2RZ</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4614,7 +4606,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -4625,7 +4617,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Engelska, Språkdidaktik l</t>
+          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4635,19 +4627,19 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>AJP278</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4657,18 +4649,18 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Interkulturella litteraturstudier: Teori och metod</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4678,19 +4670,19 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GFR2R3</t>
+          <t>AJP279</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4700,18 +4692,18 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Franska II: Muntlig franska</t>
+          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4721,19 +4713,19 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>AJP27A</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4743,18 +4735,18 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Franska II med didaktisk inriktning</t>
+          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4764,14 +4756,14 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>AJP27B</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4786,7 +4778,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -4797,7 +4789,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4807,19 +4799,19 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GEN2RZ</t>
+          <t>GAR2SQ</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4829,18 +4821,18 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
+          <t>Modern arabisk litteratur</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4850,19 +4842,19 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>AJP278</t>
+          <t>GTY2ST</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4872,18 +4864,18 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Teori och metod</t>
+          <t>Tyska: Tysk grammatik med textkommentar</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4893,19 +4885,19 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>AJP279</t>
+          <t>GTY2SV</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4915,18 +4907,18 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
+          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4936,19 +4928,19 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>AJP27A</t>
+          <t>GEN2VE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4958,18 +4950,18 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
+          <t>Engelskspråkig litteratur</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4979,19 +4971,19 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>AJP27B</t>
+          <t>GKI2VL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5001,18 +4993,18 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+          <t>Kinas kultur och samhälle - introduktionskurs</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5022,19 +5014,19 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GAR2SQ</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5044,18 +5036,18 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Modern arabisk litteratur</t>
+          <t>Franska: Språkdidaktik I</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5065,19 +5057,19 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GTY2ST</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5087,18 +5079,18 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tyska: Tysk grammatik med textkommentar</t>
+          <t>Franska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5108,19 +5100,19 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GTY2SV</t>
+          <t>AJP287</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5130,18 +5122,18 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
+          <t>Japanska: Interkulturell kommunikation</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5151,19 +5143,19 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GEN2VE</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5173,18 +5165,18 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Engelskspråkig litteratur</t>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5194,19 +5186,19 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GKI2VL</t>
+          <t>GFR2YU</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5216,18 +5208,18 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Kinas kultur och samhälle - introduktionskurs</t>
+          <t>Franska: Språkdidaktik II</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5237,19 +5229,19 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GRY325</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5259,18 +5251,18 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Franska: Språkdidaktik I</t>
+          <t>Introduktion till rysk opera 2</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5280,19 +5272,19 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5302,18 +5294,18 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Franska I med didaktisk inriktning</t>
+          <t>Tyska: Språkdidaktik II</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5323,19 +5315,19 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>AJP287</t>
+          <t>AKI28Y</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5345,18 +5337,18 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Japanska: Interkulturell kommunikation</t>
+          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5366,19 +5358,19 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>GFR35F</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5388,18 +5380,18 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5409,19 +5401,19 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GFR2YU</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5431,18 +5423,18 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Franska: Språkdidaktik II</t>
+          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5452,14 +5444,14 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GRY325</t>
+          <t>GRY36G</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5474,7 +5466,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -5485,7 +5477,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Introduktion till rysk opera 2</t>
+          <t>Introduktion till rysk film</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5495,19 +5487,19 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GRY36H</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -5517,18 +5509,18 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tyska: Språkdidaktik II</t>
+          <t>Sovjetisk och postsovjetisk science fiction-film</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5538,19 +5530,19 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>AKI28Y</t>
+          <t>GRY37X</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5560,18 +5552,18 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
+          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5581,14 +5573,14 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GFR35F</t>
+          <t>AFR29D</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5603,10 +5595,14 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr">
         <is>
           <t>Franska</t>
@@ -5614,7 +5610,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5624,19 +5620,19 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>AJP2A9</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5646,18 +5642,18 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5667,19 +5663,19 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GRY36G</t>
+          <t>ATY29E</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -5689,18 +5685,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Introduktion till rysk film</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5710,19 +5710,19 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GRY36H</t>
+          <t>TY3013</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5732,18 +5732,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sovjetisk och postsovjetisk science fiction-film</t>
+          <t>Tyska: Modern kvinnolitteratur</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5753,19 +5757,19 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GRY37X</t>
+          <t>GIT2T6</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5775,18 +5779,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
+          <t>Italienska nobelpristagare i litteratur</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5796,19 +5804,19 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>AFR29D</t>
+          <t>GIT2TD</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5818,22 +5826,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
+          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5843,19 +5851,19 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>AJP2A9</t>
+          <t>GIT2TG</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5865,18 +5873,22 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
+          <t>Italienska A: Kultur och samhälle, norra Italien</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5886,19 +5898,19 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>ATY29E</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5908,22 +5920,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
+          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5933,19 +5945,19 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>TY3013</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5955,22 +5967,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tyska: Modern kvinnolitteratur</t>
+          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5980,19 +5992,19 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>TY3016</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6002,22 +6014,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2014-01-27</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tyska: Former och villkor för dramer och prosatexter</t>
+          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6027,14 +6039,14 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GIT2T6</t>
+          <t>GIT2TM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6064,7 +6076,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Italienska nobelpristagare i litteratur</t>
+          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6074,14 +6086,14 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GIT2TD</t>
+          <t>GIT2TN</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6111,7 +6123,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
+          <t>Italienska A: Textanalys, deckargenren</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6121,14 +6133,14 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GIT2TG</t>
+          <t>GIT2TP</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6158,7 +6170,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, norra Italien</t>
+          <t>Italienska A: Kultur och samhälle, mellersta Italien</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6168,14 +6180,14 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>GIT2TQ</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6205,7 +6217,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
+          <t>Italienska A: Textanalys, en litterär resa i mellersta Italien</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6215,14 +6227,14 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TQ</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GIT2TJ</t>
+          <t>GIT2Y9</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6237,7 +6249,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6252,7 +6264,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
+          <t>Italienska A: Textanalys, familjeskildringar</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6262,14 +6274,14 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GIT2YA</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6284,7 +6296,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6299,7 +6311,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
+          <t>Italienska A: Textanalys, krig och fred</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6309,14 +6321,14 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GIT2TM</t>
+          <t>GIT2YB</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6331,7 +6343,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6346,7 +6358,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
+          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6356,14 +6368,14 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GIT2TN</t>
+          <t>GIT2YC</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6378,7 +6390,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -6393,7 +6405,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, deckargenren</t>
+          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6403,14 +6415,14 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GIT2TP</t>
+          <t>GIT2YD</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6425,7 +6437,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6440,7 +6452,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, mellersta Italien</t>
+          <t>Italienska A: Textanalys, kvinnoskildringar</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6450,19 +6462,19 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GIT2TQ</t>
+          <t>GSP39N</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -6472,22 +6484,18 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i mellersta Italien</t>
+          <t>Spanska: Förberedande kurs</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6497,19 +6505,19 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y9</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -6519,22 +6527,18 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, familjeskildringar</t>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6544,19 +6548,19 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GIT2YA</t>
+          <t>GSS39S</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6566,22 +6570,18 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, krig och fred</t>
+          <t>Den globala skolan - undervisning inom grundskolan</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6591,19 +6591,19 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GIT2YB</t>
+          <t>GSS39T</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6613,22 +6613,18 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
+          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6638,19 +6634,19 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GIT2YC</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6660,22 +6656,18 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
+          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6685,19 +6677,19 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GIT2YD</t>
+          <t>AJP2AH</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6707,22 +6699,18 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, kvinnoskildringar</t>
+          <t>Klassisk japanska</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6732,19 +6720,19 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GSP39N</t>
+          <t>GEN3BQ</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6754,18 +6742,18 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Spanska: Förberedande kurs</t>
+          <t>Teman inom populärlitteraturen</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6775,19 +6763,19 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>GEN3BR</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6797,18 +6785,18 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Kulturella texter och kontexter</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6818,14 +6806,14 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GSS39S</t>
+          <t>GSS3BN</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6840,7 +6828,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -6851,7 +6839,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom grundskolan</t>
+          <t>Svenska som andraspråk II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6861,19 +6849,19 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GSS39T</t>
+          <t>GKI3C9</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6883,18 +6871,18 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
+          <t>Kinesiska för affärslivet II</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6904,19 +6892,19 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6926,18 +6914,18 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
+          <t>Kinesiska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6947,19 +6935,19 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>AJP2AH</t>
+          <t>GSS3C6</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6969,18 +6957,18 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Klassisk japanska</t>
+          <t>Lärande genom fiktionstext i gymnasieskolan</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6990,19 +6978,19 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GEN3BQ</t>
+          <t>GSS3C7</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7012,18 +7000,18 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Teman inom populärlitteraturen</t>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7033,19 +7021,19 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GEN3BR</t>
+          <t>GFR3D2</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7055,18 +7043,18 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Kulturella texter och kontexter</t>
+          <t>Franska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7076,19 +7064,19 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GSS3BN</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7098,18 +7086,18 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk II med didaktisk inriktning</t>
+          <t>Franska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7119,19 +7107,19 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GKI3C9</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7141,18 +7129,18 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Kinesiska för affärslivet II</t>
+          <t>Tyska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7162,19 +7150,19 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7184,18 +7172,18 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Kinesiska III med didaktisk inriktning</t>
+          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7205,19 +7193,19 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GSS3C6</t>
+          <t>GPR3E5</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7227,18 +7215,18 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Portugisiska</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lärande genom fiktionstext i gymnasieskolan</t>
+          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7248,19 +7236,19 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GSS3C7</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7270,18 +7258,18 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7291,19 +7279,19 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GFR3D2</t>
+          <t>AEN2BR</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7313,18 +7301,18 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Franska I med didaktisk inriktning</t>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7334,19 +7322,19 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7356,18 +7344,18 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Franska II med didaktisk inriktning</t>
+          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7377,19 +7365,19 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GSS3K2</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7399,18 +7387,18 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tyska: Språk, media och AI</t>
+          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7420,19 +7408,19 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7442,18 +7430,18 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tyska II med didaktisk inriktning</t>
+          <t>Engelska II</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7463,19 +7451,19 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7485,18 +7473,18 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7506,19 +7494,19 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>GPR3E5</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7528,18 +7516,18 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Portugisiska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -7549,19 +7537,19 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GEN3KC</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7571,18 +7559,18 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+          <t>Engelska III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -7592,356 +7580,12 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>AEN2BR</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>ENA</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Engelska</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>GSS3HE</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Svenska som andraspråk</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Sociolingvistiska perspektiv på modersmålsundervisning</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>GSS3HF</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Svenska som andraspråk</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Flerspråkiga perspektiv på skriftspråksutveckling</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>GSV3JE</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Svenska</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>GSS3K2</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Svenska som andraspråk</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>GEN3K3</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>ENA</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Engelska</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>Engelska II</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>ASV2CP</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Svenska</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>ASV2CQ</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Svenska</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I170" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3KC</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I170"/>
+  <autoFilter ref="A1:I162"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -8265,22 +7909,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId320"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I169" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId338"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$178</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I162"/>
+  <dimension ref="A1:I178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -496,12 +496,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>TY1049</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -511,18 +511,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III - Andraspråksforskning</t>
+          <t>Tyskspråkig litteratur och litteraturhistoria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -532,19 +536,19 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TY1049</t>
+          <t>JP1045</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -554,22 +558,18 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2013-08-01</t>
-        </is>
-      </c>
+          <t>2013-10-31</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tyskspråkig litteratur och litteraturhistoria</t>
+          <t>Att kommunicera på japanskt vis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -579,14 +579,14 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>JP1045</t>
+          <t>JP1046</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Att kommunicera på japanskt vis</t>
+          <t>Att göra affärer i Japan</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -622,19 +622,19 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1046</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>JP1046</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -644,18 +644,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2013-10-31</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2013-11-04</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Att göra affärer i Japan</t>
+          <t>Kinesiska i tal och skrift IV</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -665,19 +669,19 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>SS3004</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -687,22 +691,18 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
+          <t>2014-04-11</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Kinesiska i tal och skrift IV</t>
+          <t>Svenska som andraspråk i ett tvärspråkligt perspektiv</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -712,19 +712,19 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SS3004</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -734,18 +734,18 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2014-04-11</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk i ett tvärspråkligt perspektiv</t>
+          <t>Kinesisk textläsning på medelnivå</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -755,19 +755,19 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>EN2037</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -777,18 +777,18 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2014-07-11</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kinesisk textläsning på medelnivå</t>
+          <t>Social variation, språkkontakt och språklig makt i engelskan</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -798,19 +798,19 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2037</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>EN2037</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -820,18 +820,18 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Social variation, språkkontakt och språklig makt i engelskan</t>
+          <t>Flerspråkighet, interaktion och identitetsskapande i klassrum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -841,14 +841,14 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Flerspråkighet, interaktion och identitetsskapande i klassrum</t>
+          <t>Litteracitet och flerspråkighet</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -884,19 +884,19 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>KI2012</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -906,18 +906,18 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2015-02-05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Litteracitet och flerspråkighet</t>
+          <t>Kinesiska: Forskningsmetodik</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -927,19 +927,19 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>KI2012</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -949,18 +949,18 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2015-02-05</t>
+          <t>2015-03-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Kinesiska: Forskningsmetodik</t>
+          <t>Svenska som andraspråk för lärare åk 7-9, 45 hp (1-45). Ingår i Lärarlyftet II</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -970,19 +970,19 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>EN3070</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -992,18 +992,18 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2015-03-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare åk 7-9, 45 hp (1-45). Ingår i Lärarlyftet II</t>
+          <t>Engelska IV, examensarbete 2 för ämneslärarexamen, åk 7-9</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1013,14 +1013,14 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>EN3070</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Engelska IV, examensarbete 2 för ämneslärarexamen, åk 7-9</t>
+          <t>Engelska IV, inklusive examensarbete 2 för ämneslärarexamen, gy</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>EN1129</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2015-03-12</t>
+          <t>2015-10-09</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Engelska IV, inklusive examensarbete 2 för ämneslärarexamen, gy</t>
+          <t>Engelska: Skriftlig språkfärdighet</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1099,14 +1099,14 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>EN1129</t>
+          <t>EN3064</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1121,10 +1121,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2015-10-09</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>2013-12-09</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2015-11-03</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>Engelska</t>
@@ -1132,7 +1136,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Engelska: Skriftlig språkfärdighet</t>
+          <t>Engelska: Avancerad litteraturteori</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1142,19 +1146,19 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>EN3064</t>
+          <t>SS3010</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1164,22 +1168,18 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2013-12-09</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2015-11-03</t>
-        </is>
-      </c>
+          <t>2015-12-14</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Engelska: Avancerad litteraturteori</t>
+          <t>Svensk fonologi i ett andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SS3010</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1211,18 +1211,18 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2015-12-14</t>
+          <t>2016-02-05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Svensk fonologi i ett andraspråksperspektiv</t>
+          <t>Engelska III, inklusive examensarbete 1 för ämneslärarexamen, gy</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1232,14 +1232,14 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>EN2046</t>
+          <t>EN2047</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Engelska III, inklusive examensarbete 1 för ämneslärarexamen, gy</t>
+          <t>Engelska III, examensarbete 1 för ämneslärarexamen, åk 7-9</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1275,19 +1275,19 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>EN2047</t>
+          <t>TY1069</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1297,18 +1297,18 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2016-02-05</t>
+          <t>2016-02-11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Engelska III, examensarbete 1 för ämneslärarexamen, åk 7-9</t>
+          <t>Tyska: Språk- och kulturhistoria med akademiskt skrivande</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1318,19 +1318,19 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TY1069</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1340,18 +1340,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2016-02-11</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Portugisiska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tyska: Språk- och kulturhistoria med akademiskt skrivande</t>
+          <t>Portugisiska: Vetenskaplig metod och akademiskt skrivande</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1361,19 +1365,19 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>JP2013</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1383,22 +1387,18 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2016-04-14</t>
-        </is>
-      </c>
+          <t>2016-04-15</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Portugisiska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Portugisiska: Vetenskaplig metod och akademiskt skrivande</t>
+          <t>Japanska: Modern och nutida litteratur</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1408,19 +1408,19 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>JP2013</t>
+          <t>EN2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1430,18 +1430,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2016-05-26</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Japanska: Modern och nutida litteratur</t>
+          <t>Litteratur och teori</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1451,19 +1455,19 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>EN2025</t>
+          <t>SS3014</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1473,22 +1477,18 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2016-05-26</t>
-        </is>
-      </c>
+          <t>2016-11-18</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Litteratur och teori</t>
+          <t>Flerspråkighet i ett samhällsperspektiv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1498,19 +1498,19 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SS3014</t>
+          <t>TY1073</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1520,18 +1520,18 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2016-11-18</t>
+          <t>2017-02-13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Flerspråkighet i ett samhällsperspektiv</t>
+          <t>Tyska: Muntlig språkfärdighet och kulturkunskap II</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1541,19 +1541,19 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TY1073</t>
+          <t>AR1025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1563,18 +1563,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2017-02-13</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>2013-06-14</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tyska: Muntlig språkfärdighet och kulturkunskap II</t>
+          <t>Arabiska VI - muntlig kommunikation</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1584,14 +1588,14 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AR1025</t>
+          <t>AR2006</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1606,7 +1610,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2013-06-14</t>
+          <t>2015-06-15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1621,7 +1625,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Arabiska VI - muntlig kommunikation</t>
+          <t>Arabiska: Avancerad grammatik II</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1631,14 +1635,14 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2006</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AR2006</t>
+          <t>AR2007</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1668,7 +1672,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Arabiska: Avancerad grammatik II</t>
+          <t>Det egna jaget och den andre – gestaltning i arabisk litteratur</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1678,14 +1682,14 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2007</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>AR2007</t>
+          <t>AR2009</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1700,7 +1704,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2015-06-15</t>
+          <t>2015-09-15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1715,7 +1719,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Det egna jaget och den andre – gestaltning i arabisk litteratur</t>
+          <t>Modern arabisk litteratur och sökandet efter frihet</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1725,14 +1729,14 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>AR2009</t>
+          <t>AR2010</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1762,7 +1766,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Modern arabisk litteratur och sökandet efter frihet</t>
+          <t>Arabiska: Avancerad grammatik</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1772,14 +1776,14 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>AR2010</t>
+          <t>AR2011</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1794,7 +1798,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2015-09-15</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1809,7 +1813,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Arabiska: Avancerad grammatik</t>
+          <t>Den arabiska akademiska kanon</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1819,19 +1823,19 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>AR2011</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1841,22 +1845,18 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2017-10-03</t>
-        </is>
-      </c>
+          <t>2017-12-01</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Den arabiska akademiska kanon</t>
+          <t>Kinesiska: grundläggande språkfärdighet</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1866,19 +1866,19 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>GEN222</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1888,18 +1888,18 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2018-03-22</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Kinesiska: grundläggande språkfärdighet</t>
+          <t>Engelska för lärare, 45 hp (1-45 hp), åk 7-9 - ingår i Lärarlyftet II</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GEN222</t>
+          <t>GSS22M</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1931,18 +1931,18 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2018-03-22</t>
+          <t>2018-04-19</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Engelska för lärare, 45 hp (1-45 hp), åk 7-9 - ingår i Lärarlyftet II</t>
+          <t>Studiehandledning på modersmål</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1952,14 +1952,14 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GSS22M</t>
+          <t>GSS22P</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Studiehandledning på modersmål</t>
+          <t>Den globala skolan - förskola och grundskola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1995,19 +1995,19 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GSS22P</t>
+          <t>GTY23C</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2017,18 +2017,18 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2018-04-19</t>
+          <t>2018-06-05</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Den globala skolan - förskola och grundskola</t>
+          <t>Tyskspråkig barn- och ungdomslitteratur</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2038,19 +2038,19 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GTY23C</t>
+          <t>GJP243</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2060,18 +2060,18 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tyskspråkig barn- och ungdomslitteratur</t>
+          <t>Japanska IV: Språkfärdighet</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2081,19 +2081,19 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GJP243</t>
+          <t>GFR27N</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2103,18 +2103,18 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Japanska IV: Språkfärdighet</t>
+          <t>Franska: Skriftlig språkfärdighet II</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2124,14 +2124,14 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GFR27N</t>
+          <t>GFR27Q</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Franska: Skriftlig språkfärdighet II</t>
+          <t>Franska II: Introduktion till lingvistik och akademiskt skrivande</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2167,14 +2167,14 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GFR27Q</t>
+          <t>GFR27R</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Franska II: Introduktion till lingvistik och akademiskt skrivande</t>
+          <t>Franskspråkig litteratur II: Fram till 1900</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2210,19 +2210,19 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GFR27R</t>
+          <t>GKI27M</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2232,18 +2232,18 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
+          <t>2019-03-08</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Franskspråkig litteratur II: Fram till 1900</t>
+          <t>Kinesiska V: Fördjupningskurs i modern kinesiska</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2253,19 +2253,19 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GKI27M</t>
+          <t>GFR27S</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2275,18 +2275,18 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2019-03-08</t>
+          <t>2019-03-11</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Kinesiska V: Fördjupningskurs i modern kinesiska</t>
+          <t>Franska med inriktning arbetsliv</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2296,14 +2296,14 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GFR27S</t>
+          <t>GFR283</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2019-03-11</t>
+          <t>2019-03-12</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Franska med inriktning arbetsliv</t>
+          <t>Litteratur och kultur i Maghrebregionen</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2339,19 +2339,19 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GFR283</t>
+          <t>GSV2BN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2361,18 +2361,18 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2019-03-12</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Litteratur och kultur i Maghrebregionen</t>
+          <t>Svenska: Text och tal</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2382,14 +2382,14 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GSV2BN</t>
+          <t>GSV2BP</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Svenska: Text och tal</t>
+          <t>Svenska: Barn- och ungdomslitteratur i samhällsdialog</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2425,19 +2425,19 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GSV2BP</t>
+          <t>ARY23F</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2447,18 +2447,18 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Svenska: Barn- och ungdomslitteratur i samhällsdialog</t>
+          <t>Ryska VI: Stalintidens ideologi och estetik</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2468,14 +2468,14 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ARY23F</t>
+          <t>GRY2BR</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ryska VI: Stalintidens ideologi och estetik</t>
+          <t>Ryska V: Samtida rysk litteratur och kultur</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2511,19 +2511,19 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GRY2BR</t>
+          <t>AR1003</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2533,18 +2533,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>2008-10-23</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ryska V: Samtida rysk litteratur och kultur</t>
+          <t>Den moderna arabiska novellen</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2554,14 +2558,14 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AR1003</t>
+          <t>AR1018</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2576,7 +2580,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2008-10-23</t>
+          <t>2012-04-19</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2591,7 +2595,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Den moderna arabiska novellen</t>
+          <t>Arabiska för nybörjare I</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2601,19 +2605,19 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AR1018</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2623,7 +2627,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2012-04-19</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2633,12 +2637,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Arabiska för nybörjare I</t>
+          <t>Tyska: Den moderna tyskspråkiga lingvistikens utveckling</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2648,14 +2652,14 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>TY3012</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2670,7 +2674,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2685,7 +2689,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tyska: Den moderna tyskspråkiga lingvistikens utveckling</t>
+          <t>Tyska: Språkvetenskapens historia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2695,19 +2699,19 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>TY3012</t>
+          <t>AJP23N</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2717,22 +2721,18 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tyska: Språkvetenskapens historia</t>
+          <t>Introduktion till interkulturella litteraturstudier</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2742,14 +2742,14 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AJP23N</t>
+          <t>AJP23P</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Introduktion till interkulturella litteraturstudier</t>
+          <t>Interkulturella litteraturstudier: Akademiskt skrivande</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2785,14 +2785,14 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>AJP23P</t>
+          <t>AJP23Q</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademiskt skrivande</t>
+          <t>Världslitteraturer: Asien och Europa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2828,14 +2828,14 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>AJP23Q</t>
+          <t>AJP23R</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Världslitteraturer: Asien och Europa</t>
+          <t>Världslitteraturer: Nord- och Sydamerika</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2871,19 +2871,19 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>AJP23R</t>
+          <t>AFR24Z</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2893,18 +2893,18 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
+          <t>2020-03-09</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Världslitteraturer: Nord- och Sydamerika</t>
+          <t>Franska: Argumentation och retorik</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2914,19 +2914,19 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>AFR24Z</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2936,18 +2936,18 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2020-03-09</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Franska: Argumentation och retorik</t>
+          <t>Svenska som andraspråk för lärare i åk 4-6, 30 hp (1-30 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2957,19 +2957,19 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>ARY25M</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2979,18 +2979,18 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-04-21</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i åk 4-6, 30 hp (1-30 hp). Ingår i Lärarlyftet.</t>
+          <t>Ryska VI: Det virtuella Ryssland: politik, språk och nya medier</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3000,19 +3000,19 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>ARY25M</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3022,18 +3022,18 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2020-04-21</t>
+          <t>2020-04-27</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ryska VI: Det virtuella Ryssland: politik, språk och nya medier</t>
+          <t>Modersmål: Arabiska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3043,19 +3043,19 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>GEN2HB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3065,18 +3065,18 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2020-04-27</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska III med didaktisk inriktning</t>
+          <t>Engelska för internationellt företagande: kommunikation och kultur</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GEN2HB</t>
+          <t>EN1086</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3108,10 +3108,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>2012-02-16</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>Engelska</t>
@@ -3119,7 +3123,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Engelska för internationellt företagande: kommunikation och kultur</t>
+          <t>Engelsk språkstruktur</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3129,14 +3133,14 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>EN1086</t>
+          <t>EN3029</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3151,7 +3155,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2012-02-16</t>
+          <t>2008-01-11</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3166,7 +3170,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Engelsk språkstruktur</t>
+          <t>Engelska: Samtida irländsk skönlitteratur</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3176,19 +3180,19 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>EN3029</t>
+          <t>KI2001</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3198,7 +3202,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2008-01-11</t>
+          <t>2011-02-01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3208,12 +3212,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Engelska: Samtida irländsk skönlitteratur</t>
+          <t>Kinesisk modern litteratur I</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3223,19 +3227,19 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>KI2001</t>
+          <t>AR1004</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3245,22 +3249,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
+          <t>2008-10-23</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Kinesisk modern litteratur I</t>
+          <t>Arabiska dialekter med inriktning på den Syriska</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3270,14 +3274,14 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AR1004</t>
+          <t>AR1007</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3292,7 +3296,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2008-10-23</t>
+          <t>2009-04-24</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3307,7 +3311,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Arabiska dialekter med inriktning på den Syriska</t>
+          <t>Arabiska dialekter med inriktning på den syriska II</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3317,14 +3321,14 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AR1007</t>
+          <t>AR1009</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3339,7 +3343,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2009-04-24</t>
+          <t>2009-12-01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3354,7 +3358,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Arabiska dialekter med inriktning på den syriska II</t>
+          <t>Arabiska dialekter: Syriska III</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3364,14 +3368,14 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>AR1009</t>
+          <t>AR1012</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3386,7 +3390,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2010-09-21</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3401,7 +3405,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Arabiska dialekter: Syriska III</t>
+          <t>Arabiska dialekter: Syriska IV</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3411,14 +3415,14 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>AR1012</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3433,7 +3437,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2010-09-21</t>
+          <t>2011-11-29</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3448,7 +3452,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Arabiska dialekter: Syriska IV</t>
+          <t>Arabiska VIII</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3458,19 +3462,19 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>KI1031</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3490,12 +3494,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Arabiska VIII</t>
+          <t>Kinesiska i tal och konversation</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3505,19 +3509,19 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>KI1031</t>
+          <t>GRY2HL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3527,22 +3531,18 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2011-11-29</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2020-07-03</t>
-        </is>
-      </c>
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Kinesiska i tal och konversation</t>
+          <t>Introduktion till rysk opera 1</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3552,19 +3552,19 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GRY2HL</t>
+          <t>AJP25X</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3574,18 +3574,18 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Introduktion till rysk opera 1</t>
+          <t>Interkulturella litteraturstudier: Litteratur och genus - teori och kritik</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3595,19 +3595,19 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>AJP25X</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3617,18 +3617,18 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2020-09-04</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Litteratur och genus - teori och kritik</t>
+          <t>Franska: Förberedande kurs IV</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3638,19 +3638,19 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GFR2HZ</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3660,18 +3660,18 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Franska: Förberedande kurs IV</t>
+          <t>Svenska i vardags-, samhälls- och arbetsliv för internationella studenter</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Svenska i vardags-, samhälls- och arbetsliv för internationella studenter</t>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3724,19 +3724,19 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>GEN2JG</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3746,18 +3746,18 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+          <t>Engelska, Språkdidaktik I</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3767,19 +3767,19 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GEN2JG</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3795,12 +3795,12 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Engelska, Språkdidaktik I</t>
+          <t>Spanska för lärare åk 7-9, 45 hp (1-45 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3810,19 +3810,19 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>AJP264</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3832,18 +3832,18 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Spanska för lärare åk 7-9, 45 hp (1-45 hp). Ingår i Lärarlyftet.</t>
+          <t>Migrationslitteratur i dåtid och nutid</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3853,19 +3853,19 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>AJP264</t>
+          <t>GFR2KQ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3875,18 +3875,18 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Migrationslitteratur i dåtid och nutid</t>
+          <t>Franska III: Språkhistoria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3896,14 +3896,14 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GFR2KQ</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Franska III: Språkhistoria</t>
+          <t>Franska: Examensarbete för kandidatexamen</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3939,19 +3939,19 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GFR2KR</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3961,18 +3961,18 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Franska: Examensarbete för kandidatexamen</t>
+          <t>Spanska III Lingvistisk inriktning: Kandidatexamensarbete</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3982,19 +3982,19 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4004,18 +4004,18 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Spanska III Lingvistisk inriktning: Kandidatexamensarbete</t>
+          <t>Modersmål: Arabiska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska I med didaktisk inriktning</t>
+          <t>Svenska som andraspråk II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4068,19 +4068,19 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4090,18 +4090,18 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk II med didaktisk inriktning</t>
+          <t>Tyska: Språk och nya medier</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4111,14 +4111,14 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>GTY2N4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tyska: Språk och nya medier</t>
+          <t>Tyskspråkig nutidslitteratur och litteraturkritik</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4154,14 +4154,14 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GTY2N4</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tyskspråkig nutidslitteratur och litteraturkritik</t>
+          <t>Tyska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4197,19 +4197,19 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GKI2PX</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4219,18 +4219,18 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tyska III med didaktisk inriktning</t>
+          <t>Kinesiska: skriftlig tillämpning</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4240,14 +4240,14 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GKI2PX</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Kinesiska: skriftlig tillämpning</t>
+          <t>Kinesiska i tal och skrift III</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4283,14 +4283,14 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GKI2QA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Kinesiska i tal och skrift III</t>
+          <t>Kinesiska: Kandidatexamensarbete</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4326,19 +4326,19 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GKI2QA</t>
+          <t>GEN2QW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4348,18 +4348,18 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Kinesiska: Kandidatexamensarbete</t>
+          <t>Engelska, Språkdidaktik l</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4369,19 +4369,19 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GEN2QW</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4397,12 +4397,12 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Engelska, Språkdidaktik l</t>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4412,19 +4412,19 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>GFR2R3</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4434,18 +4434,18 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Franska II: Muntlig franska</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4455,14 +4455,14 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GFR2R3</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Franska II: Muntlig franska</t>
+          <t>Franska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4498,19 +4498,19 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4526,12 +4526,12 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Franska II med didaktisk inriktning</t>
+          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4541,19 +4541,19 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>GEN2RZ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4563,18 +4563,18 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
+          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4584,19 +4584,19 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GEN2RZ</t>
+          <t>AJP278</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4612,12 +4612,12 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
+          <t>Interkulturella litteraturstudier: Teori och metod</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4627,14 +4627,14 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>AJP278</t>
+          <t>AJP279</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Teori och metod</t>
+          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4670,14 +4670,14 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>AJP279</t>
+          <t>AJP27A</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
+          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4713,14 +4713,14 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>AJP27A</t>
+          <t>AJP27B</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4756,19 +4756,19 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>AJP27B</t>
+          <t>GAR2SQ</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4778,18 +4778,18 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+          <t>Modern arabisk litteratur</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4799,19 +4799,19 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GAR2SQ</t>
+          <t>GTY2ST</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4821,18 +4821,18 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Modern arabisk litteratur</t>
+          <t>Tyska: Tysk grammatik med textkommentar</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4842,14 +4842,14 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GTY2ST</t>
+          <t>GTY2SV</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tyska: Tysk grammatik med textkommentar</t>
+          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4885,19 +4885,19 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GTY2SV</t>
+          <t>GEN2VE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4907,18 +4907,18 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
+          <t>Engelskspråkig litteratur</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4928,19 +4928,19 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GEN2VE</t>
+          <t>GKI2VL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4956,12 +4956,12 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Engelskspråkig litteratur</t>
+          <t>Kinas kultur och samhälle - introduktionskurs</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4971,19 +4971,19 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GKI2VL</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4993,18 +4993,18 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Kinas kultur och samhälle - introduktionskurs</t>
+          <t>Franska: Språkdidaktik I</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5014,14 +5014,14 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Franska: Språkdidaktik I</t>
+          <t>Franska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5057,19 +5057,19 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>AJP287</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5079,18 +5079,18 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Franska I med didaktisk inriktning</t>
+          <t>Japanska: Interkulturell kommunikation</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5100,19 +5100,19 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>AJP287</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5122,18 +5122,18 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Japanska: Interkulturell kommunikation</t>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5143,19 +5143,19 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>GFR2YU</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5165,18 +5165,18 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+          <t>Franska: Språkdidaktik II</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5186,19 +5186,19 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GFR2YU</t>
+          <t>GRY325</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5208,18 +5208,18 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Franska: Språkdidaktik II</t>
+          <t>Introduktion till rysk opera 2</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5229,19 +5229,19 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GRY325</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5251,18 +5251,18 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Introduktion till rysk opera 2</t>
+          <t>Tyska: Språkdidaktik II</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5272,19 +5272,19 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>AKI28Y</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5294,18 +5294,18 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tyska: Språkdidaktik II</t>
+          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5315,19 +5315,19 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>AKI28Y</t>
+          <t>GFR35F</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5337,18 +5337,18 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
+          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5358,19 +5358,19 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GFR35F</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5386,12 +5386,12 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
+          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5401,19 +5401,19 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>GRY36G</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5423,18 +5423,18 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
+          <t>Introduktion till rysk film</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5444,14 +5444,14 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GRY36G</t>
+          <t>GRY36H</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Introduktion till rysk film</t>
+          <t>Sovjetisk och postsovjetisk science fiction-film</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5487,14 +5487,14 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GRY36H</t>
+          <t>GRY37X</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sovjetisk och postsovjetisk science fiction-film</t>
+          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5530,19 +5530,19 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GRY37X</t>
+          <t>AFR29D</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5552,18 +5552,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5573,19 +5577,19 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>AFR29D</t>
+          <t>AJP2A9</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5595,22 +5599,18 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
           <t>2023-12-08</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5620,19 +5620,19 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>AJP2A9</t>
+          <t>ATY29E</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5642,18 +5642,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
           <t>2023-12-08</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5663,14 +5667,14 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ATY29E</t>
+          <t>TY3013</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5685,7 +5689,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5700,7 +5704,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
+          <t>Tyska: Modern kvinnolitteratur</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5710,19 +5714,19 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>TY3013</t>
+          <t>GIT2T6</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5732,22 +5736,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tyska: Modern kvinnolitteratur</t>
+          <t>Italienska nobelpristagare i litteratur</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5757,14 +5761,14 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GIT2T6</t>
+          <t>GIT2TD</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5794,7 +5798,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Italienska nobelpristagare i litteratur</t>
+          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5804,14 +5808,14 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GIT2TD</t>
+          <t>GIT2TG</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5841,7 +5845,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
+          <t>Italienska A: Kultur och samhälle, norra Italien</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5851,14 +5855,14 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GIT2TG</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5888,7 +5892,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, norra Italien</t>
+          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5898,14 +5902,14 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5935,7 +5939,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
+          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5945,14 +5949,14 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GIT2TJ</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5982,7 +5986,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
+          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5992,14 +5996,14 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GIT2TM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6029,7 +6033,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
+          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6039,14 +6043,14 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GIT2TM</t>
+          <t>GIT2TN</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6076,7 +6080,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
+          <t>Italienska A: Textanalys, deckargenren</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6086,14 +6090,14 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GIT2TN</t>
+          <t>GIT2TP</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6123,7 +6127,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, deckargenren</t>
+          <t>Italienska A: Kultur och samhälle, mellersta Italien</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6133,14 +6137,14 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GIT2TP</t>
+          <t>GIT2TQ</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6170,7 +6174,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, mellersta Italien</t>
+          <t>Italienska A: Textanalys, en litterär resa i mellersta Italien</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6180,14 +6184,14 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TQ</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GIT2TQ</t>
+          <t>GIT2Y9</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6202,7 +6206,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6217,7 +6221,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i mellersta Italien</t>
+          <t>Italienska A: Textanalys, familjeskildringar</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6227,14 +6231,14 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y9</t>
+          <t>GIT2YA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6264,7 +6268,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, familjeskildringar</t>
+          <t>Italienska A: Textanalys, krig och fred</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6274,14 +6278,14 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GIT2YA</t>
+          <t>GIT2YB</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6311,7 +6315,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, krig och fred</t>
+          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6321,14 +6325,14 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GIT2YB</t>
+          <t>GIT2YC</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6358,7 +6362,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
+          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6368,14 +6372,14 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GIT2YC</t>
+          <t>GIT2YD</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6405,7 +6409,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
+          <t>Italienska A: Textanalys, kvinnoskildringar</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6415,19 +6419,19 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GIT2YD</t>
+          <t>GSP39N</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -6437,22 +6441,18 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, kvinnoskildringar</t>
+          <t>Spanska: Förberedande kurs</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6462,19 +6462,19 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GSP39N</t>
+          <t>GSS39S</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -6490,12 +6490,12 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Spanska: Förberedande kurs</t>
+          <t>Den globala skolan - undervisning inom grundskolan</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6505,14 +6505,14 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>GSS39T</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6548,14 +6548,14 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GSS39S</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom grundskolan</t>
+          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6591,19 +6591,19 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GSS39T</t>
+          <t>AJP2AH</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6613,18 +6613,18 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
+          <t>Klassisk japanska</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6634,19 +6634,19 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GEN3BQ</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6656,18 +6656,18 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
+          <t>Teman inom populärlitteraturen</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6677,19 +6677,19 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>AJP2AH</t>
+          <t>GEN3BR</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6699,18 +6699,18 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Klassisk japanska</t>
+          <t>Kulturella texter och kontexter</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6720,19 +6720,19 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GEN3BQ</t>
+          <t>GSS3BN</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6748,12 +6748,12 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Teman inom populärlitteraturen</t>
+          <t>Svenska som andraspråk II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6763,19 +6763,19 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GEN3BR</t>
+          <t>GKI3C9</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6785,18 +6785,18 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Kulturella texter och kontexter</t>
+          <t>Kinesiska för affärslivet II</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6806,19 +6806,19 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GSS3BN</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6828,18 +6828,18 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk II med didaktisk inriktning</t>
+          <t>Kinesiska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6849,19 +6849,19 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GKI3C9</t>
+          <t>GSS3C6</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6877,12 +6877,12 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Kinesiska för affärslivet II</t>
+          <t>Lärande genom fiktionstext i gymnasieskolan</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6892,19 +6892,19 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>GFR3D2</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6914,18 +6914,18 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Kinesiska III med didaktisk inriktning</t>
+          <t>Franska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6935,19 +6935,19 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GSS3C6</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6957,18 +6957,18 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lärande genom fiktionstext i gymnasieskolan</t>
+          <t>Franska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6978,19 +6978,19 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GSS3C7</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7000,18 +7000,18 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Tyska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7021,14 +7021,14 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GFR3D2</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Franska I med didaktisk inriktning</t>
+          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7064,19 +7064,19 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GPR3E5</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7086,18 +7086,18 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Portugisiska</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Franska II med didaktisk inriktning</t>
+          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7107,19 +7107,19 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7129,18 +7129,18 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tyska II med didaktisk inriktning</t>
+          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7150,19 +7150,19 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>AEN2BR</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7172,18 +7172,18 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7193,19 +7193,19 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GPR3E5</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7215,18 +7215,18 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Portugisiska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
+          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7236,19 +7236,19 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSS3K2</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7258,18 +7258,18 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7279,14 +7279,14 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>AEN2BR</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+          <t>Engelska II</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7322,14 +7322,14 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7365,19 +7365,19 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GSS3K2</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7387,18 +7387,18 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7408,14 +7408,14 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>AEN2CT</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Engelska II</t>
+          <t>Introduktion till interkulturella litteraturstudier</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7451,19 +7451,19 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2CT</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>AEN2CU</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7473,18 +7473,18 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+          <t>Interkulturella litteraturstudier: Magisterexamensarbete</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7494,19 +7494,19 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2CU</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>GIT3KL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7516,18 +7516,18 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
+          <t>Italienska A: Textanalys, barn- och ungdomsskildringar</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -7537,19 +7537,19 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KL</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GEN3KC</t>
+          <t>GIT3KM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7559,18 +7559,18 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Engelska III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Italienska A: Fonetik och muntlig språkfärdighet</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -7580,12 +7580,712 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3KC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KM</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>GIT3KN</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Italienska</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Italienska A: Grammatik och skriftlig språkfärdighet</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KN</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>GIT3KP</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Italienska</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Italienska B: Muntlig språkfärdighet och kulturkunskap</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KP</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>GIT3KQ</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Italienska</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Italienska B: Grammatik och skriftlig produktion</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>GIT3KR</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Italienska</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Italienska B: Litteraturhistoria med textanalys</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KR</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>GSP3KS</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Spanska</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Spanska II med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>GSP3KT</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Spanska</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Spanska II: Från inbördeskriget till nutiden: Litteratur, film och samhälle i Spanien</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KT</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>GSP3KU</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Spanska</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Spanska II: Skriftlig språkfärdighet och grammatik</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>GSP3KV</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Spanska</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Spanska II: Språklig variation i den spansktalande världen</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KV</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>GTY3KG</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Tyska</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Tyska I med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>GTY3KJ</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Tyska</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Tyska I: Tysk grammatik</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>GTY3KK</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Tyska</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Tyska I: Skrivande och AI</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KK</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>BSV22A</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Svenska</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Baskurs i svenska för lärarutbildning</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BSV22A</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>GSV3KH</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Svenska</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Läs- och skrivinlärning för förskollärare som undervisar i förskoleklass</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3KH</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>GSS39R</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>GSS3C7</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>ISLL</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Svenska som andraspråk III - Andraspråksforskning</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I162"/>
+  <autoFilter ref="A1:I178"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -7909,6 +8609,38 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId320"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId354"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$177</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I178"/>
+  <dimension ref="A1:I177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8103,12 +8103,12 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GSV3KH</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8118,18 +8118,22 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr"/>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Läs- och skrivinlärning för förskollärare som undervisar i förskoleklass</t>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8139,14 +8143,14 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3KH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>GSS3C7</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8161,7 +8165,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -8186,14 +8190,14 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GSS3C7</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8208,7 +8212,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2013-02-04</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -8223,7 +8227,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Svenska som andraspråk III - Andraspråksforskning</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8233,59 +8237,12 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>SS2009</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>Svenska som andraspråk</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Svenska som andraspråk III - Andraspråksforskning</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I178"/>
+  <autoFilter ref="A1:I177"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -8639,8 +8596,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId350"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I177" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId354"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
@@ -5721,7 +5721,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GIT2T6</t>
+          <t>GIT2A3</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2019-06-19</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Italienska nobelpristagare i litteratur</t>
+          <t>Italienska B: Muntlig språkfärdighet och kulturkunskap</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5761,14 +5761,14 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GIT2TD</t>
+          <t>GIT2T6</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
+          <t>Italienska nobelpristagare i litteratur</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5808,14 +5808,14 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GIT2TG</t>
+          <t>GIT2TD</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, norra Italien</t>
+          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5855,14 +5855,14 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>GIT2TE</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
+          <t>Italienska A: Fonetik och muntlig språkfärdighet</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5902,14 +5902,14 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TE</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GIT2TJ</t>
+          <t>GIT2TG</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
+          <t>Italienska A: Kultur och samhälle, norra Italien</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5949,14 +5949,14 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
+          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5996,14 +5996,14 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GIT2TM</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
+          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6043,14 +6043,14 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GIT2TN</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, deckargenren</t>
+          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6090,14 +6090,14 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GIT2TP</t>
+          <t>GIT2TM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, mellersta Italien</t>
+          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6137,14 +6137,14 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GIT2TQ</t>
+          <t>GIT2TN</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i mellersta Italien</t>
+          <t>Italienska A: Textanalys, deckargenren</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6184,14 +6184,14 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y9</t>
+          <t>GIT2TP</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, familjeskildringar</t>
+          <t>Italienska A: Kultur och samhälle, mellersta Italien</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6231,14 +6231,14 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GIT2YA</t>
+          <t>GIT2TQ</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, krig och fred</t>
+          <t>Italienska A: Textanalys, en litterär resa i mellersta Italien</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6278,14 +6278,14 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TQ</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GIT2YB</t>
+          <t>GIT2Y9</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
+          <t>Italienska A: Textanalys, familjeskildringar</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6325,14 +6325,14 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GIT2YC</t>
+          <t>GIT2YA</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
+          <t>Italienska A: Textanalys, krig och fred</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6372,14 +6372,14 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GIT2YD</t>
+          <t>GIT2YB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, kvinnoskildringar</t>
+          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6419,19 +6419,19 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GSP39N</t>
+          <t>GIT2YC</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -6441,18 +6441,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Spanska: Förberedande kurs</t>
+          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6462,19 +6466,19 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GSS39S</t>
+          <t>GIT2YD</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -6484,18 +6488,22 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom grundskolan</t>
+          <t>Italienska A: Textanalys, kvinnoskildringar</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6505,19 +6513,19 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GSS39T</t>
+          <t>GIT2YE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -6527,18 +6535,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
+          <t>Italienska A: Textanalys, barn- och ungdomsskildringar</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6548,19 +6560,19 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YE</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GSP39N</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6576,12 +6588,12 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
+          <t>Spanska: Förberedande kurs</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6591,19 +6603,19 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>AJP2AH</t>
+          <t>GSS39S</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6613,18 +6625,18 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Klassisk japanska</t>
+          <t>Den globala skolan - undervisning inom grundskolan</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6634,19 +6646,19 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GEN3BQ</t>
+          <t>GSS39T</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6656,18 +6668,18 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Teman inom populärlitteraturen</t>
+          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6677,19 +6689,19 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GEN3BR</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6699,18 +6711,18 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Kulturella texter och kontexter</t>
+          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6720,19 +6732,19 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GSS3BN</t>
+          <t>AJP2AH</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6742,18 +6754,18 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk II med didaktisk inriktning</t>
+          <t>Klassisk japanska</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6763,19 +6775,19 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GKI3C9</t>
+          <t>GEN3BQ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6785,18 +6797,18 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Kinesiska för affärslivet II</t>
+          <t>Teman inom populärlitteraturen</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6806,19 +6818,19 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>GEN3BR</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6828,18 +6840,18 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Kinesiska III med didaktisk inriktning</t>
+          <t>Kulturella texter och kontexter</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6849,14 +6861,14 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GSS3C6</t>
+          <t>GSS3BN</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6871,7 +6883,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -6882,7 +6894,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lärande genom fiktionstext i gymnasieskolan</t>
+          <t>Svenska som andraspråk II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6892,19 +6904,19 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GFR3D2</t>
+          <t>GKI3C9</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6914,18 +6926,18 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Franska I med didaktisk inriktning</t>
+          <t>Kinesiska för affärslivet II</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6935,19 +6947,19 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6957,18 +6969,18 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Franska II med didaktisk inriktning</t>
+          <t>Kinesiska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6978,19 +6990,19 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GSS3C6</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7000,18 +7012,18 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tyska II med didaktisk inriktning</t>
+          <t>Lärande genom fiktionstext i gymnasieskolan</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7021,14 +7033,14 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GFR3D2</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -7043,7 +7055,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -7054,7 +7066,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
+          <t>Franska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7064,19 +7076,19 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GPR3E5</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7086,18 +7098,18 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Portugisiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
+          <t>Franska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7107,19 +7119,19 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7129,18 +7141,18 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+          <t>Tyska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7150,19 +7162,19 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>AEN2BR</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7172,18 +7184,18 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7193,19 +7205,19 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GPR3E5</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7215,18 +7227,18 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Portugisiska</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
+          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7236,19 +7248,19 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GSS3K2</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7258,18 +7270,18 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
+          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7279,14 +7291,14 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>AEN2BR</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7301,7 +7313,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7312,7 +7324,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Engelska II</t>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7322,14 +7334,14 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7344,7 +7356,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7355,7 +7367,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7365,19 +7377,19 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>GSS3K2</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7387,18 +7399,18 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
+          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7408,14 +7420,14 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>AEN2CT</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7430,7 +7442,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7441,7 +7453,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Introduktion till interkulturella litteraturstudier</t>
+          <t>Engelska II</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7451,19 +7463,19 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>AEN2CU</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7473,18 +7485,18 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Magisterexamensarbete</t>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7494,19 +7506,19 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>GIT3KL</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7516,18 +7528,18 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, barn- och ungdomsskildringar</t>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -7537,19 +7549,19 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GIT3KM</t>
+          <t>AEN2CT</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7565,12 +7577,12 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Italienska A: Fonetik och muntlig språkfärdighet</t>
+          <t>Introduktion till interkulturella litteraturstudier</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -7580,19 +7592,19 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2CT</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>GIT3KN</t>
+          <t>AEN2CU</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -7608,12 +7620,12 @@
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Italienska A: Grammatik och skriftlig språkfärdighet</t>
+          <t>Interkulturella litteraturstudier: Magisterexamensarbete</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7623,14 +7635,14 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2CU</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>GIT3KP</t>
+          <t>GIT3KN</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7656,7 +7668,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Italienska B: Muntlig språkfärdighet och kulturkunskap</t>
+          <t>Italienska A: Grammatik och skriftlig språkfärdighet</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7666,7 +7678,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KN</t>
         </is>
       </c>
     </row>

--- a/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Vilande kursplaner.xlsx
@@ -2612,7 +2612,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
+          <t>2013-11-04</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tyska: Den moderna tyskspråkiga lingvistikens utveckling</t>
+          <t>Tyska, Språkdidaktik II</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2652,14 +2652,14 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>TY3012</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tyska: Språkvetenskapens historia</t>
+          <t>Tyska: Den moderna tyskspråkiga lingvistikens utveckling</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2699,19 +2699,19 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AJP23N</t>
+          <t>TY3012</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2721,18 +2721,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Introduktion till interkulturella litteraturstudier</t>
+          <t>Tyska: Språkvetenskapens historia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2742,14 +2746,14 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AJP23P</t>
+          <t>AJP23N</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2775,7 +2779,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademiskt skrivande</t>
+          <t>Introduktion till interkulturella litteraturstudier</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2785,14 +2789,14 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>AJP23Q</t>
+          <t>AJP23P</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2818,7 +2822,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Världslitteraturer: Asien och Europa</t>
+          <t>Interkulturella litteraturstudier: Akademiskt skrivande</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2828,14 +2832,14 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>AJP23R</t>
+          <t>AJP23Q</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2861,7 +2865,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Världslitteraturer: Nord- och Sydamerika</t>
+          <t>Världslitteraturer: Asien och Europa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2871,19 +2875,19 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>AFR24Z</t>
+          <t>AJP23R</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2893,18 +2897,18 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2020-03-09</t>
+          <t>2020-01-29</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Franska: Argumentation och retorik</t>
+          <t>Världslitteraturer: Nord- och Sydamerika</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2914,19 +2918,19 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>AFR24Z</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2936,18 +2940,18 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-03-09</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i åk 4-6, 30 hp (1-30 hp). Ingår i Lärarlyftet.</t>
+          <t>Franska: Argumentation och retorik</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2957,19 +2961,19 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ARY25M</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2979,18 +2983,18 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2020-04-21</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ryska VI: Det virtuella Ryssland: politik, språk och nya medier</t>
+          <t>Svenska som andraspråk för lärare i åk 4-6, 30 hp (1-30 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3000,19 +3004,19 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>ARY25M</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3022,18 +3026,18 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2020-04-27</t>
+          <t>2020-04-21</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska III med didaktisk inriktning</t>
+          <t>Ryska VI: Det virtuella Ryssland: politik, språk och nya medier</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3043,19 +3047,19 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GEN2HB</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3065,18 +3069,18 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-04-27</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Engelska för internationellt företagande: kommunikation och kultur</t>
+          <t>Modersmål: Arabiska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3086,14 +3090,14 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>EN1086</t>
+          <t>GEN2HB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3108,14 +3112,10 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2012-02-16</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>Engelska</t>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Engelsk språkstruktur</t>
+          <t>Engelska för internationellt företagande: kommunikation och kultur</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3133,14 +3133,14 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>EN3029</t>
+          <t>EN1086</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2008-01-11</t>
+          <t>2012-02-16</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Engelska: Samtida irländsk skönlitteratur</t>
+          <t>Engelsk språkstruktur</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3180,19 +3180,19 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>KI2001</t>
+          <t>EN3029</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
+          <t>2008-01-11</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Kinesisk modern litteratur I</t>
+          <t>Engelska: Samtida irländsk skönlitteratur</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3227,19 +3227,19 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>AR1004</t>
+          <t>KI2001</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3249,22 +3249,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2008-10-23</t>
+          <t>2011-02-01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2020-07-03</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Arabiska dialekter med inriktning på den Syriska</t>
+          <t>Kinesisk modern litteratur I</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AR1007</t>
+          <t>AR1004</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2009-04-24</t>
+          <t>2008-10-23</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Arabiska dialekter med inriktning på den syriska II</t>
+          <t>Arabiska dialekter med inriktning på den Syriska</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3321,14 +3321,14 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AR1009</t>
+          <t>AR1007</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-04-24</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Arabiska dialekter: Syriska III</t>
+          <t>Arabiska dialekter med inriktning på den syriska II</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3368,14 +3368,14 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>AR1012</t>
+          <t>AR1009</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2010-09-21</t>
+          <t>2009-12-01</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Arabiska dialekter: Syriska IV</t>
+          <t>Arabiska dialekter: Syriska III</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3415,14 +3415,14 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AR1012</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2011-11-29</t>
+          <t>2010-09-21</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Arabiska VIII</t>
+          <t>Arabiska dialekter: Syriska IV</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3462,19 +3462,19 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>KI1031</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Kinesiska i tal och konversation</t>
+          <t>Arabiska VIII</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3509,19 +3509,19 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GRY2HL</t>
+          <t>KI1031</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3531,18 +3531,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
+          <t>2011-11-29</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Introduktion till rysk opera 1</t>
+          <t>Kinesiska i tal och konversation</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3552,19 +3556,19 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>AJP25X</t>
+          <t>GRY2HL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3574,18 +3578,18 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Litteratur och genus - teori och kritik</t>
+          <t>Introduktion till rysk opera 1</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3595,19 +3599,19 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GFR2HZ</t>
+          <t>AJP25X</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3617,18 +3621,18 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Franska: Förberedande kurs IV</t>
+          <t>Interkulturella litteraturstudier: Litteratur och genus - teori och kritik</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3638,19 +3642,19 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3660,18 +3664,18 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-09-04</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Svenska i vardags-, samhälls- och arbetsliv för internationella studenter</t>
+          <t>Franska: Förberedande kurs IV</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3681,14 +3685,14 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3703,7 +3707,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3714,7 +3718,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+          <t>Svenska i vardags-, samhälls- och arbetsliv för internationella studenter</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3724,19 +3728,19 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GEN2JG</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3746,18 +3750,18 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Engelska, Språkdidaktik I</t>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3767,19 +3771,19 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>GEN2JG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3795,12 +3799,12 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Spanska för lärare åk 7-9, 45 hp (1-45 hp). Ingår i Lärarlyftet.</t>
+          <t>Engelska, Språkdidaktik I</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3810,19 +3814,19 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>AJP264</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3832,18 +3836,18 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Migrationslitteratur i dåtid och nutid</t>
+          <t>Spanska för lärare åk 7-9, 45 hp (1-45 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3853,19 +3857,19 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GFR2KQ</t>
+          <t>AJP264</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3875,18 +3879,18 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Franska III: Språkhistoria</t>
+          <t>Migrationslitteratur i dåtid och nutid</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3896,14 +3900,14 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GFR2KR</t>
+          <t>GFR2KQ</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3929,7 +3933,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Franska: Examensarbete för kandidatexamen</t>
+          <t>Franska III: Språkhistoria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3939,19 +3943,19 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3961,18 +3965,18 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Spanska III Lingvistisk inriktning: Kandidatexamensarbete</t>
+          <t>Franska: Examensarbete för kandidatexamen</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3982,19 +3986,19 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4004,18 +4008,18 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska I med didaktisk inriktning</t>
+          <t>Spanska III Lingvistisk inriktning: Kandidatexamensarbete</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4025,14 +4029,14 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4047,7 +4051,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4058,7 +4062,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk II med didaktisk inriktning</t>
+          <t>Modersmål: Arabiska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4068,19 +4072,19 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4090,18 +4094,18 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tyska: Språk och nya medier</t>
+          <t>Svenska som andraspråk II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4111,14 +4115,14 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GTY2N4</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4144,7 +4148,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tyskspråkig nutidslitteratur och litteraturkritik</t>
+          <t>Tyska: Språk och nya medier</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4154,14 +4158,14 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GTY2N4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4187,7 +4191,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tyska III med didaktisk inriktning</t>
+          <t>Tyskspråkig nutidslitteratur och litteraturkritik</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4197,19 +4201,19 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GKI2PX</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4219,18 +4223,18 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Kinesiska: skriftlig tillämpning</t>
+          <t>Tyska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4240,14 +4244,14 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GKI2PX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4273,7 +4277,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Kinesiska i tal och skrift III</t>
+          <t>Kinesiska: skriftlig tillämpning</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4283,14 +4287,14 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GKI2QA</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4305,7 +4309,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -4316,7 +4320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Kinesiska: Kandidatexamensarbete</t>
+          <t>Kinesiska i tal och skrift III</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4326,19 +4330,19 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GEN2QW</t>
+          <t>GKI2QA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4348,18 +4352,18 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Engelska, Språkdidaktik l</t>
+          <t>Kinesiska: Kandidatexamensarbete</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4369,19 +4373,19 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>GEN2QW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4397,12 +4401,12 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Engelska, Språkdidaktik l</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4412,19 +4416,19 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GFR2R3</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4434,18 +4438,18 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Franska II: Muntlig franska</t>
+          <t>Svenska som andraspråk III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4455,14 +4459,14 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>GFR2R3</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4488,7 +4492,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Franska II med didaktisk inriktning</t>
+          <t>Franska II: Muntlig franska</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4498,19 +4502,19 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4526,12 +4530,12 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
+          <t>Franska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4541,19 +4545,19 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GEN2RZ</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4563,18 +4567,18 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
+          <t>Interkulturella litteraturstudier: Litteratur och politik i det samtida Afrika</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4584,19 +4588,19 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>AJP278</t>
+          <t>GEN2RZ</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4612,12 +4616,12 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Teori och metod</t>
+          <t>Engelska för specifika ändamål: Presentationer i akademiska och professionella sammanhang</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4627,14 +4631,14 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>AJP279</t>
+          <t>AJP278</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4660,7 +4664,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
+          <t>Interkulturella litteraturstudier: Teori och metod</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4670,14 +4674,14 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>AJP27A</t>
+          <t>AJP279</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4703,7 +4707,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
+          <t>Interkulturella litteraturstudier: Översättningsprojekt</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4713,14 +4717,14 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>AJP27B</t>
+          <t>AJP27A</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4746,7 +4750,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+          <t>Interkulturella litteraturstudier: Skönlitteratur på originalspråk</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4756,19 +4760,19 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GAR2SQ</t>
+          <t>AJP27B</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4778,18 +4782,18 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Arabiska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Modern arabisk litteratur</t>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4799,19 +4803,19 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GTY2ST</t>
+          <t>GAR2SQ</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4821,18 +4825,18 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Arabiska</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tyska: Tysk grammatik med textkommentar</t>
+          <t>Modern arabisk litteratur</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4842,14 +4846,14 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GTY2SV</t>
+          <t>GTY2ST</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4875,7 +4879,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
+          <t>Tyska: Tysk grammatik med textkommentar</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4885,19 +4889,19 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GEN2VE</t>
+          <t>GTY2SV</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4907,18 +4911,18 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Engelskspråkig litteratur</t>
+          <t>Tyska: Tyskspråkig litteratur och litteraturdidaktik i teori och praktik</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4928,19 +4932,19 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GKI2VL</t>
+          <t>GEN2VE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4956,12 +4960,12 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Kinas kultur och samhälle - introduktionskurs</t>
+          <t>Engelskspråkig litteratur</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4971,19 +4975,19 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GKI2VL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4993,18 +4997,18 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Franska: Språkdidaktik I</t>
+          <t>Kinas kultur och samhälle - introduktionskurs</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5014,14 +5018,14 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5047,7 +5051,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Franska I med didaktisk inriktning</t>
+          <t>Franska: Språkdidaktik I</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5057,19 +5061,19 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>AJP287</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5079,18 +5083,18 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Japanska: Interkulturell kommunikation</t>
+          <t>Franska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5100,19 +5104,19 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>AJP287</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5122,18 +5126,18 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
+          <t>Japanska: Interkulturell kommunikation</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5143,19 +5147,19 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GFR2YU</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5165,18 +5169,18 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Franska: Språkdidaktik II</t>
+          <t>Svenska som andraspråk för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5186,19 +5190,19 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GRY325</t>
+          <t>GFR2YU</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5208,18 +5212,18 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Introduktion till rysk opera 2</t>
+          <t>Franska: Språkdidaktik II</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5229,19 +5233,19 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GRY325</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5251,18 +5255,18 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tyska: Språkdidaktik II</t>
+          <t>Introduktion till rysk opera 2</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5272,19 +5276,19 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>AKI28Y</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5294,18 +5298,18 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
+          <t>Tyska: Språkdidaktik II</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5315,19 +5319,19 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GFR35F</t>
+          <t>AKI28Y</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5337,18 +5341,18 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
+          <t>Kinesiska: Avancerad kurs i kinesiska språket</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5358,19 +5362,19 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>GFR35F</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5386,12 +5390,12 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
+          <t>Franska III: Franskspråkig litteratur och litteraturanalys</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5401,19 +5405,19 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GRY36G</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5423,18 +5427,18 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Introduktion till rysk film</t>
+          <t>Modersmål: Arabiska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5444,14 +5448,14 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GRY36H</t>
+          <t>GRY36G</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5477,7 +5481,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sovjetisk och postsovjetisk science fiction-film</t>
+          <t>Introduktion till rysk film</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5487,14 +5491,14 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GRY37X</t>
+          <t>GRY36H</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5509,7 +5513,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -5520,7 +5524,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
+          <t>Sovjetisk och postsovjetisk science fiction-film</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5530,19 +5534,19 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>AFR29D</t>
+          <t>GRY37X</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5552,22 +5556,18 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Ryska</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
+          <t>Ryska för modersmålslärare: språkets struktur i ett kontrastivt perspektiv</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5577,19 +5577,19 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>AJP2A9</t>
+          <t>AFR29D</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5599,18 +5599,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
           <t>2023-12-08</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning franska</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5620,19 +5624,19 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>ATY29E</t>
+          <t>AJP2A9</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5642,22 +5646,18 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
           <t>2023-12-08</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5667,14 +5667,14 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>TY3013</t>
+          <t>ATY29E</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tyska: Modern kvinnolitteratur</t>
+          <t>Interkulturella litteraturstudier: Masterexamensarbete med inriktning tyska</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5714,19 +5714,19 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GIT2A3</t>
+          <t>TY3013</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5736,22 +5736,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2019-06-19</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Italienska B: Muntlig språkfärdighet och kulturkunskap</t>
+          <t>Tyska: Modern kvinnolitteratur</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5761,14 +5761,14 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GIT2T6</t>
+          <t>GIT2A3</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2019-06-19</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Italienska nobelpristagare i litteratur</t>
+          <t>Italienska B: Muntlig språkfärdighet och kulturkunskap</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5808,14 +5808,14 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GIT2TD</t>
+          <t>GIT2T6</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
+          <t>Italienska nobelpristagare i litteratur</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5855,14 +5855,14 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GIT2TE</t>
+          <t>GIT2TD</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Italienska A: Fonetik och muntlig språkfärdighet</t>
+          <t>Italienska A: Italiensk affärskommunikation och -kultur</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5902,14 +5902,14 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GIT2TG</t>
+          <t>GIT2TE</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, norra Italien</t>
+          <t>Italienska A: Fonetik och muntlig språkfärdighet</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5949,14 +5949,14 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TE</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>GIT2TG</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
+          <t>Italienska A: Kultur och samhälle, norra Italien</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5996,14 +5996,14 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GIT2TJ</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
+          <t>Italienska A: Textanalys, en litterär resa i norra Italien</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6043,14 +6043,14 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
+          <t>Italienska A: Textanalys, en litterär resa på de italienska öarna</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6090,14 +6090,14 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GIT2TM</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
+          <t>Italienska A: Kultur och samhälle, de italienska öarna</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6137,14 +6137,14 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GIT2TN</t>
+          <t>GIT2TM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, deckargenren</t>
+          <t>Italienska A: Textanalys, en litterär resa i södra Italien</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6184,14 +6184,14 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GIT2TP</t>
+          <t>GIT2TN</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Italienska A: Kultur och samhälle, mellersta Italien</t>
+          <t>Italienska A: Textanalys, deckargenren</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6231,14 +6231,14 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GIT2TQ</t>
+          <t>GIT2TP</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, en litterär resa i mellersta Italien</t>
+          <t>Italienska A: Kultur och samhälle, mellersta Italien</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6278,14 +6278,14 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y9</t>
+          <t>GIT2TQ</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, familjeskildringar</t>
+          <t>Italienska A: Textanalys, en litterär resa i mellersta Italien</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6325,14 +6325,14 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TQ</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GIT2YA</t>
+          <t>GIT2Y9</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, krig och fred</t>
+          <t>Italienska A: Textanalys, familjeskildringar</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6372,14 +6372,14 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GIT2YB</t>
+          <t>GIT2YA</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
+          <t>Italienska A: Textanalys, krig och fred</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6419,14 +6419,14 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GIT2YC</t>
+          <t>GIT2YB</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
+          <t>Italienska A: Textanalys, det nya millenniets skönlitteratur</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6466,14 +6466,14 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GIT2YD</t>
+          <t>GIT2YC</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, kvinnoskildringar</t>
+          <t>Italienska A: Textanalys, 1900-talets skönlitteratur</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6513,14 +6513,14 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GIT2YE</t>
+          <t>GIT2YD</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Italienska A: Textanalys, barn- och ungdomsskildringar</t>
+          <t>Italienska A: Textanalys, kvinnoskildringar</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6560,19 +6560,19 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GSP39N</t>
+          <t>GIT2YE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6582,18 +6582,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Spanska: Förberedande kurs</t>
+          <t>Italienska A: Textanalys, barn- och ungdomsskildringar</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6603,19 +6607,19 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YE</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GSS39S</t>
+          <t>GSP39N</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6631,12 +6635,12 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom grundskolan</t>
+          <t>Spanska: Förberedande kurs</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6646,14 +6650,14 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GSS39T</t>
+          <t>GSS39S</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6679,7 +6683,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
+          <t>Den globala skolan - undervisning inom grundskolan</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6689,14 +6693,14 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GSS39T</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6722,7 +6726,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
+          <t>Den globala skolan - undervisning inom gymnasieskolan</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6732,19 +6736,19 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>AJP2AH</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6754,18 +6758,18 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Japanska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Klassisk japanska</t>
+          <t>Den globala skolan - undervisning inom vuxenutbildningen</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6775,19 +6779,19 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GEN3BQ</t>
+          <t>AJP2AH</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6797,18 +6801,18 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Japanska</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Teman inom populärlitteraturen</t>
+          <t>Klassisk japanska</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6818,14 +6822,14 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GEN3BR</t>
+          <t>GEN3BQ</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6851,7 +6855,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Kulturella texter och kontexter</t>
+          <t>Teman inom populärlitteraturen</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6861,19 +6865,19 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GSS3BN</t>
+          <t>GEN3BR</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6889,12 +6893,12 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk II med didaktisk inriktning</t>
+          <t>Kulturella texter och kontexter</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6904,19 +6908,19 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GKI3C9</t>
+          <t>GSS3BN</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6926,18 +6930,18 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Kinesiska för affärslivet II</t>
+          <t>Svenska som andraspråk II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6947,14 +6951,14 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>GKI3C9</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6980,7 +6984,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Kinesiska III med didaktisk inriktning</t>
+          <t>Kinesiska för affärslivet II</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6990,19 +6994,19 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GSS3C6</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7018,12 +7022,12 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Kinesiska</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lärande genom fiktionstext i gymnasieskolan</t>
+          <t>Kinesiska III med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7033,19 +7037,19 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GFR3D2</t>
+          <t>GSS3C6</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7055,18 +7059,18 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Franska I med didaktisk inriktning</t>
+          <t>Lärande genom fiktionstext i gymnasieskolan</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7076,14 +7080,14 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GFR3D2</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -7109,7 +7113,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Franska II med didaktisk inriktning</t>
+          <t>Franska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7119,19 +7123,19 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7147,12 +7151,12 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tyska II med didaktisk inriktning</t>
+          <t>Franska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7162,19 +7166,19 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7184,18 +7188,18 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Franska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
+          <t>Tyska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7205,19 +7209,19 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GPR3E5</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7227,18 +7231,18 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Portugisiska</t>
+          <t>Franska</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
+          <t>Franska för lärare i gymnasieskolan, 90 hp (1-90 hp). Ingår i Lärarlyftet</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7248,19 +7252,19 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GPR3E5</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7270,18 +7274,18 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Portugisiska</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+          <t>Kommunikation på arbetsplatsen: Interkulturalitet och inkludering</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7291,19 +7295,19 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>AEN2BR</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7313,18 +7317,18 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
+          <t>Språk-, läs- och skrivutveckling i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7334,19 +7338,19 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>AEN2BR</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7356,18 +7360,18 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
+          <t>Interkulturella litteraturstudier: Akademisk läsning</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7377,19 +7381,19 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GSS3K2</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7399,18 +7403,18 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Svenska som andraspråk</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
+          <t>Språk-, läs- och skrivutveckling i åldrarna 5–9 år</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7420,19 +7424,19 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>GSS3K2</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7442,18 +7446,18 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska som andraspråk</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Engelska II</t>
+          <t>Litteraturdidaktik för ämneslärare i svenska som andraspråk på gymnasial nivå</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7463,19 +7467,19 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7485,18 +7489,18 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
+          <t>Engelska II</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7506,14 +7510,14 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7539,7 +7543,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i förskoleklass och årskurs 1–3 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -7549,19 +7553,19 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>AEN2CT</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7571,18 +7575,18 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Engelska</t>
+          <t>Svenska</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Introduktion till interkulturella litteraturstudier</t>
+          <t>Språk-, läs- och skrivdidaktisk fördjupning för undervisning i årskurs 4–6 utifrån första- och andraspråksperspektiv</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -7592,14 +7596,14 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>AEN2CU</t>
+          <t>AEN2CT</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7625,7 +7629,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Interkulturella litteraturstudier: Magisterexamensarbete</t>
+          <t>Introduktion till interkulturella litteraturstudier</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7635,19 +7639,19 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2CT</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>GIT3KN</t>
+          <t>AEN2CU</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -7663,12 +7667,12 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Italienska</t>
+          <t>Engelska</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Italienska A: Grammatik och skriftlig språkfärdighet</t>
+          <t>Interkulturella litteraturstudier: Magisterexamensarbete</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7678,14 +7682,14 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2CU</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GIT3KQ</t>
+          <t>GIT3KN</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7711,7 +7715,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Italienska B: Grammatik och skriftlig produktion</t>
+          <t>Italienska A: Grammatik och skriftlig språkfärdighet</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7721,14 +7725,14 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KN</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GIT3KR</t>
+          <t>GIT3KQ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7754,7 +7758,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Italienska B: Litteraturhistoria med textanalys</t>
+          <t>Italienska B: Grammatik och skriftlig produktion</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7764,19 +7768,19 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KQ</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GSP3KS</t>
+          <t>GIT3KR</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -7792,12 +7796,12 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spanska</t>
+          <t>Italienska</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Spanska II med didaktisk inriktning</t>
+          <t>Italienska B: Litteraturhistoria med textanalys</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7807,14 +7811,14 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KR</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GSP3KT</t>
+          <t>GSP3KS</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7840,7 +7844,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Spanska II: Från inbördeskriget till nutiden: Litteratur, film och samhälle i Spanien</t>
+          <t>Spanska II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7850,14 +7854,14 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GSP3KU</t>
+          <t>GSP3KT</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7883,7 +7887,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Spanska II: Skriftlig språkfärdighet och grammatik</t>
+          <t>Spanska II: Från inbördeskriget till nutiden: Litteratur, film och samhälle i Spanien</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7893,14 +7897,14 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KT</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GSP3KV</t>
+          <t>GSP3KU</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7926,7 +7930,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Spanska II: Språklig variation i den spansktalande världen</t>
+          <t>Spanska II: Skriftlig språkfärdighet och grammatik</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7936,19 +7940,19 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KU</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GTY3KG</t>
+          <t>GSP3KV</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -7964,12 +7968,12 @@
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tyska</t>
+          <t>Spanska</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tyska I med didaktisk inriktning</t>
+          <t>Spanska II: Språklig variation i den spansktalande världen</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7979,14 +7983,14 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KV</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GTY3KJ</t>
+          <t>GTY3KG</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -8012,7 +8016,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tyska I: Tysk grammatik</t>
+          <t>Tyska I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -8022,14 +8026,14 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KG</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GTY3KK</t>
+          <t>GTY3KJ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -8055,7 +8059,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Tyska I: Skrivande och AI</t>
+          <t>Tyska I: Tysk grammatik</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8065,19 +8069,19 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KJ</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>BSV22A</t>
+          <t>GTY3KK</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8087,18 +8091,18 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Svenska</t>
+          <t>Tyska</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Baskurs i svenska för lärarutbildning</t>
+          <t>Tyska I: Skrivande och AI</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8108,7 +8112,7 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BSV22A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KK</t>
         </is>
       </c>
     </row>
